--- a/fees.xlsx
+++ b/fees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Shlok Parekh\Downloads\Course-Verifier-3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6CB06D-983A-4B86-A53A-CEB4511BBBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB48CB16-288A-4436-9D56-CD9B184F0152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="1633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="1639">
   <si>
     <t>Acharya Nagarjuna University</t>
   </si>
@@ -4165,13 +4165,7 @@
     <t>https://www.fordham.edu/student-financial-services/tuition-and-payments/graduate-tuition/graduate-school-of-arts-and-sciences/</t>
   </si>
   <si>
-    <t>https://drexel.edu/drexelcentral/cost/tuition/graduate#on-campus</t>
-  </si>
-  <si>
     <t>https://sacd.sdsu.edu/financial-aid/financial-aid/eligibility/cost-of-attendance/cost-of-attendance-tables/graduate-and-doctoral-students</t>
-  </si>
-  <si>
-    <t>https://financialaid.ku.edu/calculate-costs/tuition-and-fees/undergraduate</t>
   </si>
   <si>
     <t>https://admissions.gsu.edu/tuition/#grad-tuition</t>
@@ -4950,6 +4944,30 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1eLKgIifsoRnP6sH1qmscIa5L4xDSfoEf/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gER0ekI5AEE6M2Ui-dRfJMRhO0GiEHg3/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18eZQqpRwmRXmItBEYCQEXNEBoHbwrQ1V/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://world.ku.edu/costs</t>
+  </si>
+  <si>
+    <t>Cybersecurity – Graduate Certificate</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xtu4zypcdZNeD5XCcibs7viTCO-0makc/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Cybersecurity Offense and Defense Graduate Certificate</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xFhajqtfm4bnrfRn4rwcXVuZS7pY7MXZ/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Ohio State University</t>
   </si>
 </sst>
 </file>
@@ -5344,8 +5362,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50FA0121-CF7E-4AD2-B2F5-45CDEB14AA45}" name="Table1" displayName="Table1" ref="A1:C2377" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
-  <autoFilter ref="A1:C2377" xr:uid="{50FA0121-CF7E-4AD2-B2F5-45CDEB14AA45}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50FA0121-CF7E-4AD2-B2F5-45CDEB14AA45}" name="Table1" displayName="Table1" ref="A1:C2376" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+  <autoFilter ref="A1:C2376" xr:uid="{50FA0121-CF7E-4AD2-B2F5-45CDEB14AA45}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{11ED7623-F105-4C85-B717-A2969B5298C0}" name="Institute Name" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{FC966060-0194-46B1-8852-472547F32F34}" name="Course Name" dataDxfId="1"/>
@@ -5672,7 +5690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E2226D-97D2-401F-BDCC-01753570F9EF}">
-  <dimension ref="A1:C2376"/>
+  <dimension ref="A1:C2375"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="108.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -7196,7 +7214,7 @@
         <v>224</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7207,7 +7225,7 @@
         <v>167</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7218,7 +7236,7 @@
         <v>107</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7229,7 +7247,7 @@
         <v>220</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7240,7 +7258,7 @@
         <v>229</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7251,7 +7269,7 @@
         <v>231</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7262,7 +7280,7 @@
         <v>233</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7273,7 +7291,7 @@
         <v>158</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7284,7 +7302,7 @@
         <v>235</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7295,7 +7313,7 @@
         <v>217</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7306,7 +7324,7 @@
         <v>237</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7317,7 +7335,7 @@
         <v>71</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7328,7 +7346,7 @@
         <v>239</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7339,7 +7357,7 @@
         <v>241</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7350,7 +7368,7 @@
         <v>243</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7361,7 +7379,7 @@
         <v>244</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7372,7 +7390,7 @@
         <v>245</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7383,7 +7401,7 @@
         <v>246</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7394,7 +7412,7 @@
         <v>248</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7405,7 +7423,7 @@
         <v>250</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7416,7 +7434,7 @@
         <v>252</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7427,7 +7445,7 @@
         <v>254</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7449,7 +7467,7 @@
         <v>175</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7460,7 +7478,7 @@
         <v>81</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11134,7 +11152,7 @@
         <v>973</v>
       </c>
       <c r="C496" s="12" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11145,7 +11163,7 @@
         <v>975</v>
       </c>
       <c r="C497" s="12" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11156,7 +11174,7 @@
         <v>977</v>
       </c>
       <c r="C498" s="12" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11167,7 +11185,7 @@
         <v>964</v>
       </c>
       <c r="C499" s="12" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11178,7 +11196,7 @@
         <v>982</v>
       </c>
       <c r="C500" s="12" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11189,7 +11207,7 @@
         <v>984</v>
       </c>
       <c r="C501" s="12" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11200,7 +11218,7 @@
         <v>985</v>
       </c>
       <c r="C502" s="12" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11211,7 +11229,7 @@
         <v>971</v>
       </c>
       <c r="C503" s="12" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11222,7 +11240,7 @@
         <v>988</v>
       </c>
       <c r="C504" s="12" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11233,7 +11251,7 @@
         <v>971</v>
       </c>
       <c r="C505" s="12" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11244,7 +11262,7 @@
         <v>991</v>
       </c>
       <c r="C506" s="12" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11255,7 +11273,7 @@
         <v>992</v>
       </c>
       <c r="C507" s="12" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11266,7 +11284,7 @@
         <v>994</v>
       </c>
       <c r="C508" s="12" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11277,7 +11295,7 @@
         <v>996</v>
       </c>
       <c r="C509" s="12" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11288,7 +11306,7 @@
         <v>971</v>
       </c>
       <c r="C510" s="12" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11299,7 +11317,7 @@
         <v>998</v>
       </c>
       <c r="C511" s="12" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11310,7 +11328,7 @@
         <v>1000</v>
       </c>
       <c r="C512" s="12" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11321,7 +11339,7 @@
         <v>998</v>
       </c>
       <c r="C513" s="12" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11332,7 +11350,7 @@
         <v>1003</v>
       </c>
       <c r="C514" s="12" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11343,7 +11361,7 @@
         <v>1004</v>
       </c>
       <c r="C515" s="12" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11354,7 +11372,7 @@
         <v>1006</v>
       </c>
       <c r="C516" s="12" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11365,7 +11383,7 @@
         <v>1008</v>
       </c>
       <c r="C517" s="12" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11376,7 +11394,7 @@
         <v>1010</v>
       </c>
       <c r="C518" s="12" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11387,7 +11405,7 @@
         <v>1012</v>
       </c>
       <c r="C519" s="12" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11398,7 +11416,7 @@
         <v>1014</v>
       </c>
       <c r="C520" s="12" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11409,7 +11427,7 @@
         <v>1016</v>
       </c>
       <c r="C521" s="12" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11420,7 +11438,7 @@
         <v>998</v>
       </c>
       <c r="C522" s="12" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11431,7 +11449,7 @@
         <v>1018</v>
       </c>
       <c r="C523" s="12" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11442,7 +11460,7 @@
         <v>1014</v>
       </c>
       <c r="C524" s="12" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11453,7 +11471,7 @@
         <v>1021</v>
       </c>
       <c r="C525" s="12" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11464,7 +11482,7 @@
         <v>1022</v>
       </c>
       <c r="C526" s="12" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11475,7 +11493,7 @@
         <v>1014</v>
       </c>
       <c r="C527" s="12" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11486,7 +11504,7 @@
         <v>980</v>
       </c>
       <c r="C528" s="12" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11497,7 +11515,7 @@
         <v>1025</v>
       </c>
       <c r="C529" s="12" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11508,7 +11526,7 @@
         <v>1027</v>
       </c>
       <c r="C530" s="12" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11519,7 +11537,7 @@
         <v>969</v>
       </c>
       <c r="C531" s="12" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11530,7 +11548,7 @@
         <v>1029</v>
       </c>
       <c r="C532" s="12" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11541,7 +11559,7 @@
         <v>973</v>
       </c>
       <c r="C533" s="12" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11552,7 +11570,7 @@
         <v>1032</v>
       </c>
       <c r="C534" s="12" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11563,7 +11581,7 @@
         <v>1022</v>
       </c>
       <c r="C535" s="12" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11574,7 +11592,7 @@
         <v>1035</v>
       </c>
       <c r="C536" s="12" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11585,7 +11603,7 @@
         <v>1037</v>
       </c>
       <c r="C537" s="12" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11596,7 +11614,7 @@
         <v>1014</v>
       </c>
       <c r="C538" s="12" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11607,7 +11625,7 @@
         <v>1040</v>
       </c>
       <c r="C539" s="12" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11618,7 +11636,7 @@
         <v>998</v>
       </c>
       <c r="C540" s="12" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11629,7 +11647,7 @@
         <v>1043</v>
       </c>
       <c r="C541" s="12" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11640,7 +11658,7 @@
         <v>1045</v>
       </c>
       <c r="C542" s="12" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11651,7 +11669,7 @@
         <v>971</v>
       </c>
       <c r="C543" s="12" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11662,7 +11680,7 @@
         <v>1014</v>
       </c>
       <c r="C544" s="12" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11673,7 +11691,7 @@
         <v>980</v>
       </c>
       <c r="C545" s="12" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11684,7 +11702,7 @@
         <v>998</v>
       </c>
       <c r="C546" s="12" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11695,7 +11713,7 @@
         <v>1049</v>
       </c>
       <c r="C547" s="12" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11706,7 +11724,7 @@
         <v>1051</v>
       </c>
       <c r="C548" s="12" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11717,7 +11735,7 @@
         <v>1053</v>
       </c>
       <c r="C549" s="12" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11728,7 +11746,7 @@
         <v>973</v>
       </c>
       <c r="C550" s="12" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11739,7 +11757,7 @@
         <v>1006</v>
       </c>
       <c r="C551" s="12" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11750,7 +11768,7 @@
         <v>1056</v>
       </c>
       <c r="C552" s="12" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11761,7 +11779,7 @@
         <v>1058</v>
       </c>
       <c r="C553" s="12" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11772,7 +11790,7 @@
         <v>971</v>
       </c>
       <c r="C554" s="12" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11783,7 +11801,7 @@
         <v>998</v>
       </c>
       <c r="C555" s="12" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11794,7 +11812,7 @@
         <v>1022</v>
       </c>
       <c r="C556" s="12" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11805,7 +11823,7 @@
         <v>1062</v>
       </c>
       <c r="C557" s="12" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11816,7 +11834,7 @@
         <v>1006</v>
       </c>
       <c r="C558" s="12" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11827,7 +11845,7 @@
         <v>969</v>
       </c>
       <c r="C559" s="12" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11838,7 +11856,7 @@
         <v>969</v>
       </c>
       <c r="C560" s="12" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11849,7 +11867,7 @@
         <v>1067</v>
       </c>
       <c r="C561" s="12" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11860,7 +11878,7 @@
         <v>1016</v>
       </c>
       <c r="C562" s="12" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11871,7 +11889,7 @@
         <v>1069</v>
       </c>
       <c r="C563" s="12" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11882,7 +11900,7 @@
         <v>973</v>
       </c>
       <c r="C564" s="12" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11893,7 +11911,7 @@
         <v>1072</v>
       </c>
       <c r="C565" s="12" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11904,7 +11922,7 @@
         <v>1073</v>
       </c>
       <c r="C566" s="12" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11915,7 +11933,7 @@
         <v>1075</v>
       </c>
       <c r="C567" s="12" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11926,7 +11944,7 @@
         <v>1077</v>
       </c>
       <c r="C568" s="12" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11937,7 +11955,7 @@
         <v>1062</v>
       </c>
       <c r="C569" s="12" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11948,7 +11966,7 @@
         <v>1080</v>
       </c>
       <c r="C570" s="12" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11959,7 +11977,7 @@
         <v>971</v>
       </c>
       <c r="C571" s="12" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11970,7 +11988,7 @@
         <v>1083</v>
       </c>
       <c r="C572" s="12" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11981,7 +11999,7 @@
         <v>1085</v>
       </c>
       <c r="C573" s="12" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11992,7 +12010,7 @@
         <v>1087</v>
       </c>
       <c r="C574" s="12" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12003,7 +12021,7 @@
         <v>1089</v>
       </c>
       <c r="C575" s="12" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12014,7 +12032,7 @@
         <v>1091</v>
       </c>
       <c r="C576" s="12" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12025,7 +12043,7 @@
         <v>1092</v>
       </c>
       <c r="C577" s="12" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12036,7 +12054,7 @@
         <v>1093</v>
       </c>
       <c r="C578" s="12" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12047,7 +12065,7 @@
         <v>1095</v>
       </c>
       <c r="C579" s="12" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12058,7 +12076,7 @@
         <v>971</v>
       </c>
       <c r="C580" s="12" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12069,7 +12087,7 @@
         <v>1096</v>
       </c>
       <c r="C581" s="12" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12080,7 +12098,7 @@
         <v>1097</v>
       </c>
       <c r="C582" s="12" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12091,7 +12109,7 @@
         <v>1098</v>
       </c>
       <c r="C583" s="12" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="584" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12102,7 +12120,7 @@
         <v>1100</v>
       </c>
       <c r="C584" s="12" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12113,7 +12131,7 @@
         <v>1102</v>
       </c>
       <c r="C585" s="12" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12124,7 +12142,7 @@
         <v>1104</v>
       </c>
       <c r="C586" s="12" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12135,7 +12153,7 @@
         <v>1106</v>
       </c>
       <c r="C587" s="12" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12146,7 +12164,7 @@
         <v>1108</v>
       </c>
       <c r="C588" s="12" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12157,7 +12175,7 @@
         <v>1109</v>
       </c>
       <c r="C589" s="12" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12168,7 +12186,7 @@
         <v>1110</v>
       </c>
       <c r="C590" s="12" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12179,7 +12197,7 @@
         <v>1112</v>
       </c>
       <c r="C591" s="12" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12190,7 +12208,7 @@
         <v>1114</v>
       </c>
       <c r="C592" s="12" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12201,7 +12219,7 @@
         <v>1115</v>
       </c>
       <c r="C593" s="12" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12212,7 +12230,7 @@
         <v>1117</v>
       </c>
       <c r="C594" s="12" t="s">
-        <v>1373</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12223,7 +12241,7 @@
         <v>1062</v>
       </c>
       <c r="C595" s="12" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12234,7 +12252,7 @@
         <v>1120</v>
       </c>
       <c r="C596" s="12" t="s">
-        <v>1371</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="597" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12245,7 +12263,7 @@
         <v>1121</v>
       </c>
       <c r="C597" s="12" t="s">
-        <v>1371</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -12256,7 +12274,7 @@
         <v>1122</v>
       </c>
       <c r="C598" s="12" t="s">
-        <v>1371</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13394,46 +13412,46 @@
     </row>
     <row r="702" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A702" s="1" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="B702" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C702" s="12" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="703" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A703" s="1" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="B703" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C703" s="12" t="s">
         <v>1479</v>
-      </c>
-      <c r="C703" s="12" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="704" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A704" s="1" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C704" s="12" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="705" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A705" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B705" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="B705" s="1" t="s">
-        <v>1484</v>
-      </c>
       <c r="C705" s="12" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="706" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13441,10 +13459,10 @@
         <v>296</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C706" s="12" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="707" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13452,76 +13470,76 @@
         <v>296</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="C707" s="12" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="708" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A708" s="1" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="C708" s="12" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="709" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A709" s="1" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B709" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C709" s="12" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="710" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A710" s="1" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="C710" s="12" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="711" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A711" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B711" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="B711" s="1" t="s">
-        <v>1494</v>
-      </c>
       <c r="C711" s="12" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="712" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A712" s="1" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="B712" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C712" s="12" t="s">
         <v>1497</v>
-      </c>
-      <c r="C712" s="12" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="713" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A713" s="1" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="B713" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C713" s="12" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="714" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13537,35 +13555,35 @@
     </row>
     <row r="715" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A715" s="1" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="C715" s="12" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="716" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A716" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B716" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="B716" s="1" t="s">
+      <c r="C716" s="12" t="s">
         <v>1503</v>
-      </c>
-      <c r="C716" s="12" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A717" s="1" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C717" s="12" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="718" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13584,7 +13602,7 @@
         <v>299</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="C719" s="12" t="s">
         <v>815</v>
@@ -13592,13 +13610,13 @@
     </row>
     <row r="720" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A720" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C720" s="12" t="s">
         <v>1507</v>
-      </c>
-      <c r="B720" s="1" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C720" s="12" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13606,10 +13624,10 @@
         <v>60</v>
       </c>
       <c r="B721" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C721" s="12" t="s">
         <v>1510</v>
-      </c>
-      <c r="C721" s="12" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="722" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13617,10 +13635,10 @@
         <v>60</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="C722" s="12" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="723" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13628,65 +13646,65 @@
         <v>230</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="C723" s="12" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="724" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A724" s="1" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B724" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C724" s="12" t="s">
         <v>1515</v>
-      </c>
-      <c r="C724" s="12" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="725" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A725" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C725" s="12" t="s">
         <v>1518</v>
-      </c>
-      <c r="B725" s="1" t="s">
-        <v>1519</v>
-      </c>
-      <c r="C725" s="12" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="726" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A726" s="1" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="B726" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C726" s="12" t="s">
         <v>1522</v>
-      </c>
-      <c r="C726" s="12" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="727" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A727" s="1" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="B727" s="1" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C727" s="12" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="728" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A728" s="1" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="B728" s="1" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C728" s="12" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="729" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13702,79 +13720,79 @@
     </row>
     <row r="730" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A730" s="1" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="B730" s="1" t="s">
         <v>303</v>
       </c>
       <c r="C730" s="12" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="731" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A731" s="1" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="B731" s="1" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="C731" s="12" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="732" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A732" s="1" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="C732" s="12" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="733" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A733" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B733" s="1" t="s">
         <v>1532</v>
       </c>
-      <c r="B733" s="1" t="s">
-        <v>1534</v>
-      </c>
       <c r="C733" s="12" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="734" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A734" s="1" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B734" s="1" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="C734" s="12" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="735" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A735" s="1" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="B735" s="1" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="C735" s="12" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="736" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A736" s="1" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="C736" s="12" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="737" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13812,112 +13830,112 @@
     </row>
     <row r="740" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A740" s="1" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C740" s="12" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="741" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A741" s="1" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="C741" s="12" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="742" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A742" s="1" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="B742" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C742" s="12" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="743" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A743" s="1" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="B743" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C743" s="12" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="744" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A744" s="1" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C744" s="12" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="745" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A745" s="1" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="B745" s="1" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="C745" s="12" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="746" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A746" s="1" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="B746" s="1" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C746" s="12" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="747" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A747" s="1" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="B747" s="1" t="s">
         <v>309</v>
       </c>
       <c r="C747" s="12" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="748" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A748" s="1" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="B748" s="1" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="C748" s="12" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="749" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A749" s="1" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="B749" s="1" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="C749" s="12" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="750" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14054,79 +14072,79 @@
     </row>
     <row r="762" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A762" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C762" s="12" t="s">
         <v>1572</v>
-      </c>
-      <c r="B762" s="1" t="s">
-        <v>1573</v>
-      </c>
-      <c r="C762" s="12" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="763" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A763" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C763" s="12" t="s">
         <v>1575</v>
-      </c>
-      <c r="B763" s="1" t="s">
-        <v>1576</v>
-      </c>
-      <c r="C763" s="12" t="s">
-        <v>1577</v>
       </c>
     </row>
     <row r="764" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A764" s="1" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="B764" s="1" t="s">
         <v>152</v>
       </c>
       <c r="C764" s="12" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="765" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A765" s="1" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="B765" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C765" s="12" t="s">
         <v>1580</v>
-      </c>
-      <c r="C765" s="12" t="s">
-        <v>1582</v>
       </c>
     </row>
     <row r="766" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A766" s="1" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="B766" s="1" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="C766" s="12" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="767" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A767" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C767" s="12" t="s">
         <v>1585</v>
-      </c>
-      <c r="B767" s="1" t="s">
-        <v>1586</v>
-      </c>
-      <c r="C767" s="12" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="768" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A768" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C768" s="12" t="s">
         <v>1588</v>
-      </c>
-      <c r="B768" s="1" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C768" s="12" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="769" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14134,65 +14152,65 @@
         <v>189</v>
       </c>
       <c r="B769" s="1" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="C769" s="12" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="770" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A770" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C770" s="12" t="s">
         <v>1594</v>
-      </c>
-      <c r="B770" s="1" t="s">
-        <v>1595</v>
-      </c>
-      <c r="C770" s="12" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="771" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A771" s="1" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="B771" s="1" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="C771" s="12" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="772" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A772" s="1" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="B772" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C772" s="12" t="s">
         <v>1600</v>
-      </c>
-      <c r="C772" s="12" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="773" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A773" s="1" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="B773" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C773" s="12" t="s">
         <v>1604</v>
-      </c>
-      <c r="C773" s="12" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="774" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A774" s="1" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="B774" s="1" t="s">
         <v>324</v>
       </c>
       <c r="C774" s="12" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="775" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14200,7 +14218,7 @@
         <v>281</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="C775" s="12" t="s">
         <v>921</v>
@@ -14208,13 +14226,13 @@
     </row>
     <row r="776" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C776" s="12" t="s">
         <v>1609</v>
-      </c>
-      <c r="B776" s="1" t="s">
-        <v>1610</v>
-      </c>
-      <c r="C776" s="12" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14230,13 +14248,13 @@
     </row>
     <row r="778" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A778" s="1" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="B778" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C778" s="12" t="s">
         <v>1612</v>
-      </c>
-      <c r="C778" s="12" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="779" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14247,80 +14265,96 @@
         <v>336</v>
       </c>
       <c r="C779" s="12" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="780" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A780" s="29" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B780" s="29" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C780" s="12" t="s">
         <v>1616</v>
-      </c>
-      <c r="B780" s="29" t="s">
-        <v>1617</v>
-      </c>
-      <c r="C780" s="12" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="781" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A781" s="1" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="B781" s="1" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="C781" s="28" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="782" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A782" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C782" s="12" t="s">
         <v>1621</v>
-      </c>
-      <c r="B782" s="1" t="s">
-        <v>1622</v>
-      </c>
-      <c r="C782" s="12" t="s">
-        <v>1623</v>
       </c>
     </row>
     <row r="783" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A783" s="1" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="B783" s="1" t="s">
         <v>1145</v>
       </c>
       <c r="C783" s="12" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="784" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A784" s="1" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="B784" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C784" s="12" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="785" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A785" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C785" s="12" t="s">
         <v>1630</v>
       </c>
-      <c r="B785" s="1" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C785" s="12" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C786" s="22"/>
-    </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C787" s="22"/>
+    </row>
+    <row r="786" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A786" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C786" s="12" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A787" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B787" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C787" s="12" t="s">
+        <v>1637</v>
+      </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C788" s="22"/>
@@ -19085,9 +19119,6 @@
     </row>
     <row r="2375" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C2375" s="22"/>
-    </row>
-    <row r="2376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C2376" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19537,213 +19568,215 @@
     <hyperlink ref="C601" r:id="rId444" xr:uid="{4AFC9F05-548F-44E8-90F3-81253EC05543}"/>
     <hyperlink ref="C600" r:id="rId445" xr:uid="{6891D883-6AA3-4692-924E-157B6C9D0857}"/>
     <hyperlink ref="C599" r:id="rId446" xr:uid="{B4D01991-686F-48D0-842B-3E97940F10DD}"/>
-    <hyperlink ref="C598" r:id="rId447" location="on-campus" xr:uid="{2E405313-56E5-47ED-ADCC-33BFDADDB2D3}"/>
-    <hyperlink ref="C597" r:id="rId448" location="on-campus" xr:uid="{C455A730-9747-43C0-B999-37BF93297755}"/>
-    <hyperlink ref="C596" r:id="rId449" location="on-campus" xr:uid="{6F8B80C4-3E81-4866-BA72-94A5D49B1C9B}"/>
-    <hyperlink ref="C595" r:id="rId450" xr:uid="{18EB0A22-4CFD-44BE-BB55-917DCEFA9CA6}"/>
-    <hyperlink ref="C594" r:id="rId451" xr:uid="{E6393A6C-F5B7-4509-82A1-5B6665A7C821}"/>
-    <hyperlink ref="C593" r:id="rId452" location="grad-tuition" xr:uid="{582AFF7E-8573-4189-986B-D6E98B1A4DA5}"/>
-    <hyperlink ref="C592" r:id="rId453" location="grad-tuition" xr:uid="{12E2B2B6-E506-417A-B52B-681DFFEE413E}"/>
-    <hyperlink ref="C591" r:id="rId454" location="resident-table" xr:uid="{770C3304-744E-40B0-A99D-2B6E86521C88}"/>
-    <hyperlink ref="C590" r:id="rId455" xr:uid="{3938ED2B-239B-4B09-A824-1CD6F646EB17}"/>
-    <hyperlink ref="C589" r:id="rId456" xr:uid="{5F647715-25EB-4657-8D93-7426C58CB684}"/>
-    <hyperlink ref="C588" r:id="rId457" xr:uid="{10C07F72-DD92-4886-9F7A-5CAF0462B509}"/>
-    <hyperlink ref="C587" r:id="rId458" xr:uid="{5741F3B1-8B60-4B23-ACB2-DA55B686C652}"/>
-    <hyperlink ref="C586" r:id="rId459" xr:uid="{3EFA6110-A11B-457B-8659-72012A54BD3A}"/>
-    <hyperlink ref="C585" r:id="rId460" xr:uid="{80B2DADD-BE3F-4EC7-9C12-3BDAD01813E8}"/>
-    <hyperlink ref="C584" r:id="rId461" xr:uid="{FC1DFD8B-AB65-442C-8A3F-D25996D5D4C0}"/>
-    <hyperlink ref="C583" r:id="rId462" xr:uid="{786B9AB5-33CB-4B37-B2A1-9FA3A61D0DD6}"/>
-    <hyperlink ref="C582" r:id="rId463" xr:uid="{7531FEF1-ECCA-4CD5-91DF-310ADDD8620D}"/>
-    <hyperlink ref="C581" r:id="rId464" xr:uid="{2D4038F2-67F3-48E2-8D1B-4C350C4242A7}"/>
-    <hyperlink ref="C580" r:id="rId465" xr:uid="{8C1E2096-E167-499A-AB57-FAC294ECEDCD}"/>
-    <hyperlink ref="C579" r:id="rId466" xr:uid="{A1C64A08-55EA-4EB5-89B5-0F7F4F342B4E}"/>
-    <hyperlink ref="C578" r:id="rId467" xr:uid="{CB94780F-B641-4597-9CE1-45FFF6AD4B24}"/>
-    <hyperlink ref="C576:C577" r:id="rId468" display="https://engineering.washu.edu/academics/graduate-admissions/tuition-financial-assistance/index.html" xr:uid="{94704AD1-79B0-45E6-9E54-DA16CCCFC1D5}"/>
-    <hyperlink ref="C575" r:id="rId469" xr:uid="{2F7C4AEF-B867-4041-A0A5-E963758EC26E}"/>
-    <hyperlink ref="C574" r:id="rId470" xr:uid="{58CC675F-324C-49CC-8E26-E01400549445}"/>
-    <hyperlink ref="C573" r:id="rId471" xr:uid="{E76C2F8E-D177-4AF5-B631-AE2D0BE2CE97}"/>
-    <hyperlink ref="C572" r:id="rId472" xr:uid="{23695B31-E2B8-4257-8223-E7539FD64A00}"/>
-    <hyperlink ref="C571" r:id="rId473" xr:uid="{6076A241-D906-428A-BAD4-365660712C56}"/>
-    <hyperlink ref="C570" r:id="rId474" xr:uid="{0583E2AF-776E-4CFE-95E6-39AB0ECC45D5}"/>
-    <hyperlink ref="C140" r:id="rId475" xr:uid="{3FA076C9-5495-4945-A4AE-B4C9F3E2D651}"/>
-    <hyperlink ref="C139" r:id="rId476" xr:uid="{51F46025-FA8D-4F49-987B-8B7ACF84D46B}"/>
-    <hyperlink ref="C138" r:id="rId477" xr:uid="{96F590C7-1AE4-4D20-949F-27E943D8E9DD}"/>
-    <hyperlink ref="C141" r:id="rId478" xr:uid="{FBABABEF-6172-480C-B6C6-FFDD1742D1BC}"/>
-    <hyperlink ref="C142" r:id="rId479" xr:uid="{1FD9EFE7-3C5D-4629-AAB4-3BA4E758F297}"/>
-    <hyperlink ref="C145" r:id="rId480" xr:uid="{E34B10FB-C082-4D97-951B-BA7BA04C2BFF}"/>
-    <hyperlink ref="C144" r:id="rId481" xr:uid="{FC90D068-9B74-4B67-8A58-04475F302838}"/>
-    <hyperlink ref="C143" r:id="rId482" xr:uid="{124C2F78-505A-46EC-BCEF-939FE257A92C}"/>
-    <hyperlink ref="C146" r:id="rId483" xr:uid="{2B0BC0FA-A684-4FE8-9ADA-F341D5031D9C}"/>
-    <hyperlink ref="C147" r:id="rId484" xr:uid="{57EA4E59-7D86-4715-AA19-80FD2129EA16}"/>
-    <hyperlink ref="C569" r:id="rId485" xr:uid="{174134F4-7EA9-406B-AC8D-971EFE1F24E3}"/>
-    <hyperlink ref="C568" r:id="rId486" xr:uid="{4CE185F9-CED9-438C-86C9-851D7566A9A7}"/>
-    <hyperlink ref="C567" r:id="rId487" xr:uid="{A20522D3-BFD6-4189-AD43-2A60AD94F7C6}"/>
-    <hyperlink ref="C566" r:id="rId488" xr:uid="{BF8FFE00-58C9-498F-9FB7-53370E4F76E6}"/>
-    <hyperlink ref="C565" r:id="rId489" xr:uid="{BA78BBFE-BA3A-4567-8842-D9DAC7BD4114}"/>
-    <hyperlink ref="C564" r:id="rId490" xr:uid="{AB8D8480-94A0-4F6D-94DD-954187AAF1CA}"/>
-    <hyperlink ref="C563" r:id="rId491" xr:uid="{F485B58C-0963-4817-B71B-E1D073DD028E}"/>
-    <hyperlink ref="C562" r:id="rId492" xr:uid="{CC59DEAF-1EFF-452A-ACA7-DC3FF58078F5}"/>
-    <hyperlink ref="C561" r:id="rId493" xr:uid="{D1F90F1B-7BD7-45D3-820D-8E747A8C92D3}"/>
-    <hyperlink ref="C560" r:id="rId494" xr:uid="{5DBD82ED-050A-43F8-8857-D34C7E4480CF}"/>
-    <hyperlink ref="C559" r:id="rId495" xr:uid="{F412E9FE-4C23-4374-A052-04C1F51DECF3}"/>
-    <hyperlink ref="C558" r:id="rId496" xr:uid="{449D0218-88EB-46E3-B0E4-2396D7F735E4}"/>
-    <hyperlink ref="C557" r:id="rId497" xr:uid="{7D6EF784-1F9A-4B36-90F6-AE8F627E5B8E}"/>
-    <hyperlink ref="C556" r:id="rId498" xr:uid="{D8B5388E-51D0-496B-A7D3-74F358D037B4}"/>
-    <hyperlink ref="C555" r:id="rId499" xr:uid="{F9F24C9F-2E3E-4D43-A177-0E5D2ACFC3DB}"/>
-    <hyperlink ref="C554" r:id="rId500" xr:uid="{EBEB933D-B423-41C9-9335-42397362BD62}"/>
-    <hyperlink ref="C553" r:id="rId501" xr:uid="{F4DC805F-FE7E-4A06-B475-D0E38D707111}"/>
-    <hyperlink ref="C552" r:id="rId502" xr:uid="{20418103-4EDF-42B7-9CBC-B36B42BA50FC}"/>
-    <hyperlink ref="C551" r:id="rId503" xr:uid="{6E09CD2C-B320-448D-A7EA-AB8C174E2970}"/>
-    <hyperlink ref="C550" r:id="rId504" xr:uid="{6E97C3B1-4CCB-44C9-ADA0-F640C6D728C6}"/>
-    <hyperlink ref="C549" r:id="rId505" xr:uid="{A3CBBBD1-2612-4CDD-81EF-7B827025D704}"/>
-    <hyperlink ref="C548" r:id="rId506" xr:uid="{889BBB9F-9281-42CD-8162-9C391B05D0E9}"/>
-    <hyperlink ref="C547" r:id="rId507" xr:uid="{3DB128D7-B924-44A9-A7C9-E6BC79E97B53}"/>
-    <hyperlink ref="C546" r:id="rId508" location="ug" xr:uid="{DC468B40-CC91-45B4-89A6-89B34BED7BF2}"/>
-    <hyperlink ref="C545" r:id="rId509" xr:uid="{33329805-9235-4129-B754-2D7734FBDDC7}"/>
-    <hyperlink ref="C544" r:id="rId510" xr:uid="{891F2F49-6F9D-42A2-B1C4-D4C4DE0F80CE}"/>
-    <hyperlink ref="C543" r:id="rId511" xr:uid="{298C3AFD-57FA-4BA3-8E29-707970F312E7}"/>
-    <hyperlink ref="C542" r:id="rId512" xr:uid="{6B0E6526-0C2D-4948-A6DC-921C8EB514C0}"/>
-    <hyperlink ref="C541" r:id="rId513" xr:uid="{58674F07-58BA-4940-9FD6-19FEB6F9995F}"/>
-    <hyperlink ref="C540" r:id="rId514" xr:uid="{CF302509-B5CB-407F-8B80-DBDE5822D97D}"/>
-    <hyperlink ref="C539" r:id="rId515" xr:uid="{53FFE010-86CC-42DA-BACE-36ECDF356E08}"/>
-    <hyperlink ref="C538" r:id="rId516" xr:uid="{B4314B32-2437-45EE-AA5A-5436BB31A223}"/>
-    <hyperlink ref="C537" r:id="rId517" xr:uid="{644D1C8A-4F41-4B57-8560-02BF758E73C4}"/>
-    <hyperlink ref="C536" r:id="rId518" xr:uid="{E86CD9EA-CFB3-41D9-B477-51F488869BDA}"/>
-    <hyperlink ref="C535" r:id="rId519" xr:uid="{0E4455B9-563E-43B3-9B53-A67F42506607}"/>
-    <hyperlink ref="C534" r:id="rId520" xr:uid="{562E68DB-94AF-45A2-936A-29A55800A148}"/>
-    <hyperlink ref="C533" r:id="rId521" xr:uid="{3A9CECF8-3087-4F4D-9265-80DC3E35D0CD}"/>
-    <hyperlink ref="C532" r:id="rId522" xr:uid="{6D8E7DFC-8EA5-4CD5-A126-6002F2E0A49F}"/>
-    <hyperlink ref="C531" r:id="rId523" xr:uid="{4185B687-50FC-4DC7-AB12-13062EE007F1}"/>
-    <hyperlink ref="C530" r:id="rId524" xr:uid="{9F49DD3E-B4A4-459C-AB78-866AAE5F3740}"/>
-    <hyperlink ref="C529" r:id="rId525" xr:uid="{39591972-9528-46B2-B533-F57A0735C396}"/>
-    <hyperlink ref="C528" r:id="rId526" xr:uid="{6A585B48-9DED-40FF-AAD1-CA36B8D95708}"/>
-    <hyperlink ref="C527" r:id="rId527" xr:uid="{77D0E52D-2981-4747-8803-EF1ED3E783DA}"/>
-    <hyperlink ref="C526" r:id="rId528" location="campus" xr:uid="{52922C32-37C3-4208-A1F7-E78E2A373254}"/>
-    <hyperlink ref="C525" r:id="rId529" location="masters" xr:uid="{D649413F-95A1-4375-9598-286113814371}"/>
-    <hyperlink ref="C524" r:id="rId530" xr:uid="{24A3EBAB-422A-4271-B422-720A28073A9F}"/>
-    <hyperlink ref="C523" r:id="rId531" xr:uid="{88691330-C7B9-467A-98B0-95319440599C}"/>
-    <hyperlink ref="C522" r:id="rId532" xr:uid="{74DC548D-C4A3-4733-AF06-0C7DD6C62157}"/>
-    <hyperlink ref="C521" r:id="rId533" xr:uid="{57365EF2-8AB1-412F-AC9D-E719A61B491A}"/>
-    <hyperlink ref="C520" r:id="rId534" xr:uid="{CA189A21-4B9A-4BB3-B64B-17F20F3049F0}"/>
-    <hyperlink ref="C519" r:id="rId535" xr:uid="{0AE22385-9740-42F1-BA48-F8E80C6C12CB}"/>
-    <hyperlink ref="C518" r:id="rId536" xr:uid="{8F7744FB-5D44-4B28-B752-EEAF67B446C9}"/>
-    <hyperlink ref="C517" r:id="rId537" xr:uid="{284E0EA3-4A3D-4CD0-AB09-51F3DF7D52BD}"/>
-    <hyperlink ref="C516" r:id="rId538" xr:uid="{EAD90F60-C919-4409-876F-FDA530F9D9EA}"/>
-    <hyperlink ref="C515" r:id="rId539" xr:uid="{A8EBE29B-AB58-466D-A3EF-065CFB1AB505}"/>
-    <hyperlink ref="C514" r:id="rId540" xr:uid="{104E7E5B-E107-4FDA-92B8-9CF512BD0F9E}"/>
-    <hyperlink ref="C513" r:id="rId541" xr:uid="{C7E8E7F0-EE55-4307-A285-F9163015384F}"/>
-    <hyperlink ref="C512" r:id="rId542" xr:uid="{7136EEAA-B7A4-423D-B8D2-4805FE4CB0E8}"/>
-    <hyperlink ref="C511" r:id="rId543" xr:uid="{2F6E9089-4464-4A32-B725-83014A8476CB}"/>
-    <hyperlink ref="C510" r:id="rId544" xr:uid="{D857A142-E2FD-451F-96F3-53CF337B9DFF}"/>
-    <hyperlink ref="C509" r:id="rId545" location="ugrad" xr:uid="{AF7624A7-2C13-4F57-A7F2-91499AD42237}"/>
-    <hyperlink ref="C508" r:id="rId546" xr:uid="{E461EA24-B5B5-4A3D-80C4-78BDF2F74205}"/>
-    <hyperlink ref="C507" r:id="rId547" xr:uid="{512D7250-7090-4D3F-9E44-63EA4B71AC1A}"/>
-    <hyperlink ref="C506" r:id="rId548" xr:uid="{0A667B60-C992-483D-82ED-9FE1A7602842}"/>
-    <hyperlink ref="C505" r:id="rId549" xr:uid="{4D1E4B4A-02C1-48DE-AFBE-EEA62554F8FE}"/>
-    <hyperlink ref="C504" r:id="rId550" xr:uid="{FFCA64BE-D68F-4C22-B508-EEDC178D5BBD}"/>
-    <hyperlink ref="C503" r:id="rId551" xr:uid="{527B727E-029F-4D33-9D75-B6891113FFA5}"/>
-    <hyperlink ref="C502" r:id="rId552" location="daytona-beach" xr:uid="{6619E01C-C97E-413A-AE3B-E4E2F21B9D48}"/>
-    <hyperlink ref="C501" r:id="rId553" location="daytona-beach" xr:uid="{FD8E6161-B879-4E13-9A78-61F21A3C7678}"/>
-    <hyperlink ref="C500" r:id="rId554" xr:uid="{F6DE756D-B8DA-4706-AF02-A1F6271A6ACF}"/>
-    <hyperlink ref="C499" r:id="rId555" xr:uid="{22C523A6-EA73-44A9-BFA9-29091694604C}"/>
-    <hyperlink ref="C498" r:id="rId556" xr:uid="{F9693B6F-6879-48C9-A0F7-4BCE9F7C0770}"/>
-    <hyperlink ref="C497" r:id="rId557" xr:uid="{0F1E4574-5A3D-4686-87F2-93F30FC4786A}"/>
-    <hyperlink ref="C496" r:id="rId558" xr:uid="{C947CCBC-4ABC-4909-88A1-891A36C3D143}"/>
-    <hyperlink ref="C148" r:id="rId559" xr:uid="{7F6B9F29-5C0B-44BD-A010-01F97569E946}"/>
-    <hyperlink ref="C149" r:id="rId560" xr:uid="{5BE80C95-BAF0-4A58-9807-04F4F10A3392}"/>
-    <hyperlink ref="C150" r:id="rId561" xr:uid="{25AC73C5-D8D1-4A68-A0ED-2C33B0812D96}"/>
-    <hyperlink ref="C151" r:id="rId562" xr:uid="{20020986-2A6B-4DF5-A8F2-DA0825DA1250}"/>
-    <hyperlink ref="C152" r:id="rId563" xr:uid="{17F73CFB-29AD-46AB-8232-950E37B0E449}"/>
-    <hyperlink ref="C153:C155" r:id="rId564" display="https://legacy.rru.ac.in/wp-content/uploads/2024/05/Fees-Structure-SITAICS-14May2024.pdf" xr:uid="{B02E8987-C0BF-4204-9DEE-15C5487B79D4}"/>
-    <hyperlink ref="C156" r:id="rId565" xr:uid="{425719C5-F52F-47A4-A471-5E9CE58AF26F}"/>
-    <hyperlink ref="C157" r:id="rId566" xr:uid="{B475B03A-FB81-4C71-B29C-70FA7AAFFF80}"/>
-    <hyperlink ref="C159" r:id="rId567" xr:uid="{2DB408F7-F842-4D81-91E1-B7EE65A5333B}"/>
-    <hyperlink ref="C158" r:id="rId568" xr:uid="{2E087C33-3DD1-4C79-9650-FEDFAF3A4CA3}"/>
-    <hyperlink ref="C702" r:id="rId569" xr:uid="{CB6F7D4F-5238-4A25-A57A-5E2CA49D5342}"/>
-    <hyperlink ref="C703" r:id="rId570" xr:uid="{C2947CAE-69C4-4BE5-8DF0-A99CE63CD05B}"/>
-    <hyperlink ref="C704" r:id="rId571" xr:uid="{B185A001-DE46-4EE0-95BB-A4E9B6B6346C}"/>
-    <hyperlink ref="C705" r:id="rId572" xr:uid="{3D7A51E3-B2A6-4C4A-AECD-AD1A1BDE0153}"/>
-    <hyperlink ref="C707" r:id="rId573" xr:uid="{81D9600D-2B5C-4080-927F-A21B1FF13BE9}"/>
-    <hyperlink ref="C706" r:id="rId574" xr:uid="{79FCD9E3-C4DF-4EC5-940E-885C48E301D8}"/>
-    <hyperlink ref="C708" r:id="rId575" xr:uid="{6C7FE20D-7316-4C13-8984-F397B99D740A}"/>
-    <hyperlink ref="C709" r:id="rId576" xr:uid="{C1038379-2771-4E84-9F19-D016F4ECC3E2}"/>
-    <hyperlink ref="C710:C711" r:id="rId577" display="https://drive.google.com/file/d/1fmepJ31Dfjm_qh5g_wunPXVkMUXKCSpc/view?usp=drive_link" xr:uid="{B72A07BB-EE24-4372-A901-142BDEB56755}"/>
-    <hyperlink ref="C712" r:id="rId578" xr:uid="{C95CACC9-22F3-4D48-8ABB-088984800843}"/>
-    <hyperlink ref="C714" r:id="rId579" xr:uid="{857B428D-FF38-4DDB-8BF7-216A91ED3B1E}"/>
-    <hyperlink ref="C713" r:id="rId580" xr:uid="{6F5B5F2A-9EAF-431A-B12D-848D191E74B5}"/>
-    <hyperlink ref="C715" r:id="rId581" xr:uid="{B5F7EFD7-D7A0-447F-8D0B-BEAA0E423624}"/>
-    <hyperlink ref="C716:C717" r:id="rId582" display="https://adypu.edu.in/wp-content/uploads/2024/07/20.ADYPU_Fees-Structure_24_25.pdf" xr:uid="{8E209706-7354-43E9-9E76-780A501BF850}"/>
-    <hyperlink ref="C718" r:id="rId583" xr:uid="{93B84C99-C0B6-427E-B792-003A6B811699}"/>
-    <hyperlink ref="C719" r:id="rId584" xr:uid="{D108B0AB-F2B0-4489-85FF-B2A32E48718F}"/>
-    <hyperlink ref="C720" r:id="rId585" xr:uid="{4A5AE46C-3678-4870-8072-2C019224F376}"/>
-    <hyperlink ref="C721" r:id="rId586" xr:uid="{87423149-8C1C-417F-8927-BA7D7AB22193}"/>
-    <hyperlink ref="C722" r:id="rId587" xr:uid="{45FBAD21-C7D2-4739-92B6-FD2076623CFA}"/>
-    <hyperlink ref="C723" r:id="rId588" xr:uid="{6186688D-F4AE-4360-8BB9-B9A4B17BEDF6}"/>
-    <hyperlink ref="C724" r:id="rId589" xr:uid="{3590360E-D482-446B-9F79-4FFE7C1C073A}"/>
-    <hyperlink ref="C725" r:id="rId590" xr:uid="{BC14503A-7E37-4FFA-9650-52DD0EADF29A}"/>
-    <hyperlink ref="C726" r:id="rId591" xr:uid="{DFDE858C-3C0E-40F6-9020-84277BF915FB}"/>
-    <hyperlink ref="C727" r:id="rId592" xr:uid="{E1D751F8-CB65-4034-804F-EA8E8F306747}"/>
-    <hyperlink ref="C728" r:id="rId593" xr:uid="{8665E79A-CE2F-45D2-BDDF-83DA3585472B}"/>
-    <hyperlink ref="C729" r:id="rId594" xr:uid="{B04D9CA0-2E77-46DA-8B87-8F1D8EF9C049}"/>
-    <hyperlink ref="C730" r:id="rId595" xr:uid="{FC3E61AF-9A93-4DBC-8CA2-A1C543CDB7D8}"/>
-    <hyperlink ref="C731" r:id="rId596" xr:uid="{68780992-6DAA-46A8-B8B4-B4BBA2917299}"/>
-    <hyperlink ref="C732" r:id="rId597" xr:uid="{C7172857-AB2C-429C-B752-E3089788612D}"/>
-    <hyperlink ref="C733" r:id="rId598" xr:uid="{3F50DD60-5393-43B0-8FFA-68A491669212}"/>
-    <hyperlink ref="C734" r:id="rId599" xr:uid="{C2627F34-5141-4887-A16B-CBF356C57E75}"/>
-    <hyperlink ref="C735" r:id="rId600" xr:uid="{EDED4804-2A29-4FCF-B16F-9093CA1F3402}"/>
-    <hyperlink ref="C736" r:id="rId601" xr:uid="{2906778E-2DEE-4AF6-B797-56BD3D3C92ED}"/>
-    <hyperlink ref="C737" r:id="rId602" xr:uid="{CF7BF210-6C7C-4748-B136-7D7D48E92F53}"/>
-    <hyperlink ref="C738" r:id="rId603" xr:uid="{9F8F3B0F-5923-4A92-AA17-551220766D9C}"/>
-    <hyperlink ref="C739" r:id="rId604" xr:uid="{D4072CFA-7E3A-4A31-924C-881FC018FA1A}"/>
-    <hyperlink ref="C741" r:id="rId605" xr:uid="{52487C8C-5AFB-4B5D-B5DF-9746B10422F0}"/>
-    <hyperlink ref="C740" r:id="rId606" xr:uid="{CF4335A8-2F33-49DD-A1EF-E4E9C570D98B}"/>
-    <hyperlink ref="C742" r:id="rId607" xr:uid="{9C63E6AF-038B-4C76-ADBA-E8DAFFC07E08}"/>
-    <hyperlink ref="C743" r:id="rId608" xr:uid="{E8B25F31-922E-4758-B02E-98B6F7060A88}"/>
-    <hyperlink ref="C744" r:id="rId609" xr:uid="{ABBAA515-0609-486C-BF64-FC3D99099187}"/>
-    <hyperlink ref="C745" r:id="rId610" xr:uid="{C00DB4FA-AF1D-4613-90A1-6FA57556076F}"/>
-    <hyperlink ref="C746" r:id="rId611" xr:uid="{CD016168-6D69-4F69-B68F-AA2EC32DFF6B}"/>
-    <hyperlink ref="C747" r:id="rId612" xr:uid="{CBE487E3-FACC-4B31-A120-61DC195C4D23}"/>
-    <hyperlink ref="C748" r:id="rId613" xr:uid="{EA090370-5F35-4063-959B-C8ADF669CEDE}"/>
-    <hyperlink ref="C749" r:id="rId614" xr:uid="{149D1ED3-CD53-4AE1-864A-A603DE5D12BC}"/>
-    <hyperlink ref="C750" r:id="rId615" xr:uid="{F017CC9E-0054-49FE-89AF-2D059AF6377F}"/>
-    <hyperlink ref="C751:C761" r:id="rId616" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{3B4E76B5-095C-45FE-B0CF-148644D9E11A}"/>
-    <hyperlink ref="C762" r:id="rId617" xr:uid="{B9D39B54-5728-4732-ACBF-88C9E7BB69BC}"/>
-    <hyperlink ref="C763" r:id="rId618" xr:uid="{5B64FB65-FE64-4A6B-AC64-EFC901A56244}"/>
-    <hyperlink ref="C764" r:id="rId619" xr:uid="{8C07BE98-0EA8-4A43-AF2B-442367D94176}"/>
-    <hyperlink ref="C765" r:id="rId620" xr:uid="{3355522E-84C3-495A-8C36-08E1DE7E740B}"/>
-    <hyperlink ref="C767" r:id="rId621" xr:uid="{B8C3CA87-1E12-457E-A5EA-C907F81668CD}"/>
-    <hyperlink ref="C768" r:id="rId622" xr:uid="{EC7491DD-D308-4AE6-824C-E20C1B0A063C}"/>
-    <hyperlink ref="C769" r:id="rId623" xr:uid="{CE4036C3-C29B-4E9A-BA2F-4103F4685B9D}"/>
-    <hyperlink ref="C161" r:id="rId624" xr:uid="{8DD02B6F-54A2-4FAC-B961-2C220AA1D943}"/>
-    <hyperlink ref="C162" r:id="rId625" xr:uid="{ED2940C7-EB7F-4547-BEC9-673E028B1F6E}"/>
-    <hyperlink ref="C770" r:id="rId626" xr:uid="{4015FD70-74FB-4621-A2FD-7986807085D5}"/>
-    <hyperlink ref="C771" r:id="rId627" xr:uid="{1F87E026-2DE2-4DBC-83B3-D6B951EA1E3C}"/>
-    <hyperlink ref="C772" r:id="rId628" xr:uid="{D6BE8929-2D3C-4A7B-BBAF-A4A4EE063EF8}"/>
-    <hyperlink ref="C773" r:id="rId629" xr:uid="{9DD1D3EA-72B8-45E8-BDA9-021B474CA435}"/>
-    <hyperlink ref="C774" r:id="rId630" xr:uid="{1BEB74B5-CAC1-4F1D-A056-DDD1E6CDBF96}"/>
-    <hyperlink ref="C775" r:id="rId631" xr:uid="{3073747A-DA6A-4CE0-A0B7-7AA867EE17D6}"/>
-    <hyperlink ref="C776" r:id="rId632" xr:uid="{B4E301A8-90DD-46D6-976D-FBA6A1684A1F}"/>
-    <hyperlink ref="C777" r:id="rId633" xr:uid="{CD3DDDEF-3C39-40EC-8B04-FA8675A7977F}"/>
-    <hyperlink ref="C778" r:id="rId634" xr:uid="{65D284DB-F879-47B9-A268-DFBC28C219E5}"/>
-    <hyperlink ref="C779" r:id="rId635" xr:uid="{3AF0420D-3F28-4CBB-BAE4-39DCD9DAEF50}"/>
-    <hyperlink ref="C51" r:id="rId636" xr:uid="{ECEE7BB5-A33D-4352-A89E-8D249C116DCB}"/>
-    <hyperlink ref="C455" r:id="rId637" xr:uid="{973FDA1F-DE1F-48CE-BE77-75DC093E98AA}"/>
-    <hyperlink ref="C366" r:id="rId638" xr:uid="{4696752E-5EF9-49D9-8362-5A976A1F5B12}"/>
-    <hyperlink ref="C365" r:id="rId639" xr:uid="{36DF91A2-AE4E-448A-A9E7-A1F91838B227}"/>
-    <hyperlink ref="C362" r:id="rId640" xr:uid="{09480EB5-1061-45DB-AA34-BC6317432F73}"/>
-    <hyperlink ref="C359" r:id="rId641" xr:uid="{4C8A3339-5E9D-44A2-851B-38820E24A7C1}"/>
-    <hyperlink ref="C457" r:id="rId642" xr:uid="{635DE0D8-AFDF-4529-93F2-B5CCE74EF50C}"/>
-    <hyperlink ref="C780" r:id="rId643" xr:uid="{BC6B2562-6B84-425C-9B87-36CDC918AC76}"/>
-    <hyperlink ref="C781" r:id="rId644" xr:uid="{D521C8BF-0148-4A06-80F7-96B5FD3E47F7}"/>
-    <hyperlink ref="C782" r:id="rId645" xr:uid="{89DA4F63-868B-410D-8AFE-DEAE3F4D14CF}"/>
-    <hyperlink ref="C783" r:id="rId646" xr:uid="{F240B56A-A908-4554-A031-75ABA7FACF20}"/>
-    <hyperlink ref="C784" r:id="rId647" xr:uid="{C6533D41-F550-4BED-9C7C-02E70C8DFA0D}"/>
-    <hyperlink ref="C766" r:id="rId648" xr:uid="{29B0C30A-FA81-4314-A11E-2CF9021B0C5D}"/>
-    <hyperlink ref="C785" r:id="rId649" xr:uid="{1DD05091-13EF-4185-8598-42B2C13DD25A}"/>
+    <hyperlink ref="C595" r:id="rId447" xr:uid="{18EB0A22-4CFD-44BE-BB55-917DCEFA9CA6}"/>
+    <hyperlink ref="C594" r:id="rId448" xr:uid="{E6393A6C-F5B7-4509-82A1-5B6665A7C821}"/>
+    <hyperlink ref="C593" r:id="rId449" location="grad-tuition" xr:uid="{582AFF7E-8573-4189-986B-D6E98B1A4DA5}"/>
+    <hyperlink ref="C592" r:id="rId450" location="grad-tuition" xr:uid="{12E2B2B6-E506-417A-B52B-681DFFEE413E}"/>
+    <hyperlink ref="C591" r:id="rId451" location="resident-table" xr:uid="{770C3304-744E-40B0-A99D-2B6E86521C88}"/>
+    <hyperlink ref="C590" r:id="rId452" xr:uid="{3938ED2B-239B-4B09-A824-1CD6F646EB17}"/>
+    <hyperlink ref="C589" r:id="rId453" xr:uid="{5F647715-25EB-4657-8D93-7426C58CB684}"/>
+    <hyperlink ref="C588" r:id="rId454" xr:uid="{10C07F72-DD92-4886-9F7A-5CAF0462B509}"/>
+    <hyperlink ref="C587" r:id="rId455" xr:uid="{5741F3B1-8B60-4B23-ACB2-DA55B686C652}"/>
+    <hyperlink ref="C586" r:id="rId456" xr:uid="{3EFA6110-A11B-457B-8659-72012A54BD3A}"/>
+    <hyperlink ref="C585" r:id="rId457" xr:uid="{80B2DADD-BE3F-4EC7-9C12-3BDAD01813E8}"/>
+    <hyperlink ref="C584" r:id="rId458" xr:uid="{FC1DFD8B-AB65-442C-8A3F-D25996D5D4C0}"/>
+    <hyperlink ref="C583" r:id="rId459" xr:uid="{786B9AB5-33CB-4B37-B2A1-9FA3A61D0DD6}"/>
+    <hyperlink ref="C582" r:id="rId460" xr:uid="{7531FEF1-ECCA-4CD5-91DF-310ADDD8620D}"/>
+    <hyperlink ref="C581" r:id="rId461" xr:uid="{2D4038F2-67F3-48E2-8D1B-4C350C4242A7}"/>
+    <hyperlink ref="C580" r:id="rId462" xr:uid="{8C1E2096-E167-499A-AB57-FAC294ECEDCD}"/>
+    <hyperlink ref="C579" r:id="rId463" xr:uid="{A1C64A08-55EA-4EB5-89B5-0F7F4F342B4E}"/>
+    <hyperlink ref="C578" r:id="rId464" xr:uid="{CB94780F-B641-4597-9CE1-45FFF6AD4B24}"/>
+    <hyperlink ref="C576:C577" r:id="rId465" display="https://engineering.washu.edu/academics/graduate-admissions/tuition-financial-assistance/index.html" xr:uid="{94704AD1-79B0-45E6-9E54-DA16CCCFC1D5}"/>
+    <hyperlink ref="C575" r:id="rId466" xr:uid="{2F7C4AEF-B867-4041-A0A5-E963758EC26E}"/>
+    <hyperlink ref="C574" r:id="rId467" xr:uid="{58CC675F-324C-49CC-8E26-E01400549445}"/>
+    <hyperlink ref="C573" r:id="rId468" xr:uid="{E76C2F8E-D177-4AF5-B631-AE2D0BE2CE97}"/>
+    <hyperlink ref="C572" r:id="rId469" xr:uid="{23695B31-E2B8-4257-8223-E7539FD64A00}"/>
+    <hyperlink ref="C571" r:id="rId470" xr:uid="{6076A241-D906-428A-BAD4-365660712C56}"/>
+    <hyperlink ref="C570" r:id="rId471" xr:uid="{0583E2AF-776E-4CFE-95E6-39AB0ECC45D5}"/>
+    <hyperlink ref="C140" r:id="rId472" xr:uid="{3FA076C9-5495-4945-A4AE-B4C9F3E2D651}"/>
+    <hyperlink ref="C139" r:id="rId473" xr:uid="{51F46025-FA8D-4F49-987B-8B7ACF84D46B}"/>
+    <hyperlink ref="C138" r:id="rId474" xr:uid="{96F590C7-1AE4-4D20-949F-27E943D8E9DD}"/>
+    <hyperlink ref="C141" r:id="rId475" xr:uid="{FBABABEF-6172-480C-B6C6-FFDD1742D1BC}"/>
+    <hyperlink ref="C142" r:id="rId476" xr:uid="{1FD9EFE7-3C5D-4629-AAB4-3BA4E758F297}"/>
+    <hyperlink ref="C145" r:id="rId477" xr:uid="{E34B10FB-C082-4D97-951B-BA7BA04C2BFF}"/>
+    <hyperlink ref="C144" r:id="rId478" xr:uid="{FC90D068-9B74-4B67-8A58-04475F302838}"/>
+    <hyperlink ref="C143" r:id="rId479" xr:uid="{124C2F78-505A-46EC-BCEF-939FE257A92C}"/>
+    <hyperlink ref="C146" r:id="rId480" xr:uid="{2B0BC0FA-A684-4FE8-9ADA-F341D5031D9C}"/>
+    <hyperlink ref="C147" r:id="rId481" xr:uid="{57EA4E59-7D86-4715-AA19-80FD2129EA16}"/>
+    <hyperlink ref="C569" r:id="rId482" xr:uid="{174134F4-7EA9-406B-AC8D-971EFE1F24E3}"/>
+    <hyperlink ref="C568" r:id="rId483" xr:uid="{4CE185F9-CED9-438C-86C9-851D7566A9A7}"/>
+    <hyperlink ref="C567" r:id="rId484" xr:uid="{A20522D3-BFD6-4189-AD43-2A60AD94F7C6}"/>
+    <hyperlink ref="C566" r:id="rId485" xr:uid="{BF8FFE00-58C9-498F-9FB7-53370E4F76E6}"/>
+    <hyperlink ref="C565" r:id="rId486" xr:uid="{BA78BBFE-BA3A-4567-8842-D9DAC7BD4114}"/>
+    <hyperlink ref="C564" r:id="rId487" xr:uid="{AB8D8480-94A0-4F6D-94DD-954187AAF1CA}"/>
+    <hyperlink ref="C563" r:id="rId488" xr:uid="{F485B58C-0963-4817-B71B-E1D073DD028E}"/>
+    <hyperlink ref="C562" r:id="rId489" xr:uid="{CC59DEAF-1EFF-452A-ACA7-DC3FF58078F5}"/>
+    <hyperlink ref="C561" r:id="rId490" xr:uid="{D1F90F1B-7BD7-45D3-820D-8E747A8C92D3}"/>
+    <hyperlink ref="C560" r:id="rId491" xr:uid="{5DBD82ED-050A-43F8-8857-D34C7E4480CF}"/>
+    <hyperlink ref="C559" r:id="rId492" xr:uid="{F412E9FE-4C23-4374-A052-04C1F51DECF3}"/>
+    <hyperlink ref="C558" r:id="rId493" xr:uid="{449D0218-88EB-46E3-B0E4-2396D7F735E4}"/>
+    <hyperlink ref="C557" r:id="rId494" xr:uid="{7D6EF784-1F9A-4B36-90F6-AE8F627E5B8E}"/>
+    <hyperlink ref="C556" r:id="rId495" xr:uid="{D8B5388E-51D0-496B-A7D3-74F358D037B4}"/>
+    <hyperlink ref="C555" r:id="rId496" xr:uid="{F9F24C9F-2E3E-4D43-A177-0E5D2ACFC3DB}"/>
+    <hyperlink ref="C554" r:id="rId497" xr:uid="{EBEB933D-B423-41C9-9335-42397362BD62}"/>
+    <hyperlink ref="C553" r:id="rId498" xr:uid="{F4DC805F-FE7E-4A06-B475-D0E38D707111}"/>
+    <hyperlink ref="C552" r:id="rId499" xr:uid="{20418103-4EDF-42B7-9CBC-B36B42BA50FC}"/>
+    <hyperlink ref="C551" r:id="rId500" xr:uid="{6E09CD2C-B320-448D-A7EA-AB8C174E2970}"/>
+    <hyperlink ref="C550" r:id="rId501" xr:uid="{6E97C3B1-4CCB-44C9-ADA0-F640C6D728C6}"/>
+    <hyperlink ref="C549" r:id="rId502" xr:uid="{A3CBBBD1-2612-4CDD-81EF-7B827025D704}"/>
+    <hyperlink ref="C548" r:id="rId503" xr:uid="{889BBB9F-9281-42CD-8162-9C391B05D0E9}"/>
+    <hyperlink ref="C547" r:id="rId504" xr:uid="{3DB128D7-B924-44A9-A7C9-E6BC79E97B53}"/>
+    <hyperlink ref="C546" r:id="rId505" location="ug" xr:uid="{DC468B40-CC91-45B4-89A6-89B34BED7BF2}"/>
+    <hyperlink ref="C545" r:id="rId506" xr:uid="{33329805-9235-4129-B754-2D7734FBDDC7}"/>
+    <hyperlink ref="C544" r:id="rId507" xr:uid="{891F2F49-6F9D-42A2-B1C4-D4C4DE0F80CE}"/>
+    <hyperlink ref="C543" r:id="rId508" xr:uid="{298C3AFD-57FA-4BA3-8E29-707970F312E7}"/>
+    <hyperlink ref="C542" r:id="rId509" xr:uid="{6B0E6526-0C2D-4948-A6DC-921C8EB514C0}"/>
+    <hyperlink ref="C541" r:id="rId510" xr:uid="{58674F07-58BA-4940-9FD6-19FEB6F9995F}"/>
+    <hyperlink ref="C540" r:id="rId511" xr:uid="{CF302509-B5CB-407F-8B80-DBDE5822D97D}"/>
+    <hyperlink ref="C539" r:id="rId512" xr:uid="{53FFE010-86CC-42DA-BACE-36ECDF356E08}"/>
+    <hyperlink ref="C538" r:id="rId513" xr:uid="{B4314B32-2437-45EE-AA5A-5436BB31A223}"/>
+    <hyperlink ref="C537" r:id="rId514" xr:uid="{644D1C8A-4F41-4B57-8560-02BF758E73C4}"/>
+    <hyperlink ref="C536" r:id="rId515" xr:uid="{E86CD9EA-CFB3-41D9-B477-51F488869BDA}"/>
+    <hyperlink ref="C535" r:id="rId516" xr:uid="{0E4455B9-563E-43B3-9B53-A67F42506607}"/>
+    <hyperlink ref="C534" r:id="rId517" xr:uid="{562E68DB-94AF-45A2-936A-29A55800A148}"/>
+    <hyperlink ref="C533" r:id="rId518" xr:uid="{3A9CECF8-3087-4F4D-9265-80DC3E35D0CD}"/>
+    <hyperlink ref="C532" r:id="rId519" xr:uid="{6D8E7DFC-8EA5-4CD5-A126-6002F2E0A49F}"/>
+    <hyperlink ref="C531" r:id="rId520" xr:uid="{4185B687-50FC-4DC7-AB12-13062EE007F1}"/>
+    <hyperlink ref="C530" r:id="rId521" xr:uid="{9F49DD3E-B4A4-459C-AB78-866AAE5F3740}"/>
+    <hyperlink ref="C529" r:id="rId522" xr:uid="{39591972-9528-46B2-B533-F57A0735C396}"/>
+    <hyperlink ref="C528" r:id="rId523" xr:uid="{6A585B48-9DED-40FF-AAD1-CA36B8D95708}"/>
+    <hyperlink ref="C527" r:id="rId524" xr:uid="{77D0E52D-2981-4747-8803-EF1ED3E783DA}"/>
+    <hyperlink ref="C526" r:id="rId525" location="campus" xr:uid="{52922C32-37C3-4208-A1F7-E78E2A373254}"/>
+    <hyperlink ref="C525" r:id="rId526" location="masters" xr:uid="{D649413F-95A1-4375-9598-286113814371}"/>
+    <hyperlink ref="C524" r:id="rId527" xr:uid="{24A3EBAB-422A-4271-B422-720A28073A9F}"/>
+    <hyperlink ref="C523" r:id="rId528" xr:uid="{88691330-C7B9-467A-98B0-95319440599C}"/>
+    <hyperlink ref="C522" r:id="rId529" xr:uid="{74DC548D-C4A3-4733-AF06-0C7DD6C62157}"/>
+    <hyperlink ref="C521" r:id="rId530" xr:uid="{57365EF2-8AB1-412F-AC9D-E719A61B491A}"/>
+    <hyperlink ref="C520" r:id="rId531" xr:uid="{CA189A21-4B9A-4BB3-B64B-17F20F3049F0}"/>
+    <hyperlink ref="C519" r:id="rId532" xr:uid="{0AE22385-9740-42F1-BA48-F8E80C6C12CB}"/>
+    <hyperlink ref="C518" r:id="rId533" xr:uid="{8F7744FB-5D44-4B28-B752-EEAF67B446C9}"/>
+    <hyperlink ref="C517" r:id="rId534" xr:uid="{284E0EA3-4A3D-4CD0-AB09-51F3DF7D52BD}"/>
+    <hyperlink ref="C516" r:id="rId535" xr:uid="{EAD90F60-C919-4409-876F-FDA530F9D9EA}"/>
+    <hyperlink ref="C515" r:id="rId536" xr:uid="{A8EBE29B-AB58-466D-A3EF-065CFB1AB505}"/>
+    <hyperlink ref="C514" r:id="rId537" xr:uid="{104E7E5B-E107-4FDA-92B8-9CF512BD0F9E}"/>
+    <hyperlink ref="C513" r:id="rId538" xr:uid="{C7E8E7F0-EE55-4307-A285-F9163015384F}"/>
+    <hyperlink ref="C512" r:id="rId539" xr:uid="{7136EEAA-B7A4-423D-B8D2-4805FE4CB0E8}"/>
+    <hyperlink ref="C511" r:id="rId540" xr:uid="{2F6E9089-4464-4A32-B725-83014A8476CB}"/>
+    <hyperlink ref="C510" r:id="rId541" xr:uid="{D857A142-E2FD-451F-96F3-53CF337B9DFF}"/>
+    <hyperlink ref="C509" r:id="rId542" location="ugrad" xr:uid="{AF7624A7-2C13-4F57-A7F2-91499AD42237}"/>
+    <hyperlink ref="C508" r:id="rId543" xr:uid="{E461EA24-B5B5-4A3D-80C4-78BDF2F74205}"/>
+    <hyperlink ref="C507" r:id="rId544" xr:uid="{512D7250-7090-4D3F-9E44-63EA4B71AC1A}"/>
+    <hyperlink ref="C506" r:id="rId545" xr:uid="{0A667B60-C992-483D-82ED-9FE1A7602842}"/>
+    <hyperlink ref="C505" r:id="rId546" xr:uid="{4D1E4B4A-02C1-48DE-AFBE-EEA62554F8FE}"/>
+    <hyperlink ref="C504" r:id="rId547" xr:uid="{FFCA64BE-D68F-4C22-B508-EEDC178D5BBD}"/>
+    <hyperlink ref="C503" r:id="rId548" xr:uid="{527B727E-029F-4D33-9D75-B6891113FFA5}"/>
+    <hyperlink ref="C502" r:id="rId549" location="daytona-beach" xr:uid="{6619E01C-C97E-413A-AE3B-E4E2F21B9D48}"/>
+    <hyperlink ref="C501" r:id="rId550" location="daytona-beach" xr:uid="{FD8E6161-B879-4E13-9A78-61F21A3C7678}"/>
+    <hyperlink ref="C500" r:id="rId551" xr:uid="{F6DE756D-B8DA-4706-AF02-A1F6271A6ACF}"/>
+    <hyperlink ref="C499" r:id="rId552" xr:uid="{22C523A6-EA73-44A9-BFA9-29091694604C}"/>
+    <hyperlink ref="C498" r:id="rId553" xr:uid="{F9693B6F-6879-48C9-A0F7-4BCE9F7C0770}"/>
+    <hyperlink ref="C497" r:id="rId554" xr:uid="{0F1E4574-5A3D-4686-87F2-93F30FC4786A}"/>
+    <hyperlink ref="C496" r:id="rId555" xr:uid="{C947CCBC-4ABC-4909-88A1-891A36C3D143}"/>
+    <hyperlink ref="C148" r:id="rId556" xr:uid="{7F6B9F29-5C0B-44BD-A010-01F97569E946}"/>
+    <hyperlink ref="C149" r:id="rId557" xr:uid="{5BE80C95-BAF0-4A58-9807-04F4F10A3392}"/>
+    <hyperlink ref="C150" r:id="rId558" xr:uid="{25AC73C5-D8D1-4A68-A0ED-2C33B0812D96}"/>
+    <hyperlink ref="C151" r:id="rId559" xr:uid="{20020986-2A6B-4DF5-A8F2-DA0825DA1250}"/>
+    <hyperlink ref="C152" r:id="rId560" xr:uid="{17F73CFB-29AD-46AB-8232-950E37B0E449}"/>
+    <hyperlink ref="C153:C155" r:id="rId561" display="https://legacy.rru.ac.in/wp-content/uploads/2024/05/Fees-Structure-SITAICS-14May2024.pdf" xr:uid="{B02E8987-C0BF-4204-9DEE-15C5487B79D4}"/>
+    <hyperlink ref="C156" r:id="rId562" xr:uid="{425719C5-F52F-47A4-A471-5E9CE58AF26F}"/>
+    <hyperlink ref="C157" r:id="rId563" xr:uid="{B475B03A-FB81-4C71-B29C-70FA7AAFFF80}"/>
+    <hyperlink ref="C159" r:id="rId564" xr:uid="{2DB408F7-F842-4D81-91E1-B7EE65A5333B}"/>
+    <hyperlink ref="C158" r:id="rId565" xr:uid="{2E087C33-3DD1-4C79-9650-FEDFAF3A4CA3}"/>
+    <hyperlink ref="C702" r:id="rId566" xr:uid="{CB6F7D4F-5238-4A25-A57A-5E2CA49D5342}"/>
+    <hyperlink ref="C703" r:id="rId567" xr:uid="{C2947CAE-69C4-4BE5-8DF0-A99CE63CD05B}"/>
+    <hyperlink ref="C704" r:id="rId568" xr:uid="{B185A001-DE46-4EE0-95BB-A4E9B6B6346C}"/>
+    <hyperlink ref="C705" r:id="rId569" xr:uid="{3D7A51E3-B2A6-4C4A-AECD-AD1A1BDE0153}"/>
+    <hyperlink ref="C707" r:id="rId570" xr:uid="{81D9600D-2B5C-4080-927F-A21B1FF13BE9}"/>
+    <hyperlink ref="C706" r:id="rId571" xr:uid="{79FCD9E3-C4DF-4EC5-940E-885C48E301D8}"/>
+    <hyperlink ref="C708" r:id="rId572" xr:uid="{6C7FE20D-7316-4C13-8984-F397B99D740A}"/>
+    <hyperlink ref="C709" r:id="rId573" xr:uid="{C1038379-2771-4E84-9F19-D016F4ECC3E2}"/>
+    <hyperlink ref="C710:C711" r:id="rId574" display="https://drive.google.com/file/d/1fmepJ31Dfjm_qh5g_wunPXVkMUXKCSpc/view?usp=drive_link" xr:uid="{B72A07BB-EE24-4372-A901-142BDEB56755}"/>
+    <hyperlink ref="C712" r:id="rId575" xr:uid="{C95CACC9-22F3-4D48-8ABB-088984800843}"/>
+    <hyperlink ref="C714" r:id="rId576" xr:uid="{857B428D-FF38-4DDB-8BF7-216A91ED3B1E}"/>
+    <hyperlink ref="C713" r:id="rId577" xr:uid="{6F5B5F2A-9EAF-431A-B12D-848D191E74B5}"/>
+    <hyperlink ref="C715" r:id="rId578" xr:uid="{B5F7EFD7-D7A0-447F-8D0B-BEAA0E423624}"/>
+    <hyperlink ref="C716:C717" r:id="rId579" display="https://adypu.edu.in/wp-content/uploads/2024/07/20.ADYPU_Fees-Structure_24_25.pdf" xr:uid="{8E209706-7354-43E9-9E76-780A501BF850}"/>
+    <hyperlink ref="C718" r:id="rId580" xr:uid="{93B84C99-C0B6-427E-B792-003A6B811699}"/>
+    <hyperlink ref="C719" r:id="rId581" xr:uid="{D108B0AB-F2B0-4489-85FF-B2A32E48718F}"/>
+    <hyperlink ref="C720" r:id="rId582" xr:uid="{4A5AE46C-3678-4870-8072-2C019224F376}"/>
+    <hyperlink ref="C721" r:id="rId583" xr:uid="{87423149-8C1C-417F-8927-BA7D7AB22193}"/>
+    <hyperlink ref="C722" r:id="rId584" xr:uid="{45FBAD21-C7D2-4739-92B6-FD2076623CFA}"/>
+    <hyperlink ref="C723" r:id="rId585" xr:uid="{6186688D-F4AE-4360-8BB9-B9A4B17BEDF6}"/>
+    <hyperlink ref="C724" r:id="rId586" xr:uid="{3590360E-D482-446B-9F79-4FFE7C1C073A}"/>
+    <hyperlink ref="C725" r:id="rId587" xr:uid="{BC14503A-7E37-4FFA-9650-52DD0EADF29A}"/>
+    <hyperlink ref="C726" r:id="rId588" xr:uid="{DFDE858C-3C0E-40F6-9020-84277BF915FB}"/>
+    <hyperlink ref="C727" r:id="rId589" xr:uid="{E1D751F8-CB65-4034-804F-EA8E8F306747}"/>
+    <hyperlink ref="C728" r:id="rId590" xr:uid="{8665E79A-CE2F-45D2-BDDF-83DA3585472B}"/>
+    <hyperlink ref="C729" r:id="rId591" xr:uid="{B04D9CA0-2E77-46DA-8B87-8F1D8EF9C049}"/>
+    <hyperlink ref="C730" r:id="rId592" xr:uid="{FC3E61AF-9A93-4DBC-8CA2-A1C543CDB7D8}"/>
+    <hyperlink ref="C731" r:id="rId593" xr:uid="{68780992-6DAA-46A8-B8B4-B4BBA2917299}"/>
+    <hyperlink ref="C732" r:id="rId594" xr:uid="{C7172857-AB2C-429C-B752-E3089788612D}"/>
+    <hyperlink ref="C733" r:id="rId595" xr:uid="{3F50DD60-5393-43B0-8FFA-68A491669212}"/>
+    <hyperlink ref="C734" r:id="rId596" xr:uid="{C2627F34-5141-4887-A16B-CBF356C57E75}"/>
+    <hyperlink ref="C735" r:id="rId597" xr:uid="{EDED4804-2A29-4FCF-B16F-9093CA1F3402}"/>
+    <hyperlink ref="C736" r:id="rId598" xr:uid="{2906778E-2DEE-4AF6-B797-56BD3D3C92ED}"/>
+    <hyperlink ref="C737" r:id="rId599" xr:uid="{CF7BF210-6C7C-4748-B136-7D7D48E92F53}"/>
+    <hyperlink ref="C738" r:id="rId600" xr:uid="{9F8F3B0F-5923-4A92-AA17-551220766D9C}"/>
+    <hyperlink ref="C739" r:id="rId601" xr:uid="{D4072CFA-7E3A-4A31-924C-881FC018FA1A}"/>
+    <hyperlink ref="C741" r:id="rId602" xr:uid="{52487C8C-5AFB-4B5D-B5DF-9746B10422F0}"/>
+    <hyperlink ref="C740" r:id="rId603" xr:uid="{CF4335A8-2F33-49DD-A1EF-E4E9C570D98B}"/>
+    <hyperlink ref="C742" r:id="rId604" xr:uid="{9C63E6AF-038B-4C76-ADBA-E8DAFFC07E08}"/>
+    <hyperlink ref="C743" r:id="rId605" xr:uid="{E8B25F31-922E-4758-B02E-98B6F7060A88}"/>
+    <hyperlink ref="C744" r:id="rId606" xr:uid="{ABBAA515-0609-486C-BF64-FC3D99099187}"/>
+    <hyperlink ref="C745" r:id="rId607" xr:uid="{C00DB4FA-AF1D-4613-90A1-6FA57556076F}"/>
+    <hyperlink ref="C746" r:id="rId608" xr:uid="{CD016168-6D69-4F69-B68F-AA2EC32DFF6B}"/>
+    <hyperlink ref="C747" r:id="rId609" xr:uid="{CBE487E3-FACC-4B31-A120-61DC195C4D23}"/>
+    <hyperlink ref="C748" r:id="rId610" xr:uid="{EA090370-5F35-4063-959B-C8ADF669CEDE}"/>
+    <hyperlink ref="C749" r:id="rId611" xr:uid="{149D1ED3-CD53-4AE1-864A-A603DE5D12BC}"/>
+    <hyperlink ref="C750" r:id="rId612" xr:uid="{F017CC9E-0054-49FE-89AF-2D059AF6377F}"/>
+    <hyperlink ref="C751:C761" r:id="rId613" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{3B4E76B5-095C-45FE-B0CF-148644D9E11A}"/>
+    <hyperlink ref="C762" r:id="rId614" xr:uid="{B9D39B54-5728-4732-ACBF-88C9E7BB69BC}"/>
+    <hyperlink ref="C763" r:id="rId615" xr:uid="{5B64FB65-FE64-4A6B-AC64-EFC901A56244}"/>
+    <hyperlink ref="C764" r:id="rId616" xr:uid="{8C07BE98-0EA8-4A43-AF2B-442367D94176}"/>
+    <hyperlink ref="C765" r:id="rId617" xr:uid="{3355522E-84C3-495A-8C36-08E1DE7E740B}"/>
+    <hyperlink ref="C767" r:id="rId618" xr:uid="{B8C3CA87-1E12-457E-A5EA-C907F81668CD}"/>
+    <hyperlink ref="C768" r:id="rId619" xr:uid="{EC7491DD-D308-4AE6-824C-E20C1B0A063C}"/>
+    <hyperlink ref="C769" r:id="rId620" xr:uid="{CE4036C3-C29B-4E9A-BA2F-4103F4685B9D}"/>
+    <hyperlink ref="C161" r:id="rId621" xr:uid="{8DD02B6F-54A2-4FAC-B961-2C220AA1D943}"/>
+    <hyperlink ref="C162" r:id="rId622" xr:uid="{ED2940C7-EB7F-4547-BEC9-673E028B1F6E}"/>
+    <hyperlink ref="C770" r:id="rId623" xr:uid="{4015FD70-74FB-4621-A2FD-7986807085D5}"/>
+    <hyperlink ref="C771" r:id="rId624" xr:uid="{1F87E026-2DE2-4DBC-83B3-D6B951EA1E3C}"/>
+    <hyperlink ref="C772" r:id="rId625" xr:uid="{D6BE8929-2D3C-4A7B-BBAF-A4A4EE063EF8}"/>
+    <hyperlink ref="C773" r:id="rId626" xr:uid="{9DD1D3EA-72B8-45E8-BDA9-021B474CA435}"/>
+    <hyperlink ref="C774" r:id="rId627" xr:uid="{1BEB74B5-CAC1-4F1D-A056-DDD1E6CDBF96}"/>
+    <hyperlink ref="C775" r:id="rId628" xr:uid="{3073747A-DA6A-4CE0-A0B7-7AA867EE17D6}"/>
+    <hyperlink ref="C776" r:id="rId629" xr:uid="{B4E301A8-90DD-46D6-976D-FBA6A1684A1F}"/>
+    <hyperlink ref="C777" r:id="rId630" xr:uid="{CD3DDDEF-3C39-40EC-8B04-FA8675A7977F}"/>
+    <hyperlink ref="C778" r:id="rId631" xr:uid="{65D284DB-F879-47B9-A268-DFBC28C219E5}"/>
+    <hyperlink ref="C779" r:id="rId632" xr:uid="{3AF0420D-3F28-4CBB-BAE4-39DCD9DAEF50}"/>
+    <hyperlink ref="C51" r:id="rId633" xr:uid="{ECEE7BB5-A33D-4352-A89E-8D249C116DCB}"/>
+    <hyperlink ref="C455" r:id="rId634" xr:uid="{973FDA1F-DE1F-48CE-BE77-75DC093E98AA}"/>
+    <hyperlink ref="C366" r:id="rId635" xr:uid="{4696752E-5EF9-49D9-8362-5A976A1F5B12}"/>
+    <hyperlink ref="C365" r:id="rId636" xr:uid="{36DF91A2-AE4E-448A-A9E7-A1F91838B227}"/>
+    <hyperlink ref="C362" r:id="rId637" xr:uid="{09480EB5-1061-45DB-AA34-BC6317432F73}"/>
+    <hyperlink ref="C359" r:id="rId638" xr:uid="{4C8A3339-5E9D-44A2-851B-38820E24A7C1}"/>
+    <hyperlink ref="C457" r:id="rId639" xr:uid="{635DE0D8-AFDF-4529-93F2-B5CCE74EF50C}"/>
+    <hyperlink ref="C780" r:id="rId640" xr:uid="{BC6B2562-6B84-425C-9B87-36CDC918AC76}"/>
+    <hyperlink ref="C781" r:id="rId641" xr:uid="{D521C8BF-0148-4A06-80F7-96B5FD3E47F7}"/>
+    <hyperlink ref="C782" r:id="rId642" xr:uid="{89DA4F63-868B-410D-8AFE-DEAE3F4D14CF}"/>
+    <hyperlink ref="C783" r:id="rId643" xr:uid="{F240B56A-A908-4554-A031-75ABA7FACF20}"/>
+    <hyperlink ref="C784" r:id="rId644" xr:uid="{C6533D41-F550-4BED-9C7C-02E70C8DFA0D}"/>
+    <hyperlink ref="C766" r:id="rId645" xr:uid="{29B0C30A-FA81-4314-A11E-2CF9021B0C5D}"/>
+    <hyperlink ref="C785" r:id="rId646" xr:uid="{1DD05091-13EF-4185-8598-42B2C13DD25A}"/>
+    <hyperlink ref="C597" r:id="rId647" xr:uid="{AAD3B5F2-348C-4D6F-B2DC-32F09F0A9B13}"/>
+    <hyperlink ref="C596" r:id="rId648" xr:uid="{664C10D8-0E38-4804-B463-7F0186B1738E}"/>
+    <hyperlink ref="C598" r:id="rId649" xr:uid="{0A368D49-1F7C-4FA0-82FD-8A76D82CD659}"/>
+    <hyperlink ref="C786" r:id="rId650" xr:uid="{B1CFA210-9743-4205-9904-B22C9F9EBED7}"/>
+    <hyperlink ref="C787" r:id="rId651" xr:uid="{4D483717-7B75-4C1D-BAF2-3E13CC02FA4B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId650"/>
+    <tablePart r:id="rId652"/>
   </tableParts>
 </worksheet>
 </file>
--- a/fees.xlsx
+++ b/fees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Shlok Parekh\Downloads\Course-Verifier-3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB48CB16-288A-4436-9D56-CD9B184F0152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790FA759-3763-498D-AC73-D9A4AF877EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="1639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="1640">
   <si>
     <t>Acharya Nagarjuna University</t>
   </si>
@@ -4968,6 +4968,9 @@
   </si>
   <si>
     <t>Ohio State University</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10JGWIaOzbsrckLvYq4LKiqHy4_Ri8Rt-/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -14356,8 +14359,16 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C788" s="22"/>
+    <row r="788" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A788" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B788" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C788" s="12" t="s">
+        <v>1639</v>
+      </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C789" s="22"/>
@@ -19773,10 +19784,11 @@
     <hyperlink ref="C598" r:id="rId649" xr:uid="{0A368D49-1F7C-4FA0-82FD-8A76D82CD659}"/>
     <hyperlink ref="C786" r:id="rId650" xr:uid="{B1CFA210-9743-4205-9904-B22C9F9EBED7}"/>
     <hyperlink ref="C787" r:id="rId651" xr:uid="{4D483717-7B75-4C1D-BAF2-3E13CC02FA4B}"/>
+    <hyperlink ref="C788" r:id="rId652" xr:uid="{BA58CA45-509E-4E2D-86A7-BCE34C89B704}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId652"/>
+    <tablePart r:id="rId653"/>
   </tableParts>
 </worksheet>
 </file>
--- a/fees.xlsx
+++ b/fees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Shlok Parekh\Downloads\Course-Verifier-3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790FA759-3763-498D-AC73-D9A4AF877EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49911BA3-CD44-4F23-9DA5-BB9484C40F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
+    <workbookView xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/fees.xlsx
+++ b/fees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Shlok Parekh\Downloads\Course-Verifier-3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49911BA3-CD44-4F23-9DA5-BB9484C40F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0006431-3A55-4387-A8BE-10B4E19E1709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2219,9 +2219,6 @@
     <t>https://drive.google.com/file/d/1vog0rWXRzF2SF33kPUkXoESePa2Hb8wr/view?usp=sharing</t>
   </si>
   <si>
-    <t>https://cetonline.karnataka.gov.in/keawebentry456/ugcet2025/NEW_PROV_FEES_STR_Engenglish.pdf</t>
-  </si>
-  <si>
     <t>https://atme.edu.in/__l5e/assets-v1/03f673b7-5e9f-4f56-9e8c-a85c80057bb3/Fees-structure-2025-26.pdf</t>
   </si>
   <si>
@@ -4971,6 +4968,9 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/10JGWIaOzbsrckLvYq4LKiqHy4_Ri8Rt-/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rdC7GBkH0w9zhAf2amRYlhGy3XpyonNb/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -6183,7 +6183,7 @@
         <v>74</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6194,7 +6194,7 @@
         <v>75</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6205,7 +6205,7 @@
         <v>78</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6216,7 +6216,7 @@
         <v>79</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6238,7 +6238,7 @@
         <v>83</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6249,7 +6249,7 @@
         <v>84</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6260,7 +6260,7 @@
         <v>86</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6271,7 +6271,7 @@
         <v>88</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6282,7 +6282,7 @@
         <v>89</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6293,7 +6293,7 @@
         <v>91</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6304,7 +6304,7 @@
         <v>92</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6315,7 +6315,7 @@
         <v>93</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6326,7 +6326,7 @@
         <v>95</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6337,7 +6337,7 @@
         <v>96</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6348,7 +6348,7 @@
         <v>98</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6359,7 +6359,7 @@
         <v>99</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6370,7 +6370,7 @@
         <v>100</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6381,7 +6381,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6392,7 +6392,7 @@
         <v>104</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6403,7 +6403,7 @@
         <v>106</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6414,7 +6414,7 @@
         <v>109</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6425,7 +6425,7 @@
         <v>110</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6436,7 +6436,7 @@
         <v>112</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6447,7 +6447,7 @@
         <v>114</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6458,7 +6458,7 @@
         <v>116</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6469,7 +6469,7 @@
         <v>118</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6480,7 +6480,7 @@
         <v>119</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6491,7 +6491,7 @@
         <v>121</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6502,7 +6502,7 @@
         <v>123</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6513,7 +6513,7 @@
         <v>125</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6524,7 +6524,7 @@
         <v>127</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6535,7 +6535,7 @@
         <v>128</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6546,7 +6546,7 @@
         <v>129</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6557,7 +6557,7 @@
         <v>131</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6568,7 +6568,7 @@
         <v>133</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6579,7 +6579,7 @@
         <v>135</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6590,7 +6590,7 @@
         <v>137</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6601,7 +6601,7 @@
         <v>138</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6612,7 +6612,7 @@
         <v>140</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6623,7 +6623,7 @@
         <v>142</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6634,7 +6634,7 @@
         <v>143</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6645,7 +6645,7 @@
         <v>145</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6656,7 +6656,7 @@
         <v>146</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6667,7 +6667,7 @@
         <v>147</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6678,7 +6678,7 @@
         <v>148</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6689,7 +6689,7 @@
         <v>150</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6711,7 +6711,7 @@
         <v>153</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6722,7 +6722,7 @@
         <v>65</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6733,7 +6733,7 @@
         <v>155</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6744,7 +6744,7 @@
         <v>158</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6755,7 +6755,7 @@
         <v>160</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6766,7 +6766,7 @@
         <v>161</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6777,7 +6777,7 @@
         <v>162</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6788,7 +6788,7 @@
         <v>71</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6799,7 +6799,7 @@
         <v>165</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6810,7 +6810,7 @@
         <v>167</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
@@ -6821,7 +6821,7 @@
         <v>169</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6832,7 +6832,7 @@
         <v>170</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6843,7 +6843,7 @@
         <v>172</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6854,7 +6854,7 @@
         <v>173</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6865,7 +6865,7 @@
         <v>175</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6876,7 +6876,7 @@
         <v>176</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6887,7 +6887,7 @@
         <v>177</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6898,7 +6898,7 @@
         <v>179</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
@@ -6909,7 +6909,7 @@
         <v>181</v>
       </c>
       <c r="C110" s="17" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6931,7 +6931,7 @@
         <v>30</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6942,7 +6942,7 @@
         <v>184</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6953,7 +6953,7 @@
         <v>185</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6964,7 +6964,7 @@
         <v>187</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6975,7 +6975,7 @@
         <v>188</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6986,7 +6986,7 @@
         <v>190</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -6997,7 +6997,7 @@
         <v>192</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7008,7 +7008,7 @@
         <v>194</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7019,7 +7019,7 @@
         <v>196</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7030,7 +7030,7 @@
         <v>197</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7041,7 +7041,7 @@
         <v>71</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7052,7 +7052,7 @@
         <v>201</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7063,7 +7063,7 @@
         <v>203</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7107,7 +7107,7 @@
         <v>207</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
@@ -7118,7 +7118,7 @@
         <v>209</v>
       </c>
       <c r="C129" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
@@ -7129,7 +7129,7 @@
         <v>210</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
@@ -7140,7 +7140,7 @@
         <v>211</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7151,7 +7151,7 @@
         <v>213</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7162,7 +7162,7 @@
         <v>215</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7173,7 +7173,7 @@
         <v>217</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7184,7 +7184,7 @@
         <v>107</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7195,7 +7195,7 @@
         <v>220</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7206,7 +7206,7 @@
         <v>222</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7217,7 +7217,7 @@
         <v>224</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7228,7 +7228,7 @@
         <v>167</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7239,7 +7239,7 @@
         <v>107</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7250,7 +7250,7 @@
         <v>220</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7261,7 +7261,7 @@
         <v>229</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7272,7 +7272,7 @@
         <v>231</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7283,7 +7283,7 @@
         <v>233</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7294,7 +7294,7 @@
         <v>158</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7305,7 +7305,7 @@
         <v>235</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7316,7 +7316,7 @@
         <v>217</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7327,7 +7327,7 @@
         <v>237</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7338,7 +7338,7 @@
         <v>71</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7349,7 +7349,7 @@
         <v>239</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7360,7 +7360,7 @@
         <v>241</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7371,7 +7371,7 @@
         <v>243</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7382,7 +7382,7 @@
         <v>244</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7393,7 +7393,7 @@
         <v>245</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7404,7 +7404,7 @@
         <v>246</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7415,7 +7415,7 @@
         <v>248</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7426,7 +7426,7 @@
         <v>250</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7437,7 +7437,7 @@
         <v>252</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7448,7 +7448,7 @@
         <v>254</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7459,7 +7459,7 @@
         <v>256</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7470,7 +7470,7 @@
         <v>175</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7481,7 +7481,7 @@
         <v>81</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7492,7 +7492,7 @@
         <v>259</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7503,7 +7503,7 @@
         <v>179</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7514,7 +7514,7 @@
         <v>260</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
@@ -7525,7 +7525,7 @@
         <v>262</v>
       </c>
       <c r="C166" s="17" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7536,7 +7536,7 @@
         <v>264</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7547,7 +7547,7 @@
         <v>265</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7558,7 +7558,7 @@
         <v>266</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7569,7 +7569,7 @@
         <v>267</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7580,7 +7580,7 @@
         <v>269</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7591,7 +7591,7 @@
         <v>271</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7602,7 +7602,7 @@
         <v>273</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7613,7 +7613,7 @@
         <v>275</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7624,7 +7624,7 @@
         <v>71</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7635,7 +7635,7 @@
         <v>277</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7646,7 +7646,7 @@
         <v>151</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7657,7 +7657,7 @@
         <v>280</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7668,7 +7668,7 @@
         <v>61</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7690,7 +7690,7 @@
         <v>283</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7701,7 +7701,7 @@
         <v>285</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7712,7 +7712,7 @@
         <v>287</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7723,7 +7723,7 @@
         <v>289</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7745,7 +7745,7 @@
         <v>265</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7756,7 +7756,7 @@
         <v>297</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7767,7 +7767,7 @@
         <v>302</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7778,7 +7778,7 @@
         <v>305</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7789,7 +7789,7 @@
         <v>305</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7800,7 +7800,7 @@
         <v>308</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7811,7 +7811,7 @@
         <v>209</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7822,7 +7822,7 @@
         <v>209</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7833,7 +7833,7 @@
         <v>209</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7844,7 +7844,7 @@
         <v>209</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7855,7 +7855,7 @@
         <v>210</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7866,7 +7866,7 @@
         <v>265</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7877,7 +7877,7 @@
         <v>265</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7888,7 +7888,7 @@
         <v>265</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7899,7 +7899,7 @@
         <v>265</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7910,7 +7910,7 @@
         <v>265</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7921,7 +7921,7 @@
         <v>265</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7932,7 +7932,7 @@
         <v>302</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7943,7 +7943,7 @@
         <v>318</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7954,7 +7954,7 @@
         <v>7</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7965,7 +7965,7 @@
         <v>319</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7976,7 +7976,7 @@
         <v>320</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7987,7 +7987,7 @@
         <v>321</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -7998,7 +7998,7 @@
         <v>322</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8009,7 +8009,7 @@
         <v>323</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8020,7 +8020,7 @@
         <v>326</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8031,7 +8031,7 @@
         <v>217</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8042,7 +8042,7 @@
         <v>327</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8053,7 +8053,7 @@
         <v>329</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8064,7 +8064,7 @@
         <v>167</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8075,7 +8075,7 @@
         <v>331</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8086,7 +8086,7 @@
         <v>332</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8097,7 +8097,7 @@
         <v>334</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8108,7 +8108,7 @@
         <v>336</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8119,7 +8119,7 @@
         <v>338</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8130,7 +8130,7 @@
         <v>339</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8141,7 +8141,7 @@
         <v>309</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8152,7 +8152,7 @@
         <v>341</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8163,7 +8163,7 @@
         <v>343</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8174,7 +8174,7 @@
         <v>345</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8185,7 +8185,7 @@
         <v>293</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8196,7 +8196,7 @@
         <v>346</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8207,7 +8207,7 @@
         <v>348</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8218,7 +8218,7 @@
         <v>349</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8229,7 +8229,7 @@
         <v>351</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8240,7 +8240,7 @@
         <v>353</v>
       </c>
       <c r="C231" s="12" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8251,7 +8251,7 @@
         <v>355</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8262,7 +8262,7 @@
         <v>356</v>
       </c>
       <c r="C233" s="12" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8273,7 +8273,7 @@
         <v>357</v>
       </c>
       <c r="C234" s="12" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8284,7 +8284,7 @@
         <v>359</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8295,7 +8295,7 @@
         <v>361</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8306,7 +8306,7 @@
         <v>362</v>
       </c>
       <c r="C237" s="12" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8317,7 +8317,7 @@
         <v>363</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8328,7 +8328,7 @@
         <v>364</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8339,7 +8339,7 @@
         <v>366</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8350,7 +8350,7 @@
         <v>367</v>
       </c>
       <c r="C241" s="12" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8361,7 +8361,7 @@
         <v>369</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8372,7 +8372,7 @@
         <v>65</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8383,7 +8383,7 @@
         <v>370</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8394,7 +8394,7 @@
         <v>298</v>
       </c>
       <c r="C245" s="12" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8405,7 +8405,7 @@
         <v>372</v>
       </c>
       <c r="C246" s="12" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8416,7 +8416,7 @@
         <v>374</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8427,7 +8427,7 @@
         <v>375</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8438,7 +8438,7 @@
         <v>376</v>
       </c>
       <c r="C249" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8449,7 +8449,7 @@
         <v>374</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8460,7 +8460,7 @@
         <v>377</v>
       </c>
       <c r="C251" s="12" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8471,7 +8471,7 @@
         <v>379</v>
       </c>
       <c r="C252" s="12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8482,7 +8482,7 @@
         <v>203</v>
       </c>
       <c r="C253" s="12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8493,7 +8493,7 @@
         <v>381</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8504,7 +8504,7 @@
         <v>382</v>
       </c>
       <c r="C255" s="12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8515,7 +8515,7 @@
         <v>384</v>
       </c>
       <c r="C256" s="12" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8526,7 +8526,7 @@
         <v>386</v>
       </c>
       <c r="C257" s="12" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8537,7 +8537,7 @@
         <v>388</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8548,7 +8548,7 @@
         <v>390</v>
       </c>
       <c r="C259" s="12" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8559,7 +8559,7 @@
         <v>392</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8570,7 +8570,7 @@
         <v>394</v>
       </c>
       <c r="C261" s="12" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8581,7 +8581,7 @@
         <v>395</v>
       </c>
       <c r="C262" s="12" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8592,7 +8592,7 @@
         <v>396</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8603,7 +8603,7 @@
         <v>233</v>
       </c>
       <c r="C264" s="12" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8614,7 +8614,7 @@
         <v>233</v>
       </c>
       <c r="C265" s="12" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8625,7 +8625,7 @@
         <v>233</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8636,7 +8636,7 @@
         <v>233</v>
       </c>
       <c r="C267" s="12" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8647,7 +8647,7 @@
         <v>395</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8658,7 +8658,7 @@
         <v>395</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8669,7 +8669,7 @@
         <v>233</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8680,7 +8680,7 @@
         <v>396</v>
       </c>
       <c r="C271" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8691,7 +8691,7 @@
         <v>398</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8702,7 +8702,7 @@
         <v>399</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8713,7 +8713,7 @@
         <v>400</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8724,7 +8724,7 @@
         <v>401</v>
       </c>
       <c r="C275" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8735,7 +8735,7 @@
         <v>402</v>
       </c>
       <c r="C276" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8746,7 +8746,7 @@
         <v>403</v>
       </c>
       <c r="C277" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8757,7 +8757,7 @@
         <v>404</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8768,7 +8768,7 @@
         <v>406</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8779,7 +8779,7 @@
         <v>407</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8790,7 +8790,7 @@
         <v>152</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8801,7 +8801,7 @@
         <v>409</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8823,7 +8823,7 @@
         <v>410</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8834,7 +8834,7 @@
         <v>411</v>
       </c>
       <c r="C285" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8845,7 +8845,7 @@
         <v>205</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8856,7 +8856,7 @@
         <v>395</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8867,7 +8867,7 @@
         <v>395</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8878,7 +8878,7 @@
         <v>395</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8889,7 +8889,7 @@
         <v>412</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8900,7 +8900,7 @@
         <v>395</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8911,7 +8911,7 @@
         <v>205</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8922,7 +8922,7 @@
         <v>395</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8933,7 +8933,7 @@
         <v>413</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8944,7 +8944,7 @@
         <v>414</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8955,7 +8955,7 @@
         <v>412</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8966,7 +8966,7 @@
         <v>205</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8977,7 +8977,7 @@
         <v>205</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8988,7 +8988,7 @@
         <v>412</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -8999,7 +8999,7 @@
         <v>395</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9010,7 +9010,7 @@
         <v>418</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9021,7 +9021,7 @@
         <v>419</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9032,7 +9032,7 @@
         <v>418</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9043,7 +9043,7 @@
         <v>420</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9054,7 +9054,7 @@
         <v>419</v>
       </c>
       <c r="C305" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9065,7 +9065,7 @@
         <v>420</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9076,7 +9076,7 @@
         <v>421</v>
       </c>
       <c r="C307" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9087,7 +9087,7 @@
         <v>420</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9098,7 +9098,7 @@
         <v>421</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9109,7 +9109,7 @@
         <v>420</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9120,7 +9120,7 @@
         <v>421</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9131,7 +9131,7 @@
         <v>420</v>
       </c>
       <c r="C312" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9142,7 +9142,7 @@
         <v>420</v>
       </c>
       <c r="C313" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9153,7 +9153,7 @@
         <v>421</v>
       </c>
       <c r="C314" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9164,7 +9164,7 @@
         <v>421</v>
       </c>
       <c r="C315" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9175,7 +9175,7 @@
         <v>421</v>
       </c>
       <c r="C316" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9186,7 +9186,7 @@
         <v>420</v>
       </c>
       <c r="C317" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9197,7 +9197,7 @@
         <v>421</v>
       </c>
       <c r="C318" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9208,7 +9208,7 @@
         <v>420</v>
       </c>
       <c r="C319" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9219,7 +9219,7 @@
         <v>421</v>
       </c>
       <c r="C320" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9230,7 +9230,7 @@
         <v>421</v>
       </c>
       <c r="C321" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9241,7 +9241,7 @@
         <v>421</v>
       </c>
       <c r="C322" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9252,7 +9252,7 @@
         <v>420</v>
       </c>
       <c r="C323" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9263,7 +9263,7 @@
         <v>421</v>
       </c>
       <c r="C324" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9274,7 +9274,7 @@
         <v>420</v>
       </c>
       <c r="C325" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9285,7 +9285,7 @@
         <v>421</v>
       </c>
       <c r="C326" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9296,7 +9296,7 @@
         <v>420</v>
       </c>
       <c r="C327" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9307,7 +9307,7 @@
         <v>421</v>
       </c>
       <c r="C328" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9318,7 +9318,7 @@
         <v>421</v>
       </c>
       <c r="C329" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9329,7 +9329,7 @@
         <v>421</v>
       </c>
       <c r="C330" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9340,7 +9340,7 @@
         <v>421</v>
       </c>
       <c r="C331" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9351,7 +9351,7 @@
         <v>425</v>
       </c>
       <c r="C332" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9362,7 +9362,7 @@
         <v>426</v>
       </c>
       <c r="C333" s="12" t="s">
-        <v>724</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9373,7 +9373,7 @@
         <v>30</v>
       </c>
       <c r="C334" s="12" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9384,7 +9384,7 @@
         <v>30</v>
       </c>
       <c r="C335" s="12" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9395,7 +9395,7 @@
         <v>30</v>
       </c>
       <c r="C336" s="12" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9406,7 +9406,7 @@
         <v>30</v>
       </c>
       <c r="C337" s="12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9417,7 +9417,7 @@
         <v>427</v>
       </c>
       <c r="C338" s="12" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9428,7 +9428,7 @@
         <v>429</v>
       </c>
       <c r="C339" s="12" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9439,7 +9439,7 @@
         <v>30</v>
       </c>
       <c r="C340" s="12" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9450,7 +9450,7 @@
         <v>30</v>
       </c>
       <c r="C341" s="12" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9461,7 +9461,7 @@
         <v>30</v>
       </c>
       <c r="C342" s="12" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9527,7 +9527,7 @@
         <v>30</v>
       </c>
       <c r="C348" s="12" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9538,7 +9538,7 @@
         <v>30</v>
       </c>
       <c r="C349" s="12" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9549,7 +9549,7 @@
         <v>30</v>
       </c>
       <c r="C350" s="12" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9560,7 +9560,7 @@
         <v>30</v>
       </c>
       <c r="C351" s="12" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9571,7 +9571,7 @@
         <v>30</v>
       </c>
       <c r="C352" s="12" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9582,7 +9582,7 @@
         <v>30</v>
       </c>
       <c r="C353" s="12" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9593,7 +9593,7 @@
         <v>30</v>
       </c>
       <c r="C354" s="12" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9604,7 +9604,7 @@
         <v>420</v>
       </c>
       <c r="C355" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9615,7 +9615,7 @@
         <v>420</v>
       </c>
       <c r="C356" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9626,7 +9626,7 @@
         <v>420</v>
       </c>
       <c r="C357" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9637,7 +9637,7 @@
         <v>420</v>
       </c>
       <c r="C358" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9648,7 +9648,7 @@
         <v>420</v>
       </c>
       <c r="C359" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9659,7 +9659,7 @@
         <v>420</v>
       </c>
       <c r="C360" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9670,7 +9670,7 @@
         <v>420</v>
       </c>
       <c r="C361" s="12" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9681,7 +9681,7 @@
         <v>420</v>
       </c>
       <c r="C362" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9692,7 +9692,7 @@
         <v>420</v>
       </c>
       <c r="C363" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9703,7 +9703,7 @@
         <v>420</v>
       </c>
       <c r="C364" s="12" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9714,7 +9714,7 @@
         <v>420</v>
       </c>
       <c r="C365" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9725,7 +9725,7 @@
         <v>420</v>
       </c>
       <c r="C366" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9736,7 +9736,7 @@
         <v>30</v>
       </c>
       <c r="C367" s="12" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9747,7 +9747,7 @@
         <v>459</v>
       </c>
       <c r="C368" s="12" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9758,7 +9758,7 @@
         <v>420</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9769,7 +9769,7 @@
         <v>420</v>
       </c>
       <c r="C370" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9780,7 +9780,7 @@
         <v>420</v>
       </c>
       <c r="C371" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9791,7 +9791,7 @@
         <v>420</v>
       </c>
       <c r="C372" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9802,7 +9802,7 @@
         <v>420</v>
       </c>
       <c r="C373" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9813,7 +9813,7 @@
         <v>420</v>
       </c>
       <c r="C374" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9824,7 +9824,7 @@
         <v>420</v>
       </c>
       <c r="C375" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9835,7 +9835,7 @@
         <v>420</v>
       </c>
       <c r="C376" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9846,7 +9846,7 @@
         <v>420</v>
       </c>
       <c r="C377" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9857,7 +9857,7 @@
         <v>420</v>
       </c>
       <c r="C378" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9868,7 +9868,7 @@
         <v>420</v>
       </c>
       <c r="C379" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9879,7 +9879,7 @@
         <v>420</v>
       </c>
       <c r="C380" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9890,7 +9890,7 @@
         <v>420</v>
       </c>
       <c r="C381" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9901,7 +9901,7 @@
         <v>420</v>
       </c>
       <c r="C382" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9912,7 +9912,7 @@
         <v>420</v>
       </c>
       <c r="C383" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9923,7 +9923,7 @@
         <v>475</v>
       </c>
       <c r="C384" s="12" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9934,7 +9934,7 @@
         <v>476</v>
       </c>
       <c r="C385" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9945,7 +9945,7 @@
         <v>479</v>
       </c>
       <c r="C386" s="12" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9956,7 +9956,7 @@
         <v>481</v>
       </c>
       <c r="C387" s="12" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9967,7 +9967,7 @@
         <v>420</v>
       </c>
       <c r="C388" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9978,7 +9978,7 @@
         <v>420</v>
       </c>
       <c r="C389" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -9989,7 +9989,7 @@
         <v>420</v>
       </c>
       <c r="C390" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10000,7 +10000,7 @@
         <v>420</v>
       </c>
       <c r="C391" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10011,7 +10011,7 @@
         <v>420</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10022,7 +10022,7 @@
         <v>420</v>
       </c>
       <c r="C393" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10033,7 +10033,7 @@
         <v>420</v>
       </c>
       <c r="C394" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10044,7 +10044,7 @@
         <v>420</v>
       </c>
       <c r="C395" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10055,7 +10055,7 @@
         <v>420</v>
       </c>
       <c r="C396" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10066,7 +10066,7 @@
         <v>420</v>
       </c>
       <c r="C397" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10077,7 +10077,7 @@
         <v>420</v>
       </c>
       <c r="C398" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10088,7 +10088,7 @@
         <v>420</v>
       </c>
       <c r="C399" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10099,7 +10099,7 @@
         <v>420</v>
       </c>
       <c r="C400" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10110,7 +10110,7 @@
         <v>420</v>
       </c>
       <c r="C401" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10121,7 +10121,7 @@
         <v>420</v>
       </c>
       <c r="C402" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10132,7 +10132,7 @@
         <v>420</v>
       </c>
       <c r="C403" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10143,7 +10143,7 @@
         <v>420</v>
       </c>
       <c r="C404" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10154,7 +10154,7 @@
         <v>500</v>
       </c>
       <c r="C405" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10165,7 +10165,7 @@
         <v>502</v>
       </c>
       <c r="C406" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10176,7 +10176,7 @@
         <v>412</v>
       </c>
       <c r="C407" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10187,7 +10187,7 @@
         <v>412</v>
       </c>
       <c r="C408" s="12" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10198,7 +10198,7 @@
         <v>412</v>
       </c>
       <c r="C409" s="12" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10209,7 +10209,7 @@
         <v>507</v>
       </c>
       <c r="C410" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10220,7 +10220,7 @@
         <v>507</v>
       </c>
       <c r="C411" s="12" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10231,7 +10231,7 @@
         <v>510</v>
       </c>
       <c r="C412" s="12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10242,7 +10242,7 @@
         <v>298</v>
       </c>
       <c r="C413" s="12" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10253,7 +10253,7 @@
         <v>298</v>
       </c>
       <c r="C414" s="12" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10264,7 +10264,7 @@
         <v>323</v>
       </c>
       <c r="C415" s="12" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10275,7 +10275,7 @@
         <v>515</v>
       </c>
       <c r="C416" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10286,7 +10286,7 @@
         <v>303</v>
       </c>
       <c r="C417" s="12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10297,7 +10297,7 @@
         <v>254</v>
       </c>
       <c r="C418" s="12" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10308,7 +10308,7 @@
         <v>254</v>
       </c>
       <c r="C419" s="12" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10319,7 +10319,7 @@
         <v>519</v>
       </c>
       <c r="C420" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10330,7 +10330,7 @@
         <v>521</v>
       </c>
       <c r="C421" s="12" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10341,7 +10341,7 @@
         <v>290</v>
       </c>
       <c r="C422" s="12" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10352,7 +10352,7 @@
         <v>295</v>
       </c>
       <c r="C423" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10363,7 +10363,7 @@
         <v>525</v>
       </c>
       <c r="C424" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10374,7 +10374,7 @@
         <v>525</v>
       </c>
       <c r="C425" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10385,7 +10385,7 @@
         <v>420</v>
       </c>
       <c r="C426" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10396,7 +10396,7 @@
         <v>528</v>
       </c>
       <c r="C427" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10407,7 +10407,7 @@
         <v>530</v>
       </c>
       <c r="C428" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10418,7 +10418,7 @@
         <v>7</v>
       </c>
       <c r="C429" s="12" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10429,7 +10429,7 @@
         <v>532</v>
       </c>
       <c r="C430" s="12" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10440,7 +10440,7 @@
         <v>324</v>
       </c>
       <c r="C431" s="12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10451,7 +10451,7 @@
         <v>535</v>
       </c>
       <c r="C432" s="12" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10462,7 +10462,7 @@
         <v>536</v>
       </c>
       <c r="C433" s="12" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10473,7 +10473,7 @@
         <v>538</v>
       </c>
       <c r="C434" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10484,7 +10484,7 @@
         <v>540</v>
       </c>
       <c r="C435" s="12" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10495,7 +10495,7 @@
         <v>542</v>
       </c>
       <c r="C436" s="12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10506,7 +10506,7 @@
         <v>540</v>
       </c>
       <c r="C437" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10517,7 +10517,7 @@
         <v>540</v>
       </c>
       <c r="C438" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10528,7 +10528,7 @@
         <v>540</v>
       </c>
       <c r="C439" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10539,7 +10539,7 @@
         <v>532</v>
       </c>
       <c r="C440" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10550,7 +10550,7 @@
         <v>547</v>
       </c>
       <c r="C441" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10561,7 +10561,7 @@
         <v>549</v>
       </c>
       <c r="C442" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10572,7 +10572,7 @@
         <v>550</v>
       </c>
       <c r="C443" s="12" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10583,7 +10583,7 @@
         <v>481</v>
       </c>
       <c r="C444" s="12" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10594,7 +10594,7 @@
         <v>554</v>
       </c>
       <c r="C445" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10605,7 +10605,7 @@
         <v>554</v>
       </c>
       <c r="C446" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10616,7 +10616,7 @@
         <v>554</v>
       </c>
       <c r="C447" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10627,7 +10627,7 @@
         <v>554</v>
       </c>
       <c r="C448" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10638,7 +10638,7 @@
         <v>554</v>
       </c>
       <c r="C449" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10649,7 +10649,7 @@
         <v>554</v>
       </c>
       <c r="C450" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10660,7 +10660,7 @@
         <v>554</v>
       </c>
       <c r="C451" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10671,7 +10671,7 @@
         <v>554</v>
       </c>
       <c r="C452" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10682,7 +10682,7 @@
         <v>554</v>
       </c>
       <c r="C453" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10693,7 +10693,7 @@
         <v>554</v>
       </c>
       <c r="C454" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10704,7 +10704,7 @@
         <v>554</v>
       </c>
       <c r="C455" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10715,7 +10715,7 @@
         <v>554</v>
       </c>
       <c r="C456" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10726,7 +10726,7 @@
         <v>554</v>
       </c>
       <c r="C457" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10737,7 +10737,7 @@
         <v>554</v>
       </c>
       <c r="C458" s="12" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10748,7 +10748,7 @@
         <v>554</v>
       </c>
       <c r="C459" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10759,7 +10759,7 @@
         <v>554</v>
       </c>
       <c r="C460" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10770,7 +10770,7 @@
         <v>554</v>
       </c>
       <c r="C461" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10781,7 +10781,7 @@
         <v>554</v>
       </c>
       <c r="C462" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10792,7 +10792,7 @@
         <v>554</v>
       </c>
       <c r="C463" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10803,7 +10803,7 @@
         <v>554</v>
       </c>
       <c r="C464" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10814,7 +10814,7 @@
         <v>554</v>
       </c>
       <c r="C465" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10825,7 +10825,7 @@
         <v>554</v>
       </c>
       <c r="C466" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10836,7 +10836,7 @@
         <v>554</v>
       </c>
       <c r="C467" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10847,7 +10847,7 @@
         <v>554</v>
       </c>
       <c r="C468" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10858,7 +10858,7 @@
         <v>554</v>
       </c>
       <c r="C469" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10869,7 +10869,7 @@
         <v>554</v>
       </c>
       <c r="C470" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10880,7 +10880,7 @@
         <v>554</v>
       </c>
       <c r="C471" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10891,7 +10891,7 @@
         <v>554</v>
       </c>
       <c r="C472" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10902,7 +10902,7 @@
         <v>554</v>
       </c>
       <c r="C473" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10913,7 +10913,7 @@
         <v>554</v>
       </c>
       <c r="C474" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10924,7 +10924,7 @@
         <v>554</v>
       </c>
       <c r="C475" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10935,7 +10935,7 @@
         <v>554</v>
       </c>
       <c r="C476" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10946,7 +10946,7 @@
         <v>554</v>
       </c>
       <c r="C477" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10957,7 +10957,7 @@
         <v>554</v>
       </c>
       <c r="C478" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10968,7 +10968,7 @@
         <v>554</v>
       </c>
       <c r="C479" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10979,7 +10979,7 @@
         <v>554</v>
       </c>
       <c r="C480" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -10990,7 +10990,7 @@
         <v>554</v>
       </c>
       <c r="C481" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11001,7 +11001,7 @@
         <v>554</v>
       </c>
       <c r="C482" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11012,7 +11012,7 @@
         <v>554</v>
       </c>
       <c r="C483" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="20" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -11023,18 +11023,18 @@
         <v>554</v>
       </c>
       <c r="C484" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A485" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B485" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="B485" s="6" t="s">
+      <c r="C485" s="21" t="s">
         <v>949</v>
-      </c>
-      <c r="C485" s="21" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -11045,2416 +11045,2416 @@
         <v>554</v>
       </c>
       <c r="C486" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A487" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="B487" s="6" t="s">
         <v>952</v>
       </c>
-      <c r="B487" s="6" t="s">
-        <v>953</v>
-      </c>
       <c r="C487" s="12" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A488" s="6" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B488" s="6" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C488" s="12" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A489" s="6" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B489" s="6" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C489" s="12" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A490" s="6" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B490" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="C490" s="12" t="s">
         <v>956</v>
-      </c>
-      <c r="C490" s="12" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A491" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="B491" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="B491" s="6" t="s">
-        <v>960</v>
-      </c>
       <c r="C491" s="12" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A492" s="6" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B492" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="C492" s="12" t="s">
         <v>961</v>
-      </c>
-      <c r="C492" s="12" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A493" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="B493" s="7" t="s">
         <v>963</v>
       </c>
-      <c r="B493" s="7" t="s">
+      <c r="C493" s="12" t="s">
         <v>964</v>
-      </c>
-      <c r="C493" s="12" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A494" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="B494" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="B494" s="6" t="s">
-        <v>971</v>
-      </c>
       <c r="C494" s="12" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A495" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="B495" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="B495" s="6" t="s">
-        <v>969</v>
-      </c>
       <c r="C495" s="12" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A496" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="B496" s="6" t="s">
         <v>972</v>
       </c>
-      <c r="B496" s="6" t="s">
-        <v>973</v>
-      </c>
       <c r="C496" s="12" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A497" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="B497" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="B497" s="6" t="s">
-        <v>975</v>
-      </c>
       <c r="C497" s="12" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A498" s="6" t="s">
+        <v>975</v>
+      </c>
+      <c r="B498" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="B498" s="6" t="s">
-        <v>977</v>
-      </c>
       <c r="C498" s="12" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A499" s="7" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B499" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C499" s="12" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A500" s="6" t="s">
+        <v>980</v>
+      </c>
+      <c r="B500" s="6" t="s">
         <v>981</v>
       </c>
-      <c r="B500" s="6" t="s">
-        <v>982</v>
-      </c>
       <c r="C500" s="12" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A501" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="B501" s="6" t="s">
         <v>983</v>
       </c>
-      <c r="B501" s="6" t="s">
-        <v>984</v>
-      </c>
       <c r="C501" s="12" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A502" s="6" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B502" s="6" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C502" s="12" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A503" s="7" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B503" s="7" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C503" s="12" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A504" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="B504" s="6" t="s">
         <v>987</v>
       </c>
-      <c r="B504" s="6" t="s">
-        <v>988</v>
-      </c>
       <c r="C504" s="12" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A505" s="6" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B505" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C505" s="12" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A506" s="7" t="s">
+        <v>989</v>
+      </c>
+      <c r="B506" s="7" t="s">
         <v>990</v>
       </c>
-      <c r="B506" s="7" t="s">
-        <v>991</v>
-      </c>
       <c r="C506" s="12" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A507" s="7" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B507" s="7" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C507" s="12" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A508" s="6" t="s">
+        <v>992</v>
+      </c>
+      <c r="B508" s="6" t="s">
         <v>993</v>
       </c>
-      <c r="B508" s="6" t="s">
-        <v>994</v>
-      </c>
       <c r="C508" s="12" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A509" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="B509" s="6" t="s">
         <v>995</v>
       </c>
-      <c r="B509" s="6" t="s">
-        <v>996</v>
-      </c>
       <c r="C509" s="12" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A510" s="6" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B510" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C510" s="12" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A511" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="B511" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="B511" s="6" t="s">
-        <v>998</v>
-      </c>
       <c r="C511" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A512" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="B512" s="6" t="s">
         <v>999</v>
       </c>
-      <c r="B512" s="6" t="s">
-        <v>1000</v>
-      </c>
       <c r="C512" s="12" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A513" s="6" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B513" s="6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C513" s="12" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A514" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B514" s="6" t="s">
         <v>1002</v>
       </c>
-      <c r="B514" s="6" t="s">
-        <v>1003</v>
-      </c>
       <c r="C514" s="12" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A515" s="6" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B515" s="6" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C515" s="12" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A516" s="6" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B516" s="6" t="s">
         <v>1005</v>
       </c>
-      <c r="B516" s="6" t="s">
-        <v>1006</v>
-      </c>
       <c r="C516" s="12" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A517" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B517" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="B517" s="6" t="s">
-        <v>1008</v>
-      </c>
       <c r="C517" s="12" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A518" s="7" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B518" s="7" t="s">
         <v>1009</v>
       </c>
-      <c r="B518" s="7" t="s">
-        <v>1010</v>
-      </c>
       <c r="C518" s="12" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A519" s="6" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B519" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="B519" s="6" t="s">
-        <v>1012</v>
-      </c>
       <c r="C519" s="12" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A520" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B520" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="B520" s="6" t="s">
-        <v>1014</v>
-      </c>
       <c r="C520" s="12" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A521" s="7" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B521" s="7" t="s">
         <v>1015</v>
       </c>
-      <c r="B521" s="7" t="s">
-        <v>1016</v>
-      </c>
       <c r="C521" s="12" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A522" s="7" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B522" s="6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C522" s="12" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A523" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B523" s="6" t="s">
         <v>1017</v>
       </c>
-      <c r="B523" s="6" t="s">
-        <v>1018</v>
-      </c>
       <c r="C523" s="12" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A524" s="6" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B524" s="6" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C524" s="12" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A525" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B525" s="6" t="s">
         <v>1020</v>
       </c>
-      <c r="B525" s="6" t="s">
-        <v>1021</v>
-      </c>
       <c r="C525" s="12" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A526" s="6" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B526" s="6" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C526" s="12" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A527" s="6" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B527" s="8" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C527" s="12" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A528" s="6" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B528" s="6" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C528" s="12" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A529" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B529" s="7" t="s">
         <v>1024</v>
       </c>
-      <c r="B529" s="7" t="s">
-        <v>1025</v>
-      </c>
       <c r="C529" s="12" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A530" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B530" s="6" t="s">
         <v>1026</v>
       </c>
-      <c r="B530" s="6" t="s">
-        <v>1027</v>
-      </c>
       <c r="C530" s="12" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A531" s="6" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B531" s="6" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C531" s="12" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A532" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B532" s="7" t="s">
         <v>1028</v>
       </c>
-      <c r="B532" s="7" t="s">
-        <v>1029</v>
-      </c>
       <c r="C532" s="12" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A533" s="7" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B533" s="6" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C533" s="12" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A534" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B534" s="6" t="s">
         <v>1031</v>
       </c>
-      <c r="B534" s="6" t="s">
-        <v>1032</v>
-      </c>
       <c r="C534" s="12" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A535" s="6" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B535" s="6" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C535" s="12" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A536" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B536" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="B536" s="7" t="s">
-        <v>1035</v>
-      </c>
       <c r="C536" s="12" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A537" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B537" s="6" t="s">
         <v>1036</v>
       </c>
-      <c r="B537" s="6" t="s">
-        <v>1037</v>
-      </c>
       <c r="C537" s="12" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A538" s="6" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B538" s="6" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C538" s="12" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A539" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B539" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="B539" s="6" t="s">
-        <v>1040</v>
-      </c>
       <c r="C539" s="12" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A540" s="6" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B540" s="6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C540" s="12" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A541" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B541" s="6" t="s">
         <v>1042</v>
       </c>
-      <c r="B541" s="6" t="s">
-        <v>1043</v>
-      </c>
       <c r="C541" s="12" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A542" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B542" s="6" t="s">
         <v>1044</v>
       </c>
-      <c r="B542" s="6" t="s">
-        <v>1045</v>
-      </c>
       <c r="C542" s="12" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A543" s="6" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B543" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C543" s="12" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A544" s="8" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B544" s="8" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C544" s="12" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A545" s="6" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B545" s="6" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C545" s="12" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A546" s="6" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B546" s="6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C546" s="12" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A547" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B547" s="6" t="s">
         <v>1048</v>
       </c>
-      <c r="B547" s="6" t="s">
-        <v>1049</v>
-      </c>
       <c r="C547" s="12" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A548" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B548" s="9" t="s">
         <v>1050</v>
       </c>
-      <c r="B548" s="9" t="s">
-        <v>1051</v>
-      </c>
       <c r="C548" s="12" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A549" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B549" s="7" t="s">
         <v>1052</v>
       </c>
-      <c r="B549" s="7" t="s">
-        <v>1053</v>
-      </c>
       <c r="C549" s="12" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A550" s="6" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B550" s="6" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C550" s="12" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A551" s="6" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B551" s="6" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C551" s="12" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A552" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B552" s="6" t="s">
         <v>1055</v>
       </c>
-      <c r="B552" s="6" t="s">
-        <v>1056</v>
-      </c>
       <c r="C552" s="12" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A553" s="6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B553" s="6" t="s">
         <v>1057</v>
       </c>
-      <c r="B553" s="6" t="s">
-        <v>1058</v>
-      </c>
       <c r="C553" s="12" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A554" s="6" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B554" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C554" s="12" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A555" s="6" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B555" s="6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C555" s="12" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A556" s="6" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B556" s="6" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C556" s="12" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A557" s="6" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B557" s="6" t="s">
         <v>1061</v>
       </c>
-      <c r="B557" s="6" t="s">
-        <v>1062</v>
-      </c>
       <c r="C557" s="12" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A558" s="6" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B558" s="6" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C558" s="12" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A559" s="6" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B559" s="6" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C559" s="12" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A560" s="6" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B560" s="6" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C560" s="12" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A561" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B561" s="7" t="s">
         <v>1066</v>
       </c>
-      <c r="B561" s="7" t="s">
-        <v>1067</v>
-      </c>
       <c r="C561" s="12" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A562" s="7" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B562" s="7" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C562" s="12" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A563" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B563" s="7" t="s">
         <v>1068</v>
       </c>
-      <c r="B563" s="7" t="s">
-        <v>1069</v>
-      </c>
       <c r="C563" s="12" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A564" s="6" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B564" s="6" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C564" s="12" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A565" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B565" s="6" t="s">
         <v>1071</v>
       </c>
-      <c r="B565" s="6" t="s">
-        <v>1072</v>
-      </c>
       <c r="C565" s="12" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A566" s="6" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B566" s="6" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C566" s="12" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A567" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B567" s="6" t="s">
         <v>1074</v>
       </c>
-      <c r="B567" s="6" t="s">
-        <v>1075</v>
-      </c>
       <c r="C567" s="12" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A568" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B568" s="6" t="s">
         <v>1076</v>
       </c>
-      <c r="B568" s="6" t="s">
-        <v>1077</v>
-      </c>
       <c r="C568" s="12" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A569" s="6" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B569" s="6" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C569" s="12" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A570" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B570" s="6" t="s">
         <v>1079</v>
       </c>
-      <c r="B570" s="6" t="s">
-        <v>1080</v>
-      </c>
       <c r="C570" s="12" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A571" s="6" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B571" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C571" s="12" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A572" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B572" s="6" t="s">
         <v>1082</v>
       </c>
-      <c r="B572" s="6" t="s">
-        <v>1083</v>
-      </c>
       <c r="C572" s="12" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A573" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B573" s="6" t="s">
         <v>1084</v>
       </c>
-      <c r="B573" s="6" t="s">
-        <v>1085</v>
-      </c>
       <c r="C573" s="12" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A574" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B574" s="6" t="s">
         <v>1086</v>
       </c>
-      <c r="B574" s="6" t="s">
-        <v>1087</v>
-      </c>
       <c r="C574" s="12" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A575" s="6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B575" s="6" t="s">
         <v>1088</v>
       </c>
-      <c r="B575" s="6" t="s">
-        <v>1089</v>
-      </c>
       <c r="C575" s="12" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A576" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B576" s="6" t="s">
         <v>1090</v>
       </c>
-      <c r="B576" s="6" t="s">
-        <v>1091</v>
-      </c>
       <c r="C576" s="12" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A577" s="6" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B577" s="6" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C577" s="12" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A578" s="6" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B578" s="6" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C578" s="12" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A579" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B579" s="6" t="s">
         <v>1094</v>
       </c>
-      <c r="B579" s="6" t="s">
-        <v>1095</v>
-      </c>
       <c r="C579" s="12" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A580" s="6" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B580" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C580" s="12" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A581" s="6" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B581" s="6" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C581" s="12" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A582" s="6" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B582" s="6" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C582" s="12" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A583" s="6" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B583" s="6" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C583" s="12" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="584" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A584" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B584" s="6" t="s">
         <v>1099</v>
       </c>
-      <c r="B584" s="6" t="s">
-        <v>1100</v>
-      </c>
       <c r="C584" s="12" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A585" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B585" s="6" t="s">
         <v>1101</v>
       </c>
-      <c r="B585" s="6" t="s">
-        <v>1102</v>
-      </c>
       <c r="C585" s="12" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A586" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B586" s="6" t="s">
         <v>1103</v>
       </c>
-      <c r="B586" s="6" t="s">
-        <v>1104</v>
-      </c>
       <c r="C586" s="12" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A587" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B587" s="6" t="s">
         <v>1105</v>
       </c>
-      <c r="B587" s="6" t="s">
-        <v>1106</v>
-      </c>
       <c r="C587" s="12" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A588" s="6" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B588" s="6" t="s">
         <v>1107</v>
       </c>
-      <c r="B588" s="6" t="s">
-        <v>1108</v>
-      </c>
       <c r="C588" s="12" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A589" s="6" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B589" s="6" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C589" s="12" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A590" s="6" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B590" s="6" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C590" s="12" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A591" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B591" s="6" t="s">
         <v>1111</v>
       </c>
-      <c r="B591" s="6" t="s">
-        <v>1112</v>
-      </c>
       <c r="C591" s="12" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A592" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B592" s="6" t="s">
         <v>1113</v>
       </c>
-      <c r="B592" s="6" t="s">
-        <v>1114</v>
-      </c>
       <c r="C592" s="12" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A593" s="6" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B593" s="6" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C593" s="12" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A594" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B594" s="6" t="s">
         <v>1116</v>
       </c>
-      <c r="B594" s="6" t="s">
-        <v>1117</v>
-      </c>
       <c r="C594" s="12" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A595" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B595" s="6" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C595" s="12" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A596" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B596" s="6" t="s">
         <v>1119</v>
       </c>
-      <c r="B596" s="6" t="s">
-        <v>1120</v>
-      </c>
       <c r="C596" s="12" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="597" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A597" s="6" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B597" s="6" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C597" s="12" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A598" s="6" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B598" s="6" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C598" s="12" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A599" s="6" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B599" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C599" s="12" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A600" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B600" s="6" t="s">
         <v>1123</v>
       </c>
-      <c r="B600" s="6" t="s">
-        <v>1124</v>
-      </c>
       <c r="C600" s="12" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="601" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A601" s="6" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B601" s="6" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C601" s="12" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A602" s="6" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B602" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="C602" s="12" t="s">
         <v>961</v>
-      </c>
-      <c r="C602" s="12" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A603" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B603" s="6" t="s">
         <v>1126</v>
       </c>
-      <c r="B603" s="6" t="s">
-        <v>1127</v>
-      </c>
       <c r="C603" s="12" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="604" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A604" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B604" s="6" t="s">
         <v>1128</v>
       </c>
-      <c r="B604" s="6" t="s">
-        <v>1129</v>
-      </c>
       <c r="C604" s="12" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="605" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A605" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B605" s="6" t="s">
         <v>1130</v>
       </c>
-      <c r="B605" s="6" t="s">
-        <v>1131</v>
-      </c>
       <c r="C605" s="12" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="606" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A606" s="6" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B606" s="6" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C606" s="28" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="607" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A607" s="6" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B607" s="6" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C607" s="12" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="608" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A608" s="6" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B608" s="6" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C608" s="12" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="609" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A609" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B609" s="6" t="s">
         <v>1135</v>
       </c>
-      <c r="B609" s="6" t="s">
-        <v>1136</v>
-      </c>
       <c r="C609" s="12" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="610" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A610" s="6" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B610" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C610" s="12" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="611" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A611" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B611" s="6" t="s">
         <v>1138</v>
       </c>
-      <c r="B611" s="6" t="s">
-        <v>1139</v>
-      </c>
       <c r="C611" s="12" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="612" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A612" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B612" s="6" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C612" s="12" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="613" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A613" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B613" s="6" t="s">
         <v>542</v>
       </c>
       <c r="C613" s="12" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="614" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A614" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B614" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C614" s="12" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="615" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A615" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B615" s="6" t="s">
         <v>1142</v>
       </c>
-      <c r="B615" s="6" t="s">
-        <v>1143</v>
-      </c>
       <c r="C615" s="12" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="616" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A616" s="23" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B616" s="23" t="s">
         <v>1144</v>
       </c>
-      <c r="B616" s="23" t="s">
-        <v>1145</v>
-      </c>
       <c r="C616" s="12" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="617" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A617" s="24" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B617" s="23" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C617" s="12" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="618" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A618" s="24" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B618" s="24" t="s">
         <v>1147</v>
       </c>
-      <c r="B618" s="24" t="s">
-        <v>1148</v>
-      </c>
       <c r="C618" s="12" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="619" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A619" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B619" s="24" t="s">
         <v>1151</v>
       </c>
-      <c r="B619" s="24" t="s">
+      <c r="C619" s="12" t="s">
         <v>1152</v>
-      </c>
-      <c r="C619" s="12" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="620" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A620" s="25" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B620" s="26" t="s">
         <v>1154</v>
       </c>
-      <c r="B620" s="26" t="s">
+      <c r="C620" s="12" t="s">
         <v>1155</v>
-      </c>
-      <c r="C620" s="12" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="621" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A621" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B621" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="B621" s="1" t="s">
+      <c r="C621" s="12" t="s">
         <v>1158</v>
-      </c>
-      <c r="C621" s="12" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="622" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A622" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B622" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="B622" s="1" t="s">
+      <c r="C622" s="12" t="s">
         <v>1161</v>
-      </c>
-      <c r="C622" s="12" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="623" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A623" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B623" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="B623" s="1" t="s">
+      <c r="C623" s="12" t="s">
         <v>1164</v>
-      </c>
-      <c r="C623" s="12" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="624" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A624" s="27" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B624" s="27" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C624" s="12" t="s">
         <v>1166</v>
-      </c>
-      <c r="B624" s="27" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C624" s="12" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="625" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A625" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B625" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="B625" s="1" t="s">
-        <v>1169</v>
-      </c>
       <c r="C625" s="12" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A626" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B626" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="B626" s="1" t="s">
+      <c r="C626" s="12" t="s">
         <v>1171</v>
-      </c>
-      <c r="C626" s="12" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="627" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A627" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B627" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C627" s="12" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="628" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A628" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B628" s="1" t="s">
         <v>1175</v>
       </c>
-      <c r="B628" s="1" t="s">
+      <c r="C628" s="12" t="s">
         <v>1176</v>
-      </c>
-      <c r="C628" s="12" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="629" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A629" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B629" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="B629" s="1" t="s">
+      <c r="C629" s="12" t="s">
         <v>1180</v>
-      </c>
-      <c r="C629" s="12" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="630" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A630" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B630" s="1" t="s">
         <v>1182</v>
       </c>
-      <c r="B630" s="1" t="s">
+      <c r="C630" s="12" t="s">
         <v>1183</v>
-      </c>
-      <c r="C630" s="12" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="631" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A631" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C631" s="12" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="632" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A632" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B632" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="B632" s="1" t="s">
-        <v>1187</v>
-      </c>
       <c r="C632" s="12" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="633" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A633" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B633" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B633" s="1" t="s">
+      <c r="C633" s="12" t="s">
         <v>1191</v>
-      </c>
-      <c r="C633" s="12" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="634" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A634" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B634" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="B634" s="1" t="s">
+      <c r="C634" s="12" t="s">
         <v>1194</v>
-      </c>
-      <c r="C634" s="12" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A635" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C635" s="12" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A636" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B636" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="B636" s="1" t="s">
+      <c r="C636" s="12" t="s">
         <v>1197</v>
-      </c>
-      <c r="C636" s="12" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A637" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B637" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="B637" s="1" t="s">
+      <c r="C637" s="12" t="s">
         <v>1200</v>
-      </c>
-      <c r="C637" s="12" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A638" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B638" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="B638" s="1" t="s">
+      <c r="C638" s="12" t="s">
         <v>1203</v>
-      </c>
-      <c r="C638" s="12" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="639" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A639" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B639" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="B639" s="1" t="s">
-        <v>1206</v>
-      </c>
       <c r="C639" s="12" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="640" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A640" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B640" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="B640" s="1" t="s">
-        <v>1208</v>
-      </c>
       <c r="C640" s="12" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A641" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B641" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="B641" s="1" t="s">
-        <v>1210</v>
-      </c>
       <c r="C641" s="12" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A642" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B642" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="B642" s="1" t="s">
-        <v>1212</v>
-      </c>
       <c r="C642" s="12" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A643" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C643" s="12" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A644" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B644" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="B644" s="1" t="s">
-        <v>1215</v>
-      </c>
       <c r="C644" s="12" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="645" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A645" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C645" s="12" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="646" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A646" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B646" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="B646" s="1" t="s">
-        <v>1218</v>
-      </c>
       <c r="C646" s="12" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="647" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A647" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B647" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="B647" s="1" t="s">
+      <c r="C647" s="12" t="s">
         <v>1227</v>
-      </c>
-      <c r="C647" s="12" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="648" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A648" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B648" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="B648" s="1" t="s">
+      <c r="C648" s="12" t="s">
         <v>1230</v>
-      </c>
-      <c r="C648" s="12" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="649" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A649" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B649" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="B649" s="1" t="s">
-        <v>1233</v>
-      </c>
       <c r="C649" s="12" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="650" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A650" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B650" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="B650" s="1" t="s">
-        <v>1235</v>
-      </c>
       <c r="C650" s="12" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="651" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A651" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B651" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="B651" s="1" t="s">
+      <c r="C651" s="12" t="s">
         <v>1239</v>
-      </c>
-      <c r="C651" s="12" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="652" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A652" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B652" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="B652" s="1" t="s">
-        <v>1242</v>
-      </c>
       <c r="C652" s="12" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="653" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A653" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C653" s="12" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="654" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A654" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C654" s="12" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="655" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A655" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B655" s="1" t="s">
         <v>1245</v>
       </c>
-      <c r="B655" s="1" t="s">
-        <v>1246</v>
-      </c>
       <c r="C655" s="12" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A656" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B656" s="1" t="s">
         <v>1247</v>
       </c>
-      <c r="B656" s="1" t="s">
-        <v>1248</v>
-      </c>
       <c r="C656" s="12" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A657" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B657" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="B657" s="1" t="s">
+      <c r="C657" s="12" t="s">
         <v>1253</v>
-      </c>
-      <c r="C657" s="12" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A658" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B658" s="1" t="s">
         <v>1255</v>
       </c>
-      <c r="B658" s="1" t="s">
-        <v>1256</v>
-      </c>
       <c r="C658" s="12" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A659" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B659" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="B659" s="1" t="s">
-        <v>1258</v>
-      </c>
       <c r="C659" s="12" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A660" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C660" s="12" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="661" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A661" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C661" s="12" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="662" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A662" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B662" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="B662" s="1" t="s">
-        <v>1262</v>
-      </c>
       <c r="C662" s="12" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="663" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A663" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B663" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="B663" s="1" t="s">
-        <v>1264</v>
-      </c>
       <c r="C663" s="12" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="664" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A664" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B664" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="B664" s="1" t="s">
+      <c r="C664" s="12" t="s">
         <v>1270</v>
-      </c>
-      <c r="C664" s="12" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="665" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A665" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B665" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="B665" s="1" t="s">
-        <v>1273</v>
-      </c>
       <c r="C665" s="12" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="666" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A666" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B666" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="B666" s="1" t="s">
-        <v>1275</v>
-      </c>
       <c r="C666" s="12" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="667" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A667" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C667" s="12" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="668" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A668" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B668" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="B668" s="1" t="s">
-        <v>1277</v>
-      </c>
       <c r="C668" s="12" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="669" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A669" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C669" s="12" t="s">
         <v>1281</v>
-      </c>
-      <c r="B669" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C669" s="12" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="670" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A670" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C670" s="12" t="s">
         <v>1283</v>
-      </c>
-      <c r="B670" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C670" s="12" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="671" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A671" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B671" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="B671" s="1" t="s">
+      <c r="C671" s="12" t="s">
         <v>1286</v>
-      </c>
-      <c r="C671" s="12" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="672" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A672" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B672" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="B672" s="1" t="s">
-        <v>1289</v>
-      </c>
       <c r="C672" s="12" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="673" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A673" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B673" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="B673" s="1" t="s">
-        <v>1291</v>
-      </c>
       <c r="C673" s="12" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="674" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A674" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B674" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="B674" s="1" t="s">
-        <v>1295</v>
-      </c>
       <c r="C674" s="12" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="675" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A675" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C675" s="12" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="676" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A676" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B676" s="1" t="s">
         <v>1297</v>
       </c>
-      <c r="B676" s="1" t="s">
-        <v>1298</v>
-      </c>
       <c r="C676" s="12" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="677" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A677" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B677" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="B677" s="1" t="s">
-        <v>1302</v>
-      </c>
       <c r="C677" s="12" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="678" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A678" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B678" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C678" s="12" t="s">
         <v>1303</v>
-      </c>
-      <c r="C678" s="12" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="679" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A679" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B679" s="1" t="s">
         <v>1305</v>
       </c>
-      <c r="B679" s="1" t="s">
-        <v>1306</v>
-      </c>
       <c r="C679" s="12" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="680" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A680" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B680" s="1" t="s">
         <v>1307</v>
       </c>
-      <c r="B680" s="1" t="s">
-        <v>1308</v>
-      </c>
       <c r="C680" s="12" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="681" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A681" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B681" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="B681" s="1" t="s">
-        <v>1310</v>
-      </c>
       <c r="C681" s="12" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="682" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A682" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B682" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="B682" s="1" t="s">
+      <c r="C682" s="12" t="s">
         <v>1315</v>
-      </c>
-      <c r="C682" s="12" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="683" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A683" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B683" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="B683" s="1" t="s">
-        <v>1318</v>
-      </c>
       <c r="C683" s="12" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="684" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A684" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B684" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="B684" s="1" t="s">
-        <v>1320</v>
-      </c>
       <c r="C684" s="12" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="685" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A685" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B685" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="B685" s="1" t="s">
-        <v>1324</v>
-      </c>
       <c r="C685" s="12" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="686" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A686" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C686" s="12" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="687" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A687" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C687" s="12" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="688" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A688" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B688" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B688" s="1" t="s">
+      <c r="C688" s="12" t="s">
         <v>1330</v>
-      </c>
-      <c r="C688" s="12" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="689" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A689" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B689" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="B689" s="1" t="s">
+      <c r="C689" s="12" t="s">
         <v>1333</v>
-      </c>
-      <c r="C689" s="12" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="690" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A690" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C690" s="12" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="691" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A691" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B691" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="B691" s="1" t="s">
+      <c r="C691" s="12" t="s">
         <v>1337</v>
-      </c>
-      <c r="C691" s="12" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="692" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A692" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C692" s="12" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="693" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A693" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B693" s="1" t="s">
         <v>1339</v>
       </c>
-      <c r="B693" s="1" t="s">
-        <v>1340</v>
-      </c>
       <c r="C693" s="12" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="694" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A694" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C694" s="12" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="695" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A695" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B695" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C695" s="12" t="s">
         <v>1342</v>
-      </c>
-      <c r="C695" s="12" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="696" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A696" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C696" s="12" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="697" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A697" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B697" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="B697" s="1" t="s">
+      <c r="C697" s="12" t="s">
         <v>1345</v>
-      </c>
-      <c r="C697" s="12" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="698" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A698" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B698" s="1" t="s">
         <v>1347</v>
       </c>
-      <c r="B698" s="1" t="s">
-        <v>1348</v>
-      </c>
       <c r="C698" s="12" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="699" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A699" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C699" s="12" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="700" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A700" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B700" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="B700" s="1" t="s">
+      <c r="C700" s="12" t="s">
         <v>1356</v>
-      </c>
-      <c r="C700" s="12" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="701" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A701" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B701" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C701" s="12" t="s">
         <v>1363</v>
-      </c>
-      <c r="C701" s="12" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="702" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A702" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B702" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C702" s="12" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="703" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A703" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C703" s="12" t="s">
         <v>1478</v>
-      </c>
-      <c r="B703" s="1" t="s">
-        <v>1477</v>
-      </c>
-      <c r="C703" s="12" t="s">
-        <v>1479</v>
       </c>
     </row>
     <row r="704" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A704" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B704" s="1" t="s">
         <v>1480</v>
       </c>
-      <c r="B704" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="C704" s="12" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="705" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A705" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="C705" s="12" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="706" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13462,10 +13462,10 @@
         <v>296</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C706" s="12" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="707" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13473,76 +13473,76 @@
         <v>296</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C707" s="12" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="708" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A708" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B708" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="B708" s="1" t="s">
-        <v>1489</v>
-      </c>
       <c r="C708" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="709" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A709" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B709" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C709" s="12" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="710" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A710" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B710" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="B710" s="1" t="s">
-        <v>1491</v>
-      </c>
       <c r="C710" s="12" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="711" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A711" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="C711" s="12" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="712" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A712" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B712" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="B712" s="1" t="s">
-        <v>1495</v>
-      </c>
       <c r="C712" s="12" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="713" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A713" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B713" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C713" s="12" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="714" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13553,40 +13553,40 @@
         <v>265</v>
       </c>
       <c r="C714" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="715" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A715" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B715" s="1" t="s">
         <v>1499</v>
       </c>
-      <c r="B715" s="1" t="s">
-        <v>1500</v>
-      </c>
       <c r="C715" s="12" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="716" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A716" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C716" s="12" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A717" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B717" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C717" s="12" t="s">
         <v>1502</v>
-      </c>
-      <c r="C717" s="12" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="718" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13597,7 +13597,7 @@
         <v>298</v>
       </c>
       <c r="C718" s="12" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="719" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13605,21 +13605,21 @@
         <v>299</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="C719" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A720" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B720" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="B720" s="1" t="s">
+      <c r="C720" s="12" t="s">
         <v>1506</v>
-      </c>
-      <c r="C720" s="12" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13627,10 +13627,10 @@
         <v>60</v>
       </c>
       <c r="B721" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C721" s="12" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="722" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13638,10 +13638,10 @@
         <v>60</v>
       </c>
       <c r="B722" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C722" s="12" t="s">
         <v>1509</v>
-      </c>
-      <c r="C722" s="12" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="723" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13649,65 +13649,65 @@
         <v>230</v>
       </c>
       <c r="B723" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C723" s="12" t="s">
         <v>1511</v>
-      </c>
-      <c r="C723" s="12" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="724" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A724" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C724" s="12" t="s">
         <v>1514</v>
-      </c>
-      <c r="B724" s="1" t="s">
-        <v>1513</v>
-      </c>
-      <c r="C724" s="12" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="725" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A725" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B725" s="1" t="s">
         <v>1516</v>
       </c>
-      <c r="B725" s="1" t="s">
+      <c r="C725" s="12" t="s">
         <v>1517</v>
-      </c>
-      <c r="C725" s="12" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="726" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A726" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B726" s="1" t="s">
         <v>1519</v>
       </c>
-      <c r="B726" s="1" t="s">
-        <v>1520</v>
-      </c>
       <c r="C726" s="12" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="727" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A727" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B727" s="1" t="s">
         <v>1523</v>
       </c>
-      <c r="B727" s="1" t="s">
-        <v>1524</v>
-      </c>
       <c r="C727" s="12" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="728" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A728" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B728" s="1" t="s">
         <v>1525</v>
       </c>
-      <c r="B728" s="1" t="s">
-        <v>1526</v>
-      </c>
       <c r="C728" s="12" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="729" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13718,84 +13718,84 @@
         <v>205</v>
       </c>
       <c r="C729" s="12" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="730" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A730" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B730" s="1" t="s">
         <v>303</v>
       </c>
       <c r="C730" s="12" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="731" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A731" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B731" s="1" t="s">
         <v>1528</v>
       </c>
-      <c r="B731" s="1" t="s">
-        <v>1529</v>
-      </c>
       <c r="C731" s="12" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="732" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A732" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B732" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="B732" s="1" t="s">
-        <v>1531</v>
-      </c>
       <c r="C732" s="12" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="733" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A733" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C733" s="12" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="734" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A734" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B734" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="B734" s="1" t="s">
-        <v>1534</v>
-      </c>
       <c r="C734" s="12" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="735" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A735" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B735" s="1" t="s">
         <v>1535</v>
       </c>
-      <c r="B735" s="1" t="s">
-        <v>1536</v>
-      </c>
       <c r="C735" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="736" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A736" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C736" s="12" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="737" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13806,7 +13806,7 @@
         <v>305</v>
       </c>
       <c r="C737" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="738" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13817,7 +13817,7 @@
         <v>305</v>
       </c>
       <c r="C738" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="739" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13828,117 +13828,117 @@
         <v>308</v>
       </c>
       <c r="C739" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="740" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A740" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C740" s="12" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="741" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A741" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B741" s="1" t="s">
         <v>1539</v>
       </c>
-      <c r="B741" s="1" t="s">
-        <v>1540</v>
-      </c>
       <c r="C741" s="12" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="742" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A742" s="1" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B742" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C742" s="12" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="743" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A743" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B743" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C743" s="12" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="744" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A744" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C744" s="12" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="745" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A745" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B745" s="1" t="s">
         <v>1554</v>
       </c>
-      <c r="B745" s="1" t="s">
-        <v>1555</v>
-      </c>
       <c r="C745" s="12" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="746" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A746" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B746" s="1" t="s">
         <v>1556</v>
       </c>
-      <c r="B746" s="1" t="s">
-        <v>1557</v>
-      </c>
       <c r="C746" s="12" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="747" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A747" s="1" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B747" s="1" t="s">
         <v>309</v>
       </c>
       <c r="C747" s="12" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="748" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A748" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B748" s="1" t="s">
         <v>1559</v>
       </c>
-      <c r="B748" s="1" t="s">
-        <v>1560</v>
-      </c>
       <c r="C748" s="12" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="749" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A749" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B749" s="1" t="s">
         <v>1561</v>
       </c>
-      <c r="B749" s="1" t="s">
-        <v>1562</v>
-      </c>
       <c r="C749" s="12" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="750" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13949,7 +13949,7 @@
         <v>209</v>
       </c>
       <c r="C750" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="751" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13960,7 +13960,7 @@
         <v>209</v>
       </c>
       <c r="C751" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="752" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13971,7 +13971,7 @@
         <v>209</v>
       </c>
       <c r="C752" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="753" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13982,7 +13982,7 @@
         <v>209</v>
       </c>
       <c r="C753" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="754" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -13993,7 +13993,7 @@
         <v>210</v>
       </c>
       <c r="C754" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="755" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14004,7 +14004,7 @@
         <v>265</v>
       </c>
       <c r="C755" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="756" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14015,7 +14015,7 @@
         <v>265</v>
       </c>
       <c r="C756" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="757" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14026,7 +14026,7 @@
         <v>265</v>
       </c>
       <c r="C757" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="758" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14037,7 +14037,7 @@
         <v>265</v>
       </c>
       <c r="C758" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="759" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14048,7 +14048,7 @@
         <v>265</v>
       </c>
       <c r="C759" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="760" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14059,7 +14059,7 @@
         <v>265</v>
       </c>
       <c r="C760" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="761" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14070,84 +14070,84 @@
         <v>302</v>
       </c>
       <c r="C761" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="762" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A762" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B762" s="1" t="s">
         <v>1570</v>
       </c>
-      <c r="B762" s="1" t="s">
+      <c r="C762" s="12" t="s">
         <v>1571</v>
-      </c>
-      <c r="C762" s="12" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="763" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A763" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B763" s="1" t="s">
         <v>1573</v>
       </c>
-      <c r="B763" s="1" t="s">
+      <c r="C763" s="12" t="s">
         <v>1574</v>
-      </c>
-      <c r="C763" s="12" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="764" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A764" s="1" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B764" s="1" t="s">
         <v>152</v>
       </c>
       <c r="C764" s="12" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="765" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A765" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B765" s="1" t="s">
         <v>1577</v>
       </c>
-      <c r="B765" s="1" t="s">
-        <v>1578</v>
-      </c>
       <c r="C765" s="12" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="766" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A766" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B766" s="1" t="s">
         <v>1581</v>
       </c>
-      <c r="B766" s="1" t="s">
-        <v>1582</v>
-      </c>
       <c r="C766" s="12" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="767" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A767" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B767" s="1" t="s">
         <v>1583</v>
       </c>
-      <c r="B767" s="1" t="s">
+      <c r="C767" s="12" t="s">
         <v>1584</v>
-      </c>
-      <c r="C767" s="12" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="768" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A768" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B768" s="1" t="s">
         <v>1586</v>
       </c>
-      <c r="B768" s="1" t="s">
+      <c r="C768" s="12" t="s">
         <v>1587</v>
-      </c>
-      <c r="C768" s="12" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="769" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14155,65 +14155,65 @@
         <v>189</v>
       </c>
       <c r="B769" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C769" s="12" t="s">
         <v>1589</v>
-      </c>
-      <c r="C769" s="12" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="770" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A770" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B770" s="1" t="s">
         <v>1592</v>
       </c>
-      <c r="B770" s="1" t="s">
+      <c r="C770" s="12" t="s">
         <v>1593</v>
-      </c>
-      <c r="C770" s="12" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="771" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A771" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B771" s="1" t="s">
         <v>1595</v>
       </c>
-      <c r="B771" s="1" t="s">
-        <v>1596</v>
-      </c>
       <c r="C771" s="12" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="772" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A772" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B772" s="1" t="s">
         <v>1597</v>
       </c>
-      <c r="B772" s="1" t="s">
-        <v>1598</v>
-      </c>
       <c r="C772" s="12" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="773" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A773" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B773" s="1" t="s">
         <v>1601</v>
       </c>
-      <c r="B773" s="1" t="s">
-        <v>1602</v>
-      </c>
       <c r="C773" s="12" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="774" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A774" s="1" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B774" s="1" t="s">
         <v>324</v>
       </c>
       <c r="C774" s="12" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="775" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14221,21 +14221,21 @@
         <v>281</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="C775" s="12" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B776" s="1" t="s">
         <v>1607</v>
       </c>
-      <c r="B776" s="1" t="s">
+      <c r="C776" s="12" t="s">
         <v>1608</v>
-      </c>
-      <c r="C776" s="12" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14246,18 +14246,18 @@
         <v>326</v>
       </c>
       <c r="C777" s="12" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="778" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A778" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C778" s="12" t="s">
         <v>1611</v>
-      </c>
-      <c r="B778" s="1" t="s">
-        <v>1610</v>
-      </c>
-      <c r="C778" s="12" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="779" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
@@ -14268,106 +14268,106 @@
         <v>336</v>
       </c>
       <c r="C779" s="12" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="780" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A780" s="29" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B780" s="29" t="s">
         <v>1614</v>
       </c>
-      <c r="B780" s="29" t="s">
+      <c r="C780" s="12" t="s">
         <v>1615</v>
-      </c>
-      <c r="C780" s="12" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="781" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A781" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B781" s="1" t="s">
         <v>1617</v>
       </c>
-      <c r="B781" s="1" t="s">
-        <v>1618</v>
-      </c>
       <c r="C781" s="28" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="782" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A782" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B782" s="1" t="s">
         <v>1619</v>
       </c>
-      <c r="B782" s="1" t="s">
+      <c r="C782" s="12" t="s">
         <v>1620</v>
-      </c>
-      <c r="C782" s="12" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="783" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A783" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C783" s="12" t="s">
         <v>1623</v>
-      </c>
-      <c r="B783" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C783" s="12" t="s">
-        <v>1624</v>
       </c>
     </row>
     <row r="784" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A784" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B784" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C784" s="12" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="785" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A785" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B785" s="1" t="s">
         <v>1628</v>
       </c>
-      <c r="B785" s="1" t="s">
+      <c r="C785" s="12" t="s">
         <v>1629</v>
-      </c>
-      <c r="C785" s="12" t="s">
-        <v>1630</v>
       </c>
     </row>
     <row r="786" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A786" s="6" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B786" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C786" s="12" t="s">
         <v>1634</v>
-      </c>
-      <c r="C786" s="12" t="s">
-        <v>1635</v>
       </c>
     </row>
     <row r="787" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A787" s="1" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B787" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C787" s="12" t="s">
         <v>1636</v>
-      </c>
-      <c r="C787" s="12" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="788" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A788" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C788" s="12" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.3">
@@ -19188,603 +19188,603 @@
     <hyperlink ref="C127" r:id="rId53" xr:uid="{1193AB46-EA19-45C3-91CC-5A519029572B}"/>
     <hyperlink ref="C185" r:id="rId54" xr:uid="{A15F5C19-02CB-48D3-90A6-E27AC5740620}"/>
     <hyperlink ref="C302" r:id="rId55" xr:uid="{2061F92B-B9B8-45C6-AB6E-DB28CF7FED42}"/>
-    <hyperlink ref="C303:C333" r:id="rId56" display="https://cetonline.karnataka.gov.in/keawebentry456/ugcet2025/NEW_PROV_FEES_STR_Engenglish.pdf" xr:uid="{7BC439DB-2B72-46A0-9939-4A3B28EE2715}"/>
-    <hyperlink ref="C301" r:id="rId57" xr:uid="{50BE28BE-EEC0-42A1-BF88-53F38F6E210D}"/>
-    <hyperlink ref="C300" r:id="rId58" xr:uid="{CFD94F31-1639-49D8-AC52-E4A9B6E79A88}"/>
-    <hyperlink ref="C281" r:id="rId59" xr:uid="{39908BCE-03CE-4E8E-88E0-14867A42C301}"/>
-    <hyperlink ref="C282" r:id="rId60" xr:uid="{B144F34E-4532-445C-99A7-8D0142EF6573}"/>
-    <hyperlink ref="C284" r:id="rId61" xr:uid="{97B1CB3D-D17B-4AA0-B81B-A13DD58BEF07}"/>
-    <hyperlink ref="C285" r:id="rId62" xr:uid="{85716DDE-1BCF-4C45-BD30-F0F32FCC7BA2}"/>
-    <hyperlink ref="C286" r:id="rId63" xr:uid="{1A73D5EC-C5F3-450A-9415-6433112AC5F5}"/>
-    <hyperlink ref="C287" r:id="rId64" xr:uid="{72B68110-7FD3-4CC3-BF9B-C2574C9FABBC}"/>
-    <hyperlink ref="C288" r:id="rId65" xr:uid="{0F47A361-B9DE-414D-8AAC-08AD33F5DBDA}"/>
-    <hyperlink ref="C289" r:id="rId66" xr:uid="{EE607C57-767F-418D-8F35-E4B1333ECE83}"/>
-    <hyperlink ref="C290" r:id="rId67" xr:uid="{3D5C617B-CE68-4732-AF17-3B49144E78EB}"/>
-    <hyperlink ref="C291" r:id="rId68" xr:uid="{76744081-BB3C-4B23-B65F-1C6CF056D4EE}"/>
-    <hyperlink ref="C292" r:id="rId69" xr:uid="{C14DC252-4FD7-49CC-8A77-D245087DAAC4}"/>
-    <hyperlink ref="C293" r:id="rId70" xr:uid="{A425C347-D05D-4B03-A1C8-85A516D4D679}"/>
-    <hyperlink ref="C294" r:id="rId71" xr:uid="{1A0A2778-C528-4240-AE1C-C721590C29A0}"/>
-    <hyperlink ref="C295" r:id="rId72" xr:uid="{075590E0-3ED6-48C1-8C36-BC102567B233}"/>
-    <hyperlink ref="C296" r:id="rId73" xr:uid="{2850DD06-7003-4B9B-91BD-7BB02A744727}"/>
-    <hyperlink ref="C297" r:id="rId74" xr:uid="{46BEC18B-400C-4027-A3EE-BB7604D3737C}"/>
-    <hyperlink ref="C298" r:id="rId75" xr:uid="{1C99AAE8-E2BA-45C3-8A01-9F78A181E0CD}"/>
-    <hyperlink ref="C299" r:id="rId76" xr:uid="{6103D502-998D-427A-9A23-6679ECC115E0}"/>
-    <hyperlink ref="C348" r:id="rId77" xr:uid="{2085C974-D039-483D-830E-688CA69587CE}"/>
-    <hyperlink ref="C349" r:id="rId78" xr:uid="{92BDC019-D47F-42C6-88EF-FF3D15C3253C}"/>
-    <hyperlink ref="C350" r:id="rId79" xr:uid="{A02D7A54-7141-4DC3-BD2C-401F1F063D6A}"/>
-    <hyperlink ref="C351" r:id="rId80" xr:uid="{3696490A-3DF9-4760-BD7A-E5DDF2847C97}"/>
-    <hyperlink ref="C352" r:id="rId81" xr:uid="{D2ED480E-8869-4050-ACEC-D41D9BED3531}"/>
-    <hyperlink ref="C353" r:id="rId82" xr:uid="{35FE7A98-D273-4A53-A436-4D6DC405CE44}"/>
-    <hyperlink ref="C354" r:id="rId83" xr:uid="{02AFB5CE-7536-438D-B2CA-FD65369F785B}"/>
-    <hyperlink ref="C355" r:id="rId84" xr:uid="{80824CD4-A47B-491E-AD53-0E7CE2983953}"/>
-    <hyperlink ref="C357" r:id="rId85" xr:uid="{E42870AF-4970-422D-BF87-CF83600C953D}"/>
-    <hyperlink ref="C358" r:id="rId86" xr:uid="{B00B442D-9361-44A2-A000-59B7159F8A5F}"/>
-    <hyperlink ref="C360" r:id="rId87" xr:uid="{E38D219C-145E-4473-B879-70FF23EE0192}"/>
-    <hyperlink ref="C361" r:id="rId88" xr:uid="{D8E0CEBF-68A2-499E-896E-05DB38D0B569}"/>
-    <hyperlink ref="C363" r:id="rId89" xr:uid="{E35E0044-2BA8-4628-84A9-FB97196C55AD}"/>
-    <hyperlink ref="C364" r:id="rId90" xr:uid="{F6947610-E27A-44A0-9509-E18C4A91087E}"/>
-    <hyperlink ref="C367" r:id="rId91" xr:uid="{DEC92388-812C-41BF-8187-02600A52A136}"/>
-    <hyperlink ref="C369" r:id="rId92" xr:uid="{95752DC6-55EC-4FB6-89D8-2502BFFA6DA2}"/>
-    <hyperlink ref="C370:C383" r:id="rId93" display="https://drive.google.com/file/d/1vog0rWXRzF2SF33kPUkXoESePa2Hb8wr/view" xr:uid="{C3AE02AF-1F36-4B36-8496-90AA87FFF470}"/>
-    <hyperlink ref="C388" r:id="rId94" xr:uid="{C6049889-C71C-406E-850C-4A6007DB2B0B}"/>
-    <hyperlink ref="C389:C404" r:id="rId95" display="https://drive.google.com/file/d/1vog0rWXRzF2SF33kPUkXoESePa2Hb8wr/view" xr:uid="{A36E29EE-BB11-4244-BCE2-DD9B55DC7098}"/>
-    <hyperlink ref="C456" r:id="rId96" xr:uid="{7CD6D41E-3B33-4720-BAB0-B43E7D8876FE}"/>
-    <hyperlink ref="C449" r:id="rId97" xr:uid="{08D546DD-62CC-4F48-85C0-BE27C50B1380}"/>
-    <hyperlink ref="C458" r:id="rId98" xr:uid="{8F138784-F396-44B3-8C5B-34D8CBB85FA8}"/>
-    <hyperlink ref="C45" r:id="rId99" xr:uid="{9C6777DC-9050-416C-A895-3805C52237CC}"/>
-    <hyperlink ref="C46" r:id="rId100" xr:uid="{D8BBE816-3252-4B73-881D-738B7A638572}"/>
-    <hyperlink ref="C47" r:id="rId101" xr:uid="{DB604BA5-DF8C-47A2-9D97-F721C4BA7E09}"/>
-    <hyperlink ref="C48" r:id="rId102" xr:uid="{8B1A4CD8-BF23-4F35-83AF-10776947E5EF}"/>
-    <hyperlink ref="C49" r:id="rId103" xr:uid="{AD98015A-EF46-4A97-9F4B-ED452873A2C9}"/>
-    <hyperlink ref="C50" r:id="rId104" xr:uid="{B6926384-7374-484C-A09B-5E6859DB1B53}"/>
-    <hyperlink ref="C444" r:id="rId105" xr:uid="{1A7BED46-A4D2-4122-AE6B-8D9B7BC1E57E}"/>
-    <hyperlink ref="C443" r:id="rId106" xr:uid="{B42A7545-0A4B-4720-8F10-69F89F36E4A2}"/>
-    <hyperlink ref="C442" r:id="rId107" xr:uid="{B01190ED-7FA4-4324-A4AA-A0B423EF3F2F}"/>
-    <hyperlink ref="C387" r:id="rId108" xr:uid="{E77156BB-529F-4C0A-9E10-F8A630153851}"/>
-    <hyperlink ref="C441" r:id="rId109" xr:uid="{5F8E80AC-1EC8-47B9-8E66-DCFA235AA1A7}"/>
-    <hyperlink ref="C429" r:id="rId110" xr:uid="{A1B03889-75C2-4FBB-90CE-69C8A85694E2}"/>
-    <hyperlink ref="C432" r:id="rId111" xr:uid="{A688D2FB-7C80-493D-8E33-81F480A1079A}"/>
-    <hyperlink ref="C334" r:id="rId112" xr:uid="{409DEF6B-637B-4337-AC44-3FBF64FC2184}"/>
-    <hyperlink ref="C52" r:id="rId113" xr:uid="{25A0B1B3-F505-42AC-B470-194048815C37}"/>
-    <hyperlink ref="C53" r:id="rId114" xr:uid="{651BB4B5-94B4-4E7C-B602-48074069E520}"/>
-    <hyperlink ref="C54" r:id="rId115" xr:uid="{ADAAA73E-15E5-4523-B79F-44D50D9F665E}"/>
-    <hyperlink ref="C55" r:id="rId116" xr:uid="{B8FF9BDA-DC69-4E1F-A29C-CA2FC6758FA4}"/>
-    <hyperlink ref="C56" r:id="rId117" xr:uid="{D1069D97-0F2F-46FE-981C-DE27B837E146}"/>
-    <hyperlink ref="C57" r:id="rId118" xr:uid="{71C34B2C-4806-4433-8843-5E2C9D37997A}"/>
-    <hyperlink ref="C58" r:id="rId119" xr:uid="{59FFCFC0-B91B-45B4-BA1A-44CC77CAB8E6}"/>
-    <hyperlink ref="C74" r:id="rId120" xr:uid="{E2C1FEF6-329B-4047-B2DC-A65627AA2EBB}"/>
-    <hyperlink ref="C80" r:id="rId121" xr:uid="{F0ECA015-E7E4-4C2E-A634-3E3DE03FF78D}"/>
-    <hyperlink ref="C83" r:id="rId122" xr:uid="{1CA08F40-73C7-4E1E-B100-CFF54A53EF6A}"/>
-    <hyperlink ref="C84" r:id="rId123" xr:uid="{C2FAD9F8-5365-4F7B-939B-161DD7F9E21E}"/>
-    <hyperlink ref="C85" r:id="rId124" xr:uid="{8749C6A4-5913-4791-8743-C46F14EB0330}"/>
-    <hyperlink ref="C86" r:id="rId125" xr:uid="{C0821B94-7A8E-4CF0-9FB2-665C66F0FEF5}"/>
-    <hyperlink ref="C90" r:id="rId126" xr:uid="{6F3A4D1D-73E0-4573-A874-B9E6BA54DB8B}"/>
-    <hyperlink ref="C92" r:id="rId127" xr:uid="{CECC8A8E-E7A2-48B9-BEF5-CFDB5FAD1789}"/>
-    <hyperlink ref="C113" r:id="rId128" location="feeDetails" xr:uid="{05D90BFF-52D2-46FA-87CB-DE7EEADAAE3B}"/>
-    <hyperlink ref="C114" r:id="rId129" location="feeDetails" xr:uid="{31BF87E5-F141-4A66-8C9C-D3305B32752F}"/>
-    <hyperlink ref="C115" r:id="rId130" xr:uid="{137D059F-835D-40BB-BE4C-4C8B10C06F79}"/>
-    <hyperlink ref="C116" r:id="rId131" xr:uid="{CDAB71DC-AB58-426A-B4A9-F3E59ADC93B8}"/>
-    <hyperlink ref="C117" r:id="rId132" xr:uid="{15BF9224-665B-4E90-BD0B-79821E6ED4D8}"/>
-    <hyperlink ref="C118" r:id="rId133" xr:uid="{C559B688-3520-4AAE-AD9D-139E016C9C51}"/>
-    <hyperlink ref="C119" r:id="rId134" xr:uid="{2890A325-FC09-4085-BECB-FFB79098E847}"/>
-    <hyperlink ref="C120" r:id="rId135" xr:uid="{E149005A-D5CD-4279-9774-1F79D5DD7384}"/>
-    <hyperlink ref="C135" r:id="rId136" xr:uid="{654C965C-4AEF-490B-BF67-74F80E293DA9}"/>
-    <hyperlink ref="C335" r:id="rId137" xr:uid="{E9AE3AFD-268E-40D4-8290-625F440E5302}"/>
-    <hyperlink ref="C336" r:id="rId138" xr:uid="{AA2909AE-78FE-473E-B408-EF8505C221E1}"/>
-    <hyperlink ref="C337" r:id="rId139" xr:uid="{9A268E81-8526-4AAD-83A0-DAAA0587F608}"/>
-    <hyperlink ref="C338" r:id="rId140" xr:uid="{9802CB4D-1666-4A2B-BD6B-C4B6DF98DE4B}"/>
-    <hyperlink ref="C339" r:id="rId141" xr:uid="{5B56D843-A553-463F-96D6-1F9B7F750CC9}"/>
-    <hyperlink ref="C340" r:id="rId142" xr:uid="{3F82A7F4-2089-4A78-AD3F-404325FD8806}"/>
-    <hyperlink ref="C341" r:id="rId143" xr:uid="{D4C39F60-C7A5-4EC5-8381-0BA84090CEF1}"/>
-    <hyperlink ref="C342" r:id="rId144" xr:uid="{E846D15C-B6B9-4C3D-9DEE-0C6D38A1B104}"/>
-    <hyperlink ref="C368" r:id="rId145" xr:uid="{C159B9BC-C021-4F27-A49F-56A8B6A7BFED}"/>
-    <hyperlink ref="C385" r:id="rId146" xr:uid="{061EE0CD-4E7F-4ACA-9861-EE92BA563DD3}"/>
-    <hyperlink ref="C386" r:id="rId147" xr:uid="{CE99FFE1-C83F-4DA8-B248-BB8F708004C2}"/>
-    <hyperlink ref="C440" r:id="rId148" xr:uid="{58AF09A1-4DA1-4C13-A924-7038BAFF295B}"/>
-    <hyperlink ref="C439" r:id="rId149" xr:uid="{236BF6F5-D6E3-45C6-8B23-68B8D0655F15}"/>
-    <hyperlink ref="C437" r:id="rId150" xr:uid="{E69F8561-4FEC-4C42-8E14-50B2E9393A13}"/>
-    <hyperlink ref="C438" r:id="rId151" xr:uid="{4C6593DF-C1C6-42A1-842C-BE5F55D1C605}"/>
-    <hyperlink ref="C436" r:id="rId152" xr:uid="{516AD057-D9E0-436D-AD29-4C3C49BC1430}"/>
-    <hyperlink ref="C435" r:id="rId153" xr:uid="{7C7C69A3-9F29-4F4D-A44D-6990529D8FAF}"/>
-    <hyperlink ref="C434" r:id="rId154" xr:uid="{91542EDF-6A2E-4075-B7BA-B2F1F8D0A714}"/>
-    <hyperlink ref="C433" r:id="rId155" xr:uid="{CB0F8AB7-B42B-4853-A3B5-088035C1D966}"/>
-    <hyperlink ref="C228" r:id="rId156" xr:uid="{FDB9A05E-682B-4C8D-80B7-C00B35288AE0}"/>
-    <hyperlink ref="C384" r:id="rId157" xr:uid="{8B09D238-BC27-4FFB-9A65-E4DF63A42C1D}"/>
-    <hyperlink ref="C59" r:id="rId158" location="!/admission" xr:uid="{61B8463B-D859-4230-9FF8-1B5393E117F3}"/>
-    <hyperlink ref="C60" r:id="rId159" location="!/mtech_cyber" xr:uid="{B55FEB65-57AD-405E-8A56-2FA984A4A9B0}"/>
-    <hyperlink ref="C61" r:id="rId160" xr:uid="{F278F221-DB82-4A2A-A653-F528F133A217}"/>
-    <hyperlink ref="C62" r:id="rId161" xr:uid="{0DF5AEA7-57A2-4E89-9283-89F20D3AF94D}"/>
-    <hyperlink ref="C431" r:id="rId162" xr:uid="{934D29A8-8919-4C31-8AB6-C15B23F2A0E9}"/>
-    <hyperlink ref="C430" r:id="rId163" xr:uid="{3A901F7E-443D-4533-B3A8-32D563BE970D}"/>
-    <hyperlink ref="C428" r:id="rId164" xr:uid="{5F53F94F-A1DD-478A-992E-B8B23E6434F4}"/>
-    <hyperlink ref="C427" r:id="rId165" xr:uid="{3295F066-4FDB-4115-9B6A-BF8DF52B2D4F}"/>
-    <hyperlink ref="C426" r:id="rId166" xr:uid="{C3B52501-E6F1-4E5A-9414-2A60F3A8BF4C}"/>
-    <hyperlink ref="C425" r:id="rId167" xr:uid="{ABFD91D8-D01D-459E-B4E0-59B864E00056}"/>
-    <hyperlink ref="C424" r:id="rId168" xr:uid="{0529A5F1-3179-4D02-8652-30F9A46D33DD}"/>
-    <hyperlink ref="C423" r:id="rId169" xr:uid="{3A72B964-7DA8-4F2E-94CF-E6E47D26B07C}"/>
-    <hyperlink ref="C422" r:id="rId170" xr:uid="{0F21AB0F-7276-40FC-8DAC-13265F890365}"/>
-    <hyperlink ref="C421" r:id="rId171" xr:uid="{E8578DFD-6ED9-4928-A1E5-DA3E7E6F68E1}"/>
-    <hyperlink ref="C420" r:id="rId172" xr:uid="{DF332798-21C9-4E8B-B57B-B6065E3D7DBD}"/>
-    <hyperlink ref="C419" r:id="rId173" xr:uid="{8E709FB1-3B19-4143-9110-724B80D71CD5}"/>
-    <hyperlink ref="C418" r:id="rId174" xr:uid="{CC5498BB-5E6F-403B-9D7F-4B5DD6C55F15}"/>
-    <hyperlink ref="C417" r:id="rId175" xr:uid="{57AF8459-4E89-47B0-B109-1902EB74EF2E}"/>
-    <hyperlink ref="C416" r:id="rId176" xr:uid="{870A97EE-A952-4484-8DB7-39D344D5DBC1}"/>
-    <hyperlink ref="C405" r:id="rId177" xr:uid="{38DF5807-6CF4-4F71-938E-536834854BFC}"/>
-    <hyperlink ref="C407" r:id="rId178" xr:uid="{70870616-497E-4084-B506-707215E9CE0A}"/>
-    <hyperlink ref="C406" r:id="rId179" xr:uid="{4DE6439C-F439-443A-BB85-E7246A24CC8C}"/>
-    <hyperlink ref="C408" r:id="rId180" xr:uid="{F1D3A36D-1474-41C0-8AD5-D6A33A52F519}"/>
-    <hyperlink ref="C409" r:id="rId181" xr:uid="{FFE2DBCB-1CCC-4940-BCAC-505A097C6ACA}"/>
-    <hyperlink ref="C411" r:id="rId182" xr:uid="{9DD54BD2-B079-4E90-A72D-103383F2F20E}"/>
-    <hyperlink ref="C410" r:id="rId183" xr:uid="{24D497AA-AF1E-486A-8878-BD99E4F3F3E4}"/>
-    <hyperlink ref="C412" r:id="rId184" xr:uid="{7D208A04-2A48-449D-9453-661B7BD8EA56}"/>
-    <hyperlink ref="C413" r:id="rId185" xr:uid="{16A944FF-67D5-4B20-A323-FE46D5E2AE88}"/>
-    <hyperlink ref="C414" r:id="rId186" xr:uid="{E17D51B2-6B89-4974-8E6A-D2079806A523}"/>
-    <hyperlink ref="C415" r:id="rId187" xr:uid="{ACB0A0C3-40A8-4A8D-9E1A-ED7AB3025BA2}"/>
-    <hyperlink ref="C280" r:id="rId188" xr:uid="{CA05E1D2-B622-49FA-B37E-10F9644FD81F}"/>
-    <hyperlink ref="C63" r:id="rId189" xr:uid="{00D49E34-09B7-4A9E-973C-31610ABB8154}"/>
-    <hyperlink ref="C64" r:id="rId190" xr:uid="{BF168807-AA0C-4040-8B55-A33C673C58D1}"/>
-    <hyperlink ref="C65" r:id="rId191" xr:uid="{42A01053-45C6-4C93-8CDC-640176507BA8}"/>
-    <hyperlink ref="C66" r:id="rId192" xr:uid="{16F0E7D0-33D8-4F6C-B2E1-55A5C1EF0BA0}"/>
-    <hyperlink ref="C67" r:id="rId193" xr:uid="{FAC80AD1-D0E1-49C5-8B4C-A85BAF8AB259}"/>
-    <hyperlink ref="C68" r:id="rId194" xr:uid="{7AE725A3-C413-4112-B74C-3B61A4C51726}"/>
-    <hyperlink ref="C69" r:id="rId195" xr:uid="{9B200477-E6FA-4964-8910-235734D4D88D}"/>
-    <hyperlink ref="C70" r:id="rId196" xr:uid="{F40500AC-8A80-4F18-85DA-4CAD2FC6AD98}"/>
-    <hyperlink ref="C71" r:id="rId197" xr:uid="{8138436D-4A9C-4406-9464-7EF994C91067}"/>
-    <hyperlink ref="C72" r:id="rId198" xr:uid="{D2BA7CF4-D077-40D7-83E8-E25BB8C4BFC8}"/>
-    <hyperlink ref="C73" r:id="rId199" xr:uid="{9B5A9BEF-F202-4CB7-80D5-801876E4D999}"/>
-    <hyperlink ref="C75" r:id="rId200" xr:uid="{B520082F-5A8C-42E4-B8A0-85A54CA0490F}"/>
-    <hyperlink ref="C76" r:id="rId201" xr:uid="{414BE7E8-4C7C-46E1-86EA-CA5BE61BD3BB}"/>
-    <hyperlink ref="C77" r:id="rId202" xr:uid="{220CEA6A-6CFE-4E9D-8149-755E9C622E49}"/>
-    <hyperlink ref="C78" r:id="rId203" xr:uid="{E00F5BD2-4966-435C-A636-0040FD4AE6EC}"/>
-    <hyperlink ref="C79" r:id="rId204" xr:uid="{8B50ECF6-203A-472A-B3B1-68D4365008FD}"/>
-    <hyperlink ref="C81" r:id="rId205" xr:uid="{89B41390-21AA-41E7-AFAE-384E689F93B8}"/>
-    <hyperlink ref="C82" r:id="rId206" xr:uid="{84869D7A-67E7-4CED-86CA-5444BCBC5F6F}"/>
-    <hyperlink ref="C93" r:id="rId207" xr:uid="{7FB09E3F-E7AF-4F62-8BB6-E2979CEB3C51}"/>
-    <hyperlink ref="C94" r:id="rId208" xr:uid="{61CB8AE9-5D0F-4FCA-B851-93B682722A4C}"/>
-    <hyperlink ref="C95" r:id="rId209" xr:uid="{2D80F475-6FC9-4172-845F-BAAFA138E4A0}"/>
-    <hyperlink ref="C96" r:id="rId210" xr:uid="{D51EC73D-CB09-4A74-A3C2-F06D27CFD5AB}"/>
-    <hyperlink ref="C97" r:id="rId211" xr:uid="{7C7D2F14-0EA3-445D-BEAD-8F7CCEC0E375}"/>
-    <hyperlink ref="C98" r:id="rId212" xr:uid="{E180A90F-81F5-4738-B2AA-7672ABEE4F37}"/>
-    <hyperlink ref="C99" r:id="rId213" xr:uid="{4ECA026B-0747-44CB-9D31-474E1A82D397}"/>
-    <hyperlink ref="C100" r:id="rId214" xr:uid="{48D08408-BB76-4331-B95E-B1F5E44AECB3}"/>
-    <hyperlink ref="C101" r:id="rId215" xr:uid="{62C42544-F088-440A-ACEC-B663575744EC}"/>
-    <hyperlink ref="C192" r:id="rId216" xr:uid="{FD8F3FF6-B6D3-470D-A2B1-F17BE6071352}"/>
-    <hyperlink ref="C193:C201" r:id="rId217" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{C58B0A20-C20C-47C7-880A-56B75CCD0AA4}"/>
-    <hyperlink ref="C202" r:id="rId218" xr:uid="{70518E27-1FB3-4922-A9A0-6F0B82901DC3}"/>
-    <hyperlink ref="C203" r:id="rId219" xr:uid="{5178E260-CD9F-4988-BC34-CA9577046958}"/>
-    <hyperlink ref="C128" r:id="rId220" xr:uid="{E87D8A80-F6BC-452B-B97C-CAF8F9A3BB5A}"/>
-    <hyperlink ref="C129:C131" r:id="rId221" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{08C8A54B-58B2-4F53-888C-E421AACE9D9A}"/>
-    <hyperlink ref="C186" r:id="rId222" xr:uid="{DDF05934-8C66-408F-A3FE-7356C1AFB789}"/>
-    <hyperlink ref="C188" r:id="rId223" xr:uid="{EA2271AC-EFC5-4265-B6EB-546C89D8F321}"/>
-    <hyperlink ref="C247" r:id="rId224" xr:uid="{4EC4FF74-1934-49F8-A1CA-7BBABB016C70}"/>
-    <hyperlink ref="C248:C250" r:id="rId225" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{2E883870-4C94-41D5-9745-3E512B680395}"/>
-    <hyperlink ref="C251" r:id="rId226" xr:uid="{C679360F-EDEF-4CF9-AD5D-DDB5C453EFA3}"/>
-    <hyperlink ref="C252" r:id="rId227" xr:uid="{31073172-6E59-40A0-B301-1C3E80E80C79}"/>
-    <hyperlink ref="C253" r:id="rId228" xr:uid="{D91C0790-63C8-4D7E-B375-838D54599BB5}"/>
-    <hyperlink ref="C254" r:id="rId229" xr:uid="{3BE4031E-904D-479C-B94F-FA21E9BB6C9B}"/>
-    <hyperlink ref="C255" r:id="rId230" xr:uid="{D9320C11-CF38-4DC5-A972-4CE40F2702A0}"/>
-    <hyperlink ref="C279" r:id="rId231" xr:uid="{E022713A-1ABD-4553-8D41-38E0D2117BC0}"/>
-    <hyperlink ref="C278" r:id="rId232" xr:uid="{A603A503-83F2-413F-8441-AB78EB17DA72}"/>
-    <hyperlink ref="C187" r:id="rId233" xr:uid="{1D565744-D70E-4E1A-B939-DEA40AFCBDFA}"/>
-    <hyperlink ref="C273" r:id="rId234" xr:uid="{9FAFA356-00F7-458E-8170-CCFBA7A8CAF9}"/>
-    <hyperlink ref="C274" r:id="rId235" xr:uid="{91F50700-E6E1-405D-884D-003BAD84CF6E}"/>
-    <hyperlink ref="C275" r:id="rId236" xr:uid="{AA3DA20E-FE16-41F6-8ED7-8F5678E81426}"/>
-    <hyperlink ref="C276" r:id="rId237" xr:uid="{8CE261A8-CA95-4381-8F7A-BA7947013160}"/>
-    <hyperlink ref="C277" r:id="rId238" xr:uid="{6A25D613-5662-4B27-AE60-55FA6309D7A7}"/>
-    <hyperlink ref="C160" r:id="rId239" xr:uid="{7D8A021C-BEFB-46B6-9465-17F517B264FA}"/>
-    <hyperlink ref="C163" r:id="rId240" xr:uid="{754497C5-B35D-4D8D-A73D-D6C04230A65D}"/>
-    <hyperlink ref="C164:C165" r:id="rId241" display="https://www.sanskriti.edu.in/admissions/eligibilty-and-fee-structure.php" xr:uid="{67EC2355-EEEA-4588-9FB9-030B9D46FA56}"/>
-    <hyperlink ref="C166" r:id="rId242" xr:uid="{B906D7DB-4CBB-4051-98B6-D84969E49A3D}"/>
-    <hyperlink ref="C167" r:id="rId243" xr:uid="{D0A25218-E720-4813-94C7-A3AFFC06EE5D}"/>
-    <hyperlink ref="C168" r:id="rId244" xr:uid="{0DB740AE-A804-4189-975E-34555E589CE0}"/>
-    <hyperlink ref="C169" r:id="rId245" xr:uid="{1AAB6151-0D15-4AE9-8D34-BB1459CEAB33}"/>
-    <hyperlink ref="C191" r:id="rId246" xr:uid="{6223C244-02A7-4FC0-A825-B1CEDF933567}"/>
-    <hyperlink ref="C190" r:id="rId247" xr:uid="{E370FD19-9FFA-428C-9F77-5E3E9C2842B9}"/>
-    <hyperlink ref="C189" r:id="rId248" xr:uid="{A742A948-3925-4118-801D-7A89FC650F19}"/>
-    <hyperlink ref="C102" r:id="rId249" xr:uid="{5F65C71C-DEA5-425C-828B-57EF9A6B6746}"/>
-    <hyperlink ref="C103" r:id="rId250" xr:uid="{61A7FFCA-C177-4280-90B0-9C2F3B852BDC}"/>
-    <hyperlink ref="C104" r:id="rId251" xr:uid="{82202B66-784F-4D9C-BA61-A5D395291FB1}"/>
-    <hyperlink ref="C105" r:id="rId252" xr:uid="{D1FC4980-AA57-4887-AB9A-91CE4936A97C}"/>
-    <hyperlink ref="C106" r:id="rId253" xr:uid="{D1D99F66-E8E7-4092-AD14-AF5347154355}"/>
-    <hyperlink ref="C107:C108" r:id="rId254" display="https://www.krmangalam.edu.in/fee-structure" xr:uid="{041D9F7C-0B8D-4204-BDD2-41566D9CDABA}"/>
-    <hyperlink ref="C109" r:id="rId255" xr:uid="{B1DA8F4A-A9BF-430C-ADCD-1467BD21089F}"/>
-    <hyperlink ref="C110" r:id="rId256" xr:uid="{8B00BAAF-6A4E-4F37-AB70-9E5584E5E0AD}"/>
-    <hyperlink ref="C112" r:id="rId257" xr:uid="{DCC6876A-46B3-4475-8D11-D32285D0066B}"/>
-    <hyperlink ref="C121" r:id="rId258" xr:uid="{87F7A942-4D6F-40DB-975B-6D93C1BA428C}"/>
-    <hyperlink ref="C122" r:id="rId259" xr:uid="{DE0490D6-496F-4F6C-8BA9-CD46CF5C9F77}"/>
-    <hyperlink ref="C272" r:id="rId260" xr:uid="{6CE3AFEA-E1D9-489B-8C5D-201EAF186C38}"/>
-    <hyperlink ref="C271" r:id="rId261" xr:uid="{934B4DFF-33A3-4EA4-AC1F-597C69761C0B}"/>
-    <hyperlink ref="C270" r:id="rId262" xr:uid="{E669D885-E739-4BD6-869A-D12708B4E845}"/>
-    <hyperlink ref="C269" r:id="rId263" xr:uid="{833A5F42-00A6-4864-AB2A-502D00F0178F}"/>
-    <hyperlink ref="C268" r:id="rId264" xr:uid="{C9A75FFF-6031-4BF4-A2EF-2B74612FC588}"/>
-    <hyperlink ref="C267" r:id="rId265" xr:uid="{910B5DBB-5CBF-4A25-B2C8-C34AFAD9A15B}"/>
-    <hyperlink ref="C266" r:id="rId266" xr:uid="{E7BB6CD5-434F-4DAD-B7B2-FEF59F5BDF6A}"/>
-    <hyperlink ref="C265" r:id="rId267" xr:uid="{AA4C275D-D058-4FE8-8B2B-D7966333612E}"/>
-    <hyperlink ref="C264" r:id="rId268" xr:uid="{2A007E23-5293-4B95-B807-97D238EB1028}"/>
-    <hyperlink ref="C263" r:id="rId269" xr:uid="{781268BD-6ECD-48F8-B948-CA1763EB88B5}"/>
-    <hyperlink ref="C262" r:id="rId270" xr:uid="{A014BCDF-8751-44F9-8255-EC6EF94F02EB}"/>
-    <hyperlink ref="C261" r:id="rId271" xr:uid="{32BE2A73-3831-4F9F-9188-82D7241CC633}"/>
-    <hyperlink ref="C260" r:id="rId272" xr:uid="{28931F66-6D1F-450B-BA78-6079CD437337}"/>
-    <hyperlink ref="C259" r:id="rId273" xr:uid="{03A1A604-E522-4B2E-9129-2DBCC086E524}"/>
-    <hyperlink ref="C258" r:id="rId274" xr:uid="{11CC5024-0FAC-43F9-A277-A0FABE39A171}"/>
-    <hyperlink ref="C257" r:id="rId275" xr:uid="{00EED605-FD52-4668-B4C9-3AE6A0380213}"/>
-    <hyperlink ref="C256" r:id="rId276" xr:uid="{B73E7671-B06F-48B7-A489-DF42F8206025}"/>
-    <hyperlink ref="C210" r:id="rId277" xr:uid="{884A2211-4FF0-40E0-9D41-63827D4F9E33}"/>
-    <hyperlink ref="C205:C209" r:id="rId278" display="https://www.niilmuniversity.ac.in/page/domestic-fee" xr:uid="{4D0998A5-ADE4-474F-8919-F9D9E65445C7}"/>
-    <hyperlink ref="C204" r:id="rId279" xr:uid="{92AB9E3A-3740-4E42-8C5E-3AE1F91C4248}"/>
-    <hyperlink ref="C244" r:id="rId280" xr:uid="{F7A24EF7-FFF2-4EB9-A23D-278B2F25FF71}"/>
-    <hyperlink ref="C245" r:id="rId281" xr:uid="{0E76EC08-B404-4A3B-895C-55A24BA3DE07}"/>
-    <hyperlink ref="C246" r:id="rId282" xr:uid="{A5E36846-E219-462A-8019-2BD0A5912A91}"/>
-    <hyperlink ref="C243" r:id="rId283" xr:uid="{D1E84938-1080-4D26-8E66-44242951B470}"/>
-    <hyperlink ref="C242" r:id="rId284" xr:uid="{C396EDF0-1A95-4843-B018-7A004FCC0CA1}"/>
-    <hyperlink ref="C241" r:id="rId285" xr:uid="{BBC3A9F2-24DD-409F-A293-A40816186309}"/>
-    <hyperlink ref="C240" r:id="rId286" xr:uid="{861A8984-FC97-432D-AEDB-6C6F0C28849E}"/>
-    <hyperlink ref="C239" r:id="rId287" xr:uid="{73E8FC8B-D981-4D40-B451-08A903237BF6}"/>
-    <hyperlink ref="C238" r:id="rId288" xr:uid="{93144211-564D-4012-87FD-FADD1C7BB886}"/>
-    <hyperlink ref="C237" r:id="rId289" xr:uid="{752B0DA3-974C-4265-B2E3-745AAC530D50}"/>
-    <hyperlink ref="C236" r:id="rId290" xr:uid="{D9A762DF-9474-4708-B4FC-576A5BF5417B}"/>
-    <hyperlink ref="C234" r:id="rId291" xr:uid="{74443DD3-85E5-4D8D-AF47-025F0237936A}"/>
-    <hyperlink ref="C235" r:id="rId292" xr:uid="{26C6D44F-AD06-404E-A439-BAB869152981}"/>
-    <hyperlink ref="C232:C233" r:id="rId293" display="https://drive.google.com/file/d/1-XYvZlg7yblN8siHvowA7MDqYvaVwxmT/view?usp=drive_link" xr:uid="{9CB5D6BA-45EF-435D-AA05-5D8D0F634A29}"/>
-    <hyperlink ref="C231" r:id="rId294" xr:uid="{7243E531-903C-4938-9F91-52535DE094A3}"/>
-    <hyperlink ref="C230" r:id="rId295" xr:uid="{9BB80BA5-E208-48F8-9305-2C19B3F4AE50}"/>
-    <hyperlink ref="C229" r:id="rId296" xr:uid="{EE33DEC9-C7FD-45DD-8172-DB3C92F205DD}"/>
-    <hyperlink ref="C170" r:id="rId297" xr:uid="{E609FE68-8129-4F76-A406-C616F4475FFF}"/>
-    <hyperlink ref="C171" r:id="rId298" xr:uid="{8C71D231-DEFC-41D2-B20C-A2B68ED1AF50}"/>
-    <hyperlink ref="C172" r:id="rId299" xr:uid="{D9227C42-5CFB-4E22-88F0-D1DA08A5B641}"/>
-    <hyperlink ref="C173" r:id="rId300" xr:uid="{C4E9765D-AD6D-45C0-82FD-C48F5D2DFF7A}"/>
-    <hyperlink ref="C174" r:id="rId301" xr:uid="{63279210-5C8F-48D9-8A96-4F2EEB965471}"/>
-    <hyperlink ref="C175" r:id="rId302" xr:uid="{17552510-4E38-4F27-BABB-EF7117617DA1}"/>
-    <hyperlink ref="C176" r:id="rId303" xr:uid="{1FF3E28B-483B-4301-948F-210FDA7A328F}"/>
-    <hyperlink ref="C177" r:id="rId304" xr:uid="{2B3BB96A-22A5-4DF3-819F-AC6C2F83D70D}"/>
-    <hyperlink ref="C178" r:id="rId305" xr:uid="{27396A5C-ABAF-4AC4-8BFC-DE96363F1329}"/>
-    <hyperlink ref="C179" r:id="rId306" xr:uid="{A0D9E9FE-9B75-45B4-8C98-2E918DA04801}"/>
-    <hyperlink ref="C180" r:id="rId307" xr:uid="{BA9D60C8-3A62-4FBF-AC68-30BCE66C3054}"/>
-    <hyperlink ref="C181" r:id="rId308" xr:uid="{94371691-82FF-4BC1-8C40-6060D10DEA93}"/>
-    <hyperlink ref="C182" r:id="rId309" xr:uid="{F161FF5D-D939-4ECD-A684-367B9D4E8F3B}"/>
-    <hyperlink ref="C183" r:id="rId310" xr:uid="{A87C3849-3A96-4E64-B06B-0FA36A4D1A50}"/>
-    <hyperlink ref="C227" r:id="rId311" xr:uid="{69A6E3B4-B9BE-406B-9449-B6F1C52859BD}"/>
-    <hyperlink ref="C226" r:id="rId312" xr:uid="{A65F5E63-F864-497D-B4E2-8D7B991B7A9F}"/>
-    <hyperlink ref="C225" r:id="rId313" xr:uid="{9E0A3F3E-F295-4D05-9358-31E7E3F975B0}"/>
-    <hyperlink ref="C123" r:id="rId314" xr:uid="{025751A2-5E7B-4B2C-94BC-0695460BE8FA}"/>
-    <hyperlink ref="C124" r:id="rId315" xr:uid="{333AB1E1-ED40-4E48-BB49-34418ED912F7}"/>
-    <hyperlink ref="C217" r:id="rId316" xr:uid="{FBB97787-2F14-4BB2-917B-775C371C9762}"/>
-    <hyperlink ref="C184" r:id="rId317" xr:uid="{5DCA712E-B5BD-450D-B0B7-2BE98A50C5B4}"/>
-    <hyperlink ref="C132" r:id="rId318" xr:uid="{957E3857-240F-405B-8368-4641DF8EC154}"/>
-    <hyperlink ref="C133" r:id="rId319" xr:uid="{B4D4928E-7C0F-45C4-8CE2-873EC0C89A81}"/>
-    <hyperlink ref="C134" r:id="rId320" xr:uid="{4061BF43-FC11-4722-A43E-C366B88F19F1}"/>
-    <hyperlink ref="C136" r:id="rId321" xr:uid="{34F9BF4C-6418-4046-A21C-92FE36275EF2}"/>
-    <hyperlink ref="C137" r:id="rId322" xr:uid="{F2578955-7E22-4475-80C7-A39349E8FEA6}"/>
-    <hyperlink ref="C224" r:id="rId323" xr:uid="{86DA7070-85E7-462C-92FB-83548FC9FDEF}"/>
-    <hyperlink ref="C223" r:id="rId324" xr:uid="{4239EE1C-E740-4EF1-B3C2-2930AFF4ED33}"/>
-    <hyperlink ref="C222" r:id="rId325" xr:uid="{8113E903-7AE6-499F-826D-AA5E1D82404A}"/>
-    <hyperlink ref="C221" r:id="rId326" xr:uid="{19C2FEE2-A4BD-4801-8A7E-E5A2B4BB7DF9}"/>
-    <hyperlink ref="C220" r:id="rId327" xr:uid="{7F873713-D8E7-4368-8D89-D4EA6A780A4D}"/>
-    <hyperlink ref="C219" r:id="rId328" xr:uid="{257A14A4-3665-4E91-A3DF-75AF79A04428}"/>
-    <hyperlink ref="C218" r:id="rId329" xr:uid="{17DE8754-080F-42A0-8008-3B22FE424381}"/>
-    <hyperlink ref="C216" r:id="rId330" xr:uid="{C7A26D3E-6B13-4390-A3B8-076C93AC8280}"/>
-    <hyperlink ref="C215" r:id="rId331" xr:uid="{3CC019A7-5595-4626-B258-2152CBAEF85E}"/>
-    <hyperlink ref="C214" r:id="rId332" xr:uid="{37E486E4-616E-40B3-B0C1-F3FF6CC33F97}"/>
-    <hyperlink ref="C213" r:id="rId333" xr:uid="{5CE33C60-403A-4391-A6ED-75181F17DB38}"/>
-    <hyperlink ref="C212" r:id="rId334" xr:uid="{88A01FF5-9960-46AC-B62A-D63A692F81EC}"/>
-    <hyperlink ref="C211" r:id="rId335" xr:uid="{375182E1-BF7E-4D5B-AEB9-B21138D96106}"/>
-    <hyperlink ref="C485" r:id="rId336" xr:uid="{0D700A3B-31B6-49B0-9A4C-8800BD838F55}"/>
-    <hyperlink ref="C487" r:id="rId337" xr:uid="{37D6CE14-05F0-4575-90CA-1961380A3B0A}"/>
-    <hyperlink ref="C488" r:id="rId338" xr:uid="{BD7ED2EB-D561-4548-9ECD-9D18B410E687}"/>
-    <hyperlink ref="C489" r:id="rId339" xr:uid="{822813F8-60EB-439F-8E3A-F86768DEB37B}"/>
-    <hyperlink ref="C490" r:id="rId340" xr:uid="{958FA13C-EEE0-4F80-9135-81CA5B1A0295}"/>
-    <hyperlink ref="C491" r:id="rId341" xr:uid="{4D572C2A-6FDB-4913-A3E0-517056D63DA7}"/>
-    <hyperlink ref="C492" r:id="rId342" xr:uid="{71657101-3C84-4944-9D2E-2C1E23E72A41}"/>
-    <hyperlink ref="C493" r:id="rId343" xr:uid="{62611662-48DB-4599-BABF-444498618EB1}"/>
-    <hyperlink ref="C494" r:id="rId344" xr:uid="{821D9F99-F1A5-4C60-A0B8-EC5B800A5572}"/>
-    <hyperlink ref="C495" r:id="rId345" xr:uid="{84BED024-EB1B-4425-A1CA-922374ACF188}"/>
-    <hyperlink ref="C616" r:id="rId346" xr:uid="{0EFC7DC7-72F6-4B29-89C8-67F10DEE9A54}"/>
-    <hyperlink ref="C618" r:id="rId347" xr:uid="{85605A6A-6936-4352-A4E0-080226705436}"/>
-    <hyperlink ref="C617" r:id="rId348" xr:uid="{A33CC4D9-2118-40F3-8797-04D5E7CA31C3}"/>
-    <hyperlink ref="C619" r:id="rId349" xr:uid="{496B62F6-A429-4833-9B25-45FF193F1B69}"/>
-    <hyperlink ref="C620" r:id="rId350" xr:uid="{23B0E2BF-C57E-41BE-AE89-729361F9D101}"/>
-    <hyperlink ref="C621" r:id="rId351" xr:uid="{FD5F0098-93F2-4746-BA83-9394F7706198}"/>
-    <hyperlink ref="C622" r:id="rId352" xr:uid="{ABF20253-94C6-4105-8060-5DD8ACBCF3ED}"/>
-    <hyperlink ref="C623" r:id="rId353" xr:uid="{5AAD0D59-1AE3-4A27-8D5A-A8782A47BEFF}"/>
-    <hyperlink ref="C624" r:id="rId354" xr:uid="{4A1CAE48-1E67-4FE0-8974-A0FBC3D89A15}"/>
-    <hyperlink ref="C626" r:id="rId355" xr:uid="{DFDA7392-9030-46C1-8E32-782EE28524DC}"/>
-    <hyperlink ref="C625" r:id="rId356" xr:uid="{B9060AA0-D62C-46CB-B594-315F3EECD8D4}"/>
-    <hyperlink ref="C628" r:id="rId357" xr:uid="{BAC0E18A-DF61-4CAF-AC82-B4EB7B8C8F3C}"/>
-    <hyperlink ref="C627" r:id="rId358" xr:uid="{3A75497B-A717-4B4D-BECB-0FFB8BC79629}"/>
-    <hyperlink ref="C629" r:id="rId359" xr:uid="{E1B1465D-C375-4CA0-B346-4058CD793DF6}"/>
-    <hyperlink ref="C630" r:id="rId360" xr:uid="{AD92CF36-346E-4A37-B661-80DF86D590EF}"/>
-    <hyperlink ref="C631" r:id="rId361" xr:uid="{FB2F82BC-70B9-4149-8269-BB52AFCF9AE2}"/>
-    <hyperlink ref="C632" r:id="rId362" xr:uid="{B6022C23-98EB-4D0F-9B5C-A29C3BF69B04}"/>
-    <hyperlink ref="C633" r:id="rId363" xr:uid="{D0FB1C11-C3F6-4ED3-9465-C7F546387C21}"/>
-    <hyperlink ref="C634" r:id="rId364" xr:uid="{BDEF1248-1B6C-4C2E-99F0-BB23AC10FAE7}"/>
-    <hyperlink ref="C635" r:id="rId365" xr:uid="{C012353D-A7C1-4C9F-9034-CAAF98034D25}"/>
-    <hyperlink ref="C636" r:id="rId366" xr:uid="{79189C6E-4C69-4F02-A218-69A8C0803FD5}"/>
-    <hyperlink ref="C637" r:id="rId367" xr:uid="{BD278F26-DE2D-4294-9F54-E705BD0E01F4}"/>
-    <hyperlink ref="C638" r:id="rId368" xr:uid="{3A3CF422-DB40-4AC2-A775-FE585834DEA3}"/>
-    <hyperlink ref="C639" r:id="rId369" xr:uid="{4C73EEAB-646D-4568-B4A0-A11CC0BC7713}"/>
-    <hyperlink ref="C640" r:id="rId370" xr:uid="{6B84AD41-BC2D-4783-B320-4B30D9E8E8FA}"/>
-    <hyperlink ref="C641" r:id="rId371" xr:uid="{99E79A20-8220-4969-B2B1-D8FBFBB512DC}"/>
-    <hyperlink ref="C642" r:id="rId372" xr:uid="{C149BBA6-109D-4CAF-9D2F-22FD82A6B132}"/>
-    <hyperlink ref="C643" r:id="rId373" xr:uid="{C731F0B6-7F48-4318-8635-EBF35CBF46BD}"/>
-    <hyperlink ref="C644" r:id="rId374" xr:uid="{198C72BF-1766-4C20-963F-266D3042F81A}"/>
-    <hyperlink ref="C645" r:id="rId375" xr:uid="{A061E847-AE51-475E-AD17-C671B390B5B3}"/>
-    <hyperlink ref="C646" r:id="rId376" xr:uid="{CE07D610-59B2-4041-B18D-AD4AE9A4670A}"/>
-    <hyperlink ref="C647" r:id="rId377" xr:uid="{80A033D7-4C74-484D-A0B0-F34217F5C104}"/>
-    <hyperlink ref="C648" r:id="rId378" xr:uid="{0D21866E-AF2B-43E3-B333-42B18F1445F4}"/>
-    <hyperlink ref="C649" r:id="rId379" xr:uid="{F0416CDE-3D0C-480A-BE65-7201D4D12F82}"/>
-    <hyperlink ref="C650" r:id="rId380" xr:uid="{DCA6828D-43E2-43A8-B09D-F5C390B6E180}"/>
-    <hyperlink ref="C651" r:id="rId381" xr:uid="{E26BC46D-70D9-41D6-8DAA-0B375579437D}"/>
-    <hyperlink ref="C652" r:id="rId382" xr:uid="{287A5501-C096-4A06-A6B6-CD41C2FEE1F9}"/>
-    <hyperlink ref="C653" r:id="rId383" xr:uid="{BDBB7C64-2A5A-44B0-81A4-98071DA1B340}"/>
-    <hyperlink ref="C654" r:id="rId384" xr:uid="{D531282E-505B-4400-ADCA-1AB93A945183}"/>
-    <hyperlink ref="C655" r:id="rId385" xr:uid="{FA80F1FC-48E4-4917-AA8F-D9C36A18E7C1}"/>
-    <hyperlink ref="C656" r:id="rId386" xr:uid="{386BBE77-3464-47B3-9372-C585691F46B0}"/>
-    <hyperlink ref="C657" r:id="rId387" xr:uid="{AB473EB1-D825-4DDF-8E1A-4CA160AE68EE}"/>
-    <hyperlink ref="C658" r:id="rId388" xr:uid="{80CD06A1-FB90-4B6B-86FF-D0A47E7D0BA6}"/>
-    <hyperlink ref="C659" r:id="rId389" xr:uid="{14B7A1AD-A6A0-4F1F-A1DC-385B65B72767}"/>
-    <hyperlink ref="C660" r:id="rId390" xr:uid="{998A36D4-03A0-4C6C-8131-1AE94A96617B}"/>
-    <hyperlink ref="C661" r:id="rId391" xr:uid="{40D5F952-36AE-4165-B326-2487A88030F1}"/>
-    <hyperlink ref="C662" r:id="rId392" xr:uid="{09144B8E-7793-47BE-AD91-466849211AD9}"/>
-    <hyperlink ref="C663" r:id="rId393" xr:uid="{00D2F3EE-0EDB-4583-982F-7920B3E07F3D}"/>
-    <hyperlink ref="C664" r:id="rId394" xr:uid="{C3271A95-F2E6-4826-9884-9B95E04A8A93}"/>
-    <hyperlink ref="C665" r:id="rId395" xr:uid="{F57EE512-19F2-4AFE-9F73-10B11F7F1034}"/>
-    <hyperlink ref="C666" r:id="rId396" xr:uid="{A3E2614C-92D9-45E7-BD75-D9A81CB35C8B}"/>
-    <hyperlink ref="C667" r:id="rId397" xr:uid="{BFA1A328-EAFC-4A59-975D-1F4916645A21}"/>
-    <hyperlink ref="C668" r:id="rId398" xr:uid="{5B92D9F8-244C-4016-929F-BB7644514E62}"/>
-    <hyperlink ref="C669" r:id="rId399" xr:uid="{9C5475AE-2251-4061-8B47-A905C1B49030}"/>
-    <hyperlink ref="C670" r:id="rId400" xr:uid="{5815F2F9-997D-4B2A-A8FC-CB735FEE4830}"/>
-    <hyperlink ref="C671" r:id="rId401" xr:uid="{E2DC4F07-1866-4752-923A-B3F471F1A220}"/>
-    <hyperlink ref="C672" r:id="rId402" location="costs" xr:uid="{49AA71EC-190B-4115-BCFF-CFFAD2984979}"/>
-    <hyperlink ref="C673" r:id="rId403" xr:uid="{272B1A72-18FD-46D5-BC64-22AB89BE362D}"/>
-    <hyperlink ref="C674" r:id="rId404" xr:uid="{741CEB76-A7BA-4773-9A62-89EFC6D4E6CF}"/>
-    <hyperlink ref="C675" r:id="rId405" xr:uid="{1007ADA1-4291-470A-9A52-5A3DC9278117}"/>
-    <hyperlink ref="C676" r:id="rId406" xr:uid="{73F9F876-2ACC-40CF-A0E8-288E9B4311A9}"/>
-    <hyperlink ref="C677" r:id="rId407" xr:uid="{3395B036-CCBA-4783-99DA-8435E02A25E6}"/>
-    <hyperlink ref="C678" r:id="rId408" xr:uid="{8022E184-A012-460F-9EFB-764A47B0692C}"/>
-    <hyperlink ref="C679" r:id="rId409" xr:uid="{B141A840-39F3-4D59-A96C-795FA224B5D1}"/>
-    <hyperlink ref="C680" r:id="rId410" xr:uid="{074EC546-A68C-4A62-9C9D-2E0B05E2ADF5}"/>
-    <hyperlink ref="C681" r:id="rId411" xr:uid="{B99D8076-D718-4573-B81C-EC0D11D4459E}"/>
-    <hyperlink ref="C682" r:id="rId412" xr:uid="{06E87414-821D-4C0F-9D21-329503A51BDD}"/>
-    <hyperlink ref="C683" r:id="rId413" xr:uid="{1B54B4A3-52EE-4E72-A4ED-5EB4433F548F}"/>
-    <hyperlink ref="C684" r:id="rId414" xr:uid="{3AB6E156-29F8-48A0-95D1-737838B26C8A}"/>
-    <hyperlink ref="C685" r:id="rId415" xr:uid="{1BAFC71F-F029-4EE4-A8FE-06BC7BF24C1C}"/>
-    <hyperlink ref="C686" r:id="rId416" xr:uid="{5F2B17CB-999A-49E4-9746-1988BE345B17}"/>
-    <hyperlink ref="C687" r:id="rId417" xr:uid="{46970D8B-ABF8-4FD0-B1BA-7886430454BF}"/>
-    <hyperlink ref="C688" r:id="rId418" xr:uid="{E3789310-5C51-45AA-8C38-8A481E35B0F2}"/>
-    <hyperlink ref="C689" r:id="rId419" xr:uid="{75BC526E-2B46-4B67-AA68-02482139533E}"/>
-    <hyperlink ref="C690" r:id="rId420" xr:uid="{AA2C8397-ED3F-49A3-B14D-D4F7ADADD221}"/>
-    <hyperlink ref="C691" r:id="rId421" xr:uid="{9152CA66-3393-4655-BE4B-05C1343B0938}"/>
-    <hyperlink ref="C692" r:id="rId422" xr:uid="{6B7B50F8-364F-4BC9-A5D6-6A381D15C57F}"/>
-    <hyperlink ref="C693:C695" r:id="rId423" display="https://aahe.edu.au/fees/" xr:uid="{03793D0C-6ED7-4717-B84A-05D4D94B6B19}"/>
-    <hyperlink ref="C696" r:id="rId424" xr:uid="{80DA8DE6-1E1C-49A2-B7A8-F9BE0CC4377E}"/>
-    <hyperlink ref="C697" r:id="rId425" xr:uid="{E2DFCB04-71CF-4514-9DB7-D3600957043D}"/>
-    <hyperlink ref="C698" r:id="rId426" xr:uid="{32D3427F-E74C-4266-A4CF-90D1088AF8D7}"/>
-    <hyperlink ref="C699" r:id="rId427" xr:uid="{85D020A3-C099-441F-B9BE-27CC597C4427}"/>
-    <hyperlink ref="C615" r:id="rId428" xr:uid="{881AA85A-03E8-43BD-AD9C-986E38129888}"/>
-    <hyperlink ref="C614" r:id="rId429" xr:uid="{95B49150-A566-4A62-9562-78EEA4F04444}"/>
-    <hyperlink ref="C613" r:id="rId430" xr:uid="{DF271968-FF08-4467-8410-9DF2DB5D5417}"/>
-    <hyperlink ref="C612" r:id="rId431" xr:uid="{ABCC119E-64AB-49D8-A93F-AC60C5741214}"/>
-    <hyperlink ref="C700" r:id="rId432" xr:uid="{D2D23298-4669-4260-BB99-338E4AFCB5B5}"/>
-    <hyperlink ref="C611" r:id="rId433" xr:uid="{DC80456E-4C0C-4D3C-9562-9CE0E3CEA735}"/>
-    <hyperlink ref="C610" r:id="rId434" xr:uid="{9D7444EB-5819-4A7C-9CA6-ACEA70D06652}"/>
-    <hyperlink ref="C609" r:id="rId435" xr:uid="{80CB13C0-25F1-482D-9B7F-9FFAFE64A323}"/>
-    <hyperlink ref="C608" r:id="rId436" location="2025-2026-undergraduate-tuition-and-fees" xr:uid="{5EDBF750-7EDA-4C4E-AB95-93B94C4EDD4F}"/>
-    <hyperlink ref="C607" r:id="rId437" xr:uid="{8C499F14-E8E7-4EB0-A1DB-1B8BAAEABE2C}"/>
-    <hyperlink ref="C606" r:id="rId438" xr:uid="{8AB4357A-A73B-4115-BAE3-A1B617B4C8BA}"/>
-    <hyperlink ref="C701" r:id="rId439" xr:uid="{0C1168BC-C6A2-4561-928F-DA6BAF02551F}"/>
-    <hyperlink ref="C605" r:id="rId440" xr:uid="{2598ACD9-91FD-4348-9E6A-8C465D24D830}"/>
-    <hyperlink ref="C604" r:id="rId441" xr:uid="{F382E6ED-3EB0-4D36-B9B7-7989AA09F029}"/>
-    <hyperlink ref="C603" r:id="rId442" xr:uid="{CAFC4424-D243-454D-B0F7-5A1C02751D44}"/>
-    <hyperlink ref="C602" r:id="rId443" xr:uid="{A3D39A32-3CA5-403F-B5CB-C21BA9DA6CF6}"/>
-    <hyperlink ref="C601" r:id="rId444" xr:uid="{4AFC9F05-548F-44E8-90F3-81253EC05543}"/>
-    <hyperlink ref="C600" r:id="rId445" xr:uid="{6891D883-6AA3-4692-924E-157B6C9D0857}"/>
-    <hyperlink ref="C599" r:id="rId446" xr:uid="{B4D01991-686F-48D0-842B-3E97940F10DD}"/>
-    <hyperlink ref="C595" r:id="rId447" xr:uid="{18EB0A22-4CFD-44BE-BB55-917DCEFA9CA6}"/>
-    <hyperlink ref="C594" r:id="rId448" xr:uid="{E6393A6C-F5B7-4509-82A1-5B6665A7C821}"/>
-    <hyperlink ref="C593" r:id="rId449" location="grad-tuition" xr:uid="{582AFF7E-8573-4189-986B-D6E98B1A4DA5}"/>
-    <hyperlink ref="C592" r:id="rId450" location="grad-tuition" xr:uid="{12E2B2B6-E506-417A-B52B-681DFFEE413E}"/>
-    <hyperlink ref="C591" r:id="rId451" location="resident-table" xr:uid="{770C3304-744E-40B0-A99D-2B6E86521C88}"/>
-    <hyperlink ref="C590" r:id="rId452" xr:uid="{3938ED2B-239B-4B09-A824-1CD6F646EB17}"/>
-    <hyperlink ref="C589" r:id="rId453" xr:uid="{5F647715-25EB-4657-8D93-7426C58CB684}"/>
-    <hyperlink ref="C588" r:id="rId454" xr:uid="{10C07F72-DD92-4886-9F7A-5CAF0462B509}"/>
-    <hyperlink ref="C587" r:id="rId455" xr:uid="{5741F3B1-8B60-4B23-ACB2-DA55B686C652}"/>
-    <hyperlink ref="C586" r:id="rId456" xr:uid="{3EFA6110-A11B-457B-8659-72012A54BD3A}"/>
-    <hyperlink ref="C585" r:id="rId457" xr:uid="{80B2DADD-BE3F-4EC7-9C12-3BDAD01813E8}"/>
-    <hyperlink ref="C584" r:id="rId458" xr:uid="{FC1DFD8B-AB65-442C-8A3F-D25996D5D4C0}"/>
-    <hyperlink ref="C583" r:id="rId459" xr:uid="{786B9AB5-33CB-4B37-B2A1-9FA3A61D0DD6}"/>
-    <hyperlink ref="C582" r:id="rId460" xr:uid="{7531FEF1-ECCA-4CD5-91DF-310ADDD8620D}"/>
-    <hyperlink ref="C581" r:id="rId461" xr:uid="{2D4038F2-67F3-48E2-8D1B-4C350C4242A7}"/>
-    <hyperlink ref="C580" r:id="rId462" xr:uid="{8C1E2096-E167-499A-AB57-FAC294ECEDCD}"/>
-    <hyperlink ref="C579" r:id="rId463" xr:uid="{A1C64A08-55EA-4EB5-89B5-0F7F4F342B4E}"/>
-    <hyperlink ref="C578" r:id="rId464" xr:uid="{CB94780F-B641-4597-9CE1-45FFF6AD4B24}"/>
-    <hyperlink ref="C576:C577" r:id="rId465" display="https://engineering.washu.edu/academics/graduate-admissions/tuition-financial-assistance/index.html" xr:uid="{94704AD1-79B0-45E6-9E54-DA16CCCFC1D5}"/>
-    <hyperlink ref="C575" r:id="rId466" xr:uid="{2F7C4AEF-B867-4041-A0A5-E963758EC26E}"/>
-    <hyperlink ref="C574" r:id="rId467" xr:uid="{58CC675F-324C-49CC-8E26-E01400549445}"/>
-    <hyperlink ref="C573" r:id="rId468" xr:uid="{E76C2F8E-D177-4AF5-B631-AE2D0BE2CE97}"/>
-    <hyperlink ref="C572" r:id="rId469" xr:uid="{23695B31-E2B8-4257-8223-E7539FD64A00}"/>
-    <hyperlink ref="C571" r:id="rId470" xr:uid="{6076A241-D906-428A-BAD4-365660712C56}"/>
-    <hyperlink ref="C570" r:id="rId471" xr:uid="{0583E2AF-776E-4CFE-95E6-39AB0ECC45D5}"/>
-    <hyperlink ref="C140" r:id="rId472" xr:uid="{3FA076C9-5495-4945-A4AE-B4C9F3E2D651}"/>
-    <hyperlink ref="C139" r:id="rId473" xr:uid="{51F46025-FA8D-4F49-987B-8B7ACF84D46B}"/>
-    <hyperlink ref="C138" r:id="rId474" xr:uid="{96F590C7-1AE4-4D20-949F-27E943D8E9DD}"/>
-    <hyperlink ref="C141" r:id="rId475" xr:uid="{FBABABEF-6172-480C-B6C6-FFDD1742D1BC}"/>
-    <hyperlink ref="C142" r:id="rId476" xr:uid="{1FD9EFE7-3C5D-4629-AAB4-3BA4E758F297}"/>
-    <hyperlink ref="C145" r:id="rId477" xr:uid="{E34B10FB-C082-4D97-951B-BA7BA04C2BFF}"/>
-    <hyperlink ref="C144" r:id="rId478" xr:uid="{FC90D068-9B74-4B67-8A58-04475F302838}"/>
-    <hyperlink ref="C143" r:id="rId479" xr:uid="{124C2F78-505A-46EC-BCEF-939FE257A92C}"/>
-    <hyperlink ref="C146" r:id="rId480" xr:uid="{2B0BC0FA-A684-4FE8-9ADA-F341D5031D9C}"/>
-    <hyperlink ref="C147" r:id="rId481" xr:uid="{57EA4E59-7D86-4715-AA19-80FD2129EA16}"/>
-    <hyperlink ref="C569" r:id="rId482" xr:uid="{174134F4-7EA9-406B-AC8D-971EFE1F24E3}"/>
-    <hyperlink ref="C568" r:id="rId483" xr:uid="{4CE185F9-CED9-438C-86C9-851D7566A9A7}"/>
-    <hyperlink ref="C567" r:id="rId484" xr:uid="{A20522D3-BFD6-4189-AD43-2A60AD94F7C6}"/>
-    <hyperlink ref="C566" r:id="rId485" xr:uid="{BF8FFE00-58C9-498F-9FB7-53370E4F76E6}"/>
-    <hyperlink ref="C565" r:id="rId486" xr:uid="{BA78BBFE-BA3A-4567-8842-D9DAC7BD4114}"/>
-    <hyperlink ref="C564" r:id="rId487" xr:uid="{AB8D8480-94A0-4F6D-94DD-954187AAF1CA}"/>
-    <hyperlink ref="C563" r:id="rId488" xr:uid="{F485B58C-0963-4817-B71B-E1D073DD028E}"/>
-    <hyperlink ref="C562" r:id="rId489" xr:uid="{CC59DEAF-1EFF-452A-ACA7-DC3FF58078F5}"/>
-    <hyperlink ref="C561" r:id="rId490" xr:uid="{D1F90F1B-7BD7-45D3-820D-8E747A8C92D3}"/>
-    <hyperlink ref="C560" r:id="rId491" xr:uid="{5DBD82ED-050A-43F8-8857-D34C7E4480CF}"/>
-    <hyperlink ref="C559" r:id="rId492" xr:uid="{F412E9FE-4C23-4374-A052-04C1F51DECF3}"/>
-    <hyperlink ref="C558" r:id="rId493" xr:uid="{449D0218-88EB-46E3-B0E4-2396D7F735E4}"/>
-    <hyperlink ref="C557" r:id="rId494" xr:uid="{7D6EF784-1F9A-4B36-90F6-AE8F627E5B8E}"/>
-    <hyperlink ref="C556" r:id="rId495" xr:uid="{D8B5388E-51D0-496B-A7D3-74F358D037B4}"/>
-    <hyperlink ref="C555" r:id="rId496" xr:uid="{F9F24C9F-2E3E-4D43-A177-0E5D2ACFC3DB}"/>
-    <hyperlink ref="C554" r:id="rId497" xr:uid="{EBEB933D-B423-41C9-9335-42397362BD62}"/>
-    <hyperlink ref="C553" r:id="rId498" xr:uid="{F4DC805F-FE7E-4A06-B475-D0E38D707111}"/>
-    <hyperlink ref="C552" r:id="rId499" xr:uid="{20418103-4EDF-42B7-9CBC-B36B42BA50FC}"/>
-    <hyperlink ref="C551" r:id="rId500" xr:uid="{6E09CD2C-B320-448D-A7EA-AB8C174E2970}"/>
-    <hyperlink ref="C550" r:id="rId501" xr:uid="{6E97C3B1-4CCB-44C9-ADA0-F640C6D728C6}"/>
-    <hyperlink ref="C549" r:id="rId502" xr:uid="{A3CBBBD1-2612-4CDD-81EF-7B827025D704}"/>
-    <hyperlink ref="C548" r:id="rId503" xr:uid="{889BBB9F-9281-42CD-8162-9C391B05D0E9}"/>
-    <hyperlink ref="C547" r:id="rId504" xr:uid="{3DB128D7-B924-44A9-A7C9-E6BC79E97B53}"/>
-    <hyperlink ref="C546" r:id="rId505" location="ug" xr:uid="{DC468B40-CC91-45B4-89A6-89B34BED7BF2}"/>
-    <hyperlink ref="C545" r:id="rId506" xr:uid="{33329805-9235-4129-B754-2D7734FBDDC7}"/>
-    <hyperlink ref="C544" r:id="rId507" xr:uid="{891F2F49-6F9D-42A2-B1C4-D4C4DE0F80CE}"/>
-    <hyperlink ref="C543" r:id="rId508" xr:uid="{298C3AFD-57FA-4BA3-8E29-707970F312E7}"/>
-    <hyperlink ref="C542" r:id="rId509" xr:uid="{6B0E6526-0C2D-4948-A6DC-921C8EB514C0}"/>
-    <hyperlink ref="C541" r:id="rId510" xr:uid="{58674F07-58BA-4940-9FD6-19FEB6F9995F}"/>
-    <hyperlink ref="C540" r:id="rId511" xr:uid="{CF302509-B5CB-407F-8B80-DBDE5822D97D}"/>
-    <hyperlink ref="C539" r:id="rId512" xr:uid="{53FFE010-86CC-42DA-BACE-36ECDF356E08}"/>
-    <hyperlink ref="C538" r:id="rId513" xr:uid="{B4314B32-2437-45EE-AA5A-5436BB31A223}"/>
-    <hyperlink ref="C537" r:id="rId514" xr:uid="{644D1C8A-4F41-4B57-8560-02BF758E73C4}"/>
-    <hyperlink ref="C536" r:id="rId515" xr:uid="{E86CD9EA-CFB3-41D9-B477-51F488869BDA}"/>
-    <hyperlink ref="C535" r:id="rId516" xr:uid="{0E4455B9-563E-43B3-9B53-A67F42506607}"/>
-    <hyperlink ref="C534" r:id="rId517" xr:uid="{562E68DB-94AF-45A2-936A-29A55800A148}"/>
-    <hyperlink ref="C533" r:id="rId518" xr:uid="{3A9CECF8-3087-4F4D-9265-80DC3E35D0CD}"/>
-    <hyperlink ref="C532" r:id="rId519" xr:uid="{6D8E7DFC-8EA5-4CD5-A126-6002F2E0A49F}"/>
-    <hyperlink ref="C531" r:id="rId520" xr:uid="{4185B687-50FC-4DC7-AB12-13062EE007F1}"/>
-    <hyperlink ref="C530" r:id="rId521" xr:uid="{9F49DD3E-B4A4-459C-AB78-866AAE5F3740}"/>
-    <hyperlink ref="C529" r:id="rId522" xr:uid="{39591972-9528-46B2-B533-F57A0735C396}"/>
-    <hyperlink ref="C528" r:id="rId523" xr:uid="{6A585B48-9DED-40FF-AAD1-CA36B8D95708}"/>
-    <hyperlink ref="C527" r:id="rId524" xr:uid="{77D0E52D-2981-4747-8803-EF1ED3E783DA}"/>
-    <hyperlink ref="C526" r:id="rId525" location="campus" xr:uid="{52922C32-37C3-4208-A1F7-E78E2A373254}"/>
-    <hyperlink ref="C525" r:id="rId526" location="masters" xr:uid="{D649413F-95A1-4375-9598-286113814371}"/>
-    <hyperlink ref="C524" r:id="rId527" xr:uid="{24A3EBAB-422A-4271-B422-720A28073A9F}"/>
-    <hyperlink ref="C523" r:id="rId528" xr:uid="{88691330-C7B9-467A-98B0-95319440599C}"/>
-    <hyperlink ref="C522" r:id="rId529" xr:uid="{74DC548D-C4A3-4733-AF06-0C7DD6C62157}"/>
-    <hyperlink ref="C521" r:id="rId530" xr:uid="{57365EF2-8AB1-412F-AC9D-E719A61B491A}"/>
-    <hyperlink ref="C520" r:id="rId531" xr:uid="{CA189A21-4B9A-4BB3-B64B-17F20F3049F0}"/>
-    <hyperlink ref="C519" r:id="rId532" xr:uid="{0AE22385-9740-42F1-BA48-F8E80C6C12CB}"/>
-    <hyperlink ref="C518" r:id="rId533" xr:uid="{8F7744FB-5D44-4B28-B752-EEAF67B446C9}"/>
-    <hyperlink ref="C517" r:id="rId534" xr:uid="{284E0EA3-4A3D-4CD0-AB09-51F3DF7D52BD}"/>
-    <hyperlink ref="C516" r:id="rId535" xr:uid="{EAD90F60-C919-4409-876F-FDA530F9D9EA}"/>
-    <hyperlink ref="C515" r:id="rId536" xr:uid="{A8EBE29B-AB58-466D-A3EF-065CFB1AB505}"/>
-    <hyperlink ref="C514" r:id="rId537" xr:uid="{104E7E5B-E107-4FDA-92B8-9CF512BD0F9E}"/>
-    <hyperlink ref="C513" r:id="rId538" xr:uid="{C7E8E7F0-EE55-4307-A285-F9163015384F}"/>
-    <hyperlink ref="C512" r:id="rId539" xr:uid="{7136EEAA-B7A4-423D-B8D2-4805FE4CB0E8}"/>
-    <hyperlink ref="C511" r:id="rId540" xr:uid="{2F6E9089-4464-4A32-B725-83014A8476CB}"/>
-    <hyperlink ref="C510" r:id="rId541" xr:uid="{D857A142-E2FD-451F-96F3-53CF337B9DFF}"/>
-    <hyperlink ref="C509" r:id="rId542" location="ugrad" xr:uid="{AF7624A7-2C13-4F57-A7F2-91499AD42237}"/>
-    <hyperlink ref="C508" r:id="rId543" xr:uid="{E461EA24-B5B5-4A3D-80C4-78BDF2F74205}"/>
-    <hyperlink ref="C507" r:id="rId544" xr:uid="{512D7250-7090-4D3F-9E44-63EA4B71AC1A}"/>
-    <hyperlink ref="C506" r:id="rId545" xr:uid="{0A667B60-C992-483D-82ED-9FE1A7602842}"/>
-    <hyperlink ref="C505" r:id="rId546" xr:uid="{4D1E4B4A-02C1-48DE-AFBE-EEA62554F8FE}"/>
-    <hyperlink ref="C504" r:id="rId547" xr:uid="{FFCA64BE-D68F-4C22-B508-EEDC178D5BBD}"/>
-    <hyperlink ref="C503" r:id="rId548" xr:uid="{527B727E-029F-4D33-9D75-B6891113FFA5}"/>
-    <hyperlink ref="C502" r:id="rId549" location="daytona-beach" xr:uid="{6619E01C-C97E-413A-AE3B-E4E2F21B9D48}"/>
-    <hyperlink ref="C501" r:id="rId550" location="daytona-beach" xr:uid="{FD8E6161-B879-4E13-9A78-61F21A3C7678}"/>
-    <hyperlink ref="C500" r:id="rId551" xr:uid="{F6DE756D-B8DA-4706-AF02-A1F6271A6ACF}"/>
-    <hyperlink ref="C499" r:id="rId552" xr:uid="{22C523A6-EA73-44A9-BFA9-29091694604C}"/>
-    <hyperlink ref="C498" r:id="rId553" xr:uid="{F9693B6F-6879-48C9-A0F7-4BCE9F7C0770}"/>
-    <hyperlink ref="C497" r:id="rId554" xr:uid="{0F1E4574-5A3D-4686-87F2-93F30FC4786A}"/>
-    <hyperlink ref="C496" r:id="rId555" xr:uid="{C947CCBC-4ABC-4909-88A1-891A36C3D143}"/>
-    <hyperlink ref="C148" r:id="rId556" xr:uid="{7F6B9F29-5C0B-44BD-A010-01F97569E946}"/>
-    <hyperlink ref="C149" r:id="rId557" xr:uid="{5BE80C95-BAF0-4A58-9807-04F4F10A3392}"/>
-    <hyperlink ref="C150" r:id="rId558" xr:uid="{25AC73C5-D8D1-4A68-A0ED-2C33B0812D96}"/>
-    <hyperlink ref="C151" r:id="rId559" xr:uid="{20020986-2A6B-4DF5-A8F2-DA0825DA1250}"/>
-    <hyperlink ref="C152" r:id="rId560" xr:uid="{17F73CFB-29AD-46AB-8232-950E37B0E449}"/>
-    <hyperlink ref="C153:C155" r:id="rId561" display="https://legacy.rru.ac.in/wp-content/uploads/2024/05/Fees-Structure-SITAICS-14May2024.pdf" xr:uid="{B02E8987-C0BF-4204-9DEE-15C5487B79D4}"/>
-    <hyperlink ref="C156" r:id="rId562" xr:uid="{425719C5-F52F-47A4-A471-5E9CE58AF26F}"/>
-    <hyperlink ref="C157" r:id="rId563" xr:uid="{B475B03A-FB81-4C71-B29C-70FA7AAFFF80}"/>
-    <hyperlink ref="C159" r:id="rId564" xr:uid="{2DB408F7-F842-4D81-91E1-B7EE65A5333B}"/>
-    <hyperlink ref="C158" r:id="rId565" xr:uid="{2E087C33-3DD1-4C79-9650-FEDFAF3A4CA3}"/>
-    <hyperlink ref="C702" r:id="rId566" xr:uid="{CB6F7D4F-5238-4A25-A57A-5E2CA49D5342}"/>
-    <hyperlink ref="C703" r:id="rId567" xr:uid="{C2947CAE-69C4-4BE5-8DF0-A99CE63CD05B}"/>
-    <hyperlink ref="C704" r:id="rId568" xr:uid="{B185A001-DE46-4EE0-95BB-A4E9B6B6346C}"/>
-    <hyperlink ref="C705" r:id="rId569" xr:uid="{3D7A51E3-B2A6-4C4A-AECD-AD1A1BDE0153}"/>
-    <hyperlink ref="C707" r:id="rId570" xr:uid="{81D9600D-2B5C-4080-927F-A21B1FF13BE9}"/>
-    <hyperlink ref="C706" r:id="rId571" xr:uid="{79FCD9E3-C4DF-4EC5-940E-885C48E301D8}"/>
-    <hyperlink ref="C708" r:id="rId572" xr:uid="{6C7FE20D-7316-4C13-8984-F397B99D740A}"/>
-    <hyperlink ref="C709" r:id="rId573" xr:uid="{C1038379-2771-4E84-9F19-D016F4ECC3E2}"/>
-    <hyperlink ref="C710:C711" r:id="rId574" display="https://drive.google.com/file/d/1fmepJ31Dfjm_qh5g_wunPXVkMUXKCSpc/view?usp=drive_link" xr:uid="{B72A07BB-EE24-4372-A901-142BDEB56755}"/>
-    <hyperlink ref="C712" r:id="rId575" xr:uid="{C95CACC9-22F3-4D48-8ABB-088984800843}"/>
-    <hyperlink ref="C714" r:id="rId576" xr:uid="{857B428D-FF38-4DDB-8BF7-216A91ED3B1E}"/>
-    <hyperlink ref="C713" r:id="rId577" xr:uid="{6F5B5F2A-9EAF-431A-B12D-848D191E74B5}"/>
-    <hyperlink ref="C715" r:id="rId578" xr:uid="{B5F7EFD7-D7A0-447F-8D0B-BEAA0E423624}"/>
-    <hyperlink ref="C716:C717" r:id="rId579" display="https://adypu.edu.in/wp-content/uploads/2024/07/20.ADYPU_Fees-Structure_24_25.pdf" xr:uid="{8E209706-7354-43E9-9E76-780A501BF850}"/>
-    <hyperlink ref="C718" r:id="rId580" xr:uid="{93B84C99-C0B6-427E-B792-003A6B811699}"/>
-    <hyperlink ref="C719" r:id="rId581" xr:uid="{D108B0AB-F2B0-4489-85FF-B2A32E48718F}"/>
-    <hyperlink ref="C720" r:id="rId582" xr:uid="{4A5AE46C-3678-4870-8072-2C019224F376}"/>
-    <hyperlink ref="C721" r:id="rId583" xr:uid="{87423149-8C1C-417F-8927-BA7D7AB22193}"/>
-    <hyperlink ref="C722" r:id="rId584" xr:uid="{45FBAD21-C7D2-4739-92B6-FD2076623CFA}"/>
-    <hyperlink ref="C723" r:id="rId585" xr:uid="{6186688D-F4AE-4360-8BB9-B9A4B17BEDF6}"/>
-    <hyperlink ref="C724" r:id="rId586" xr:uid="{3590360E-D482-446B-9F79-4FFE7C1C073A}"/>
-    <hyperlink ref="C725" r:id="rId587" xr:uid="{BC14503A-7E37-4FFA-9650-52DD0EADF29A}"/>
-    <hyperlink ref="C726" r:id="rId588" xr:uid="{DFDE858C-3C0E-40F6-9020-84277BF915FB}"/>
-    <hyperlink ref="C727" r:id="rId589" xr:uid="{E1D751F8-CB65-4034-804F-EA8E8F306747}"/>
-    <hyperlink ref="C728" r:id="rId590" xr:uid="{8665E79A-CE2F-45D2-BDDF-83DA3585472B}"/>
-    <hyperlink ref="C729" r:id="rId591" xr:uid="{B04D9CA0-2E77-46DA-8B87-8F1D8EF9C049}"/>
-    <hyperlink ref="C730" r:id="rId592" xr:uid="{FC3E61AF-9A93-4DBC-8CA2-A1C543CDB7D8}"/>
-    <hyperlink ref="C731" r:id="rId593" xr:uid="{68780992-6DAA-46A8-B8B4-B4BBA2917299}"/>
-    <hyperlink ref="C732" r:id="rId594" xr:uid="{C7172857-AB2C-429C-B752-E3089788612D}"/>
-    <hyperlink ref="C733" r:id="rId595" xr:uid="{3F50DD60-5393-43B0-8FFA-68A491669212}"/>
-    <hyperlink ref="C734" r:id="rId596" xr:uid="{C2627F34-5141-4887-A16B-CBF356C57E75}"/>
-    <hyperlink ref="C735" r:id="rId597" xr:uid="{EDED4804-2A29-4FCF-B16F-9093CA1F3402}"/>
-    <hyperlink ref="C736" r:id="rId598" xr:uid="{2906778E-2DEE-4AF6-B797-56BD3D3C92ED}"/>
-    <hyperlink ref="C737" r:id="rId599" xr:uid="{CF7BF210-6C7C-4748-B136-7D7D48E92F53}"/>
-    <hyperlink ref="C738" r:id="rId600" xr:uid="{9F8F3B0F-5923-4A92-AA17-551220766D9C}"/>
-    <hyperlink ref="C739" r:id="rId601" xr:uid="{D4072CFA-7E3A-4A31-924C-881FC018FA1A}"/>
-    <hyperlink ref="C741" r:id="rId602" xr:uid="{52487C8C-5AFB-4B5D-B5DF-9746B10422F0}"/>
-    <hyperlink ref="C740" r:id="rId603" xr:uid="{CF4335A8-2F33-49DD-A1EF-E4E9C570D98B}"/>
-    <hyperlink ref="C742" r:id="rId604" xr:uid="{9C63E6AF-038B-4C76-ADBA-E8DAFFC07E08}"/>
-    <hyperlink ref="C743" r:id="rId605" xr:uid="{E8B25F31-922E-4758-B02E-98B6F7060A88}"/>
-    <hyperlink ref="C744" r:id="rId606" xr:uid="{ABBAA515-0609-486C-BF64-FC3D99099187}"/>
-    <hyperlink ref="C745" r:id="rId607" xr:uid="{C00DB4FA-AF1D-4613-90A1-6FA57556076F}"/>
-    <hyperlink ref="C746" r:id="rId608" xr:uid="{CD016168-6D69-4F69-B68F-AA2EC32DFF6B}"/>
-    <hyperlink ref="C747" r:id="rId609" xr:uid="{CBE487E3-FACC-4B31-A120-61DC195C4D23}"/>
-    <hyperlink ref="C748" r:id="rId610" xr:uid="{EA090370-5F35-4063-959B-C8ADF669CEDE}"/>
-    <hyperlink ref="C749" r:id="rId611" xr:uid="{149D1ED3-CD53-4AE1-864A-A603DE5D12BC}"/>
-    <hyperlink ref="C750" r:id="rId612" xr:uid="{F017CC9E-0054-49FE-89AF-2D059AF6377F}"/>
-    <hyperlink ref="C751:C761" r:id="rId613" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{3B4E76B5-095C-45FE-B0CF-148644D9E11A}"/>
-    <hyperlink ref="C762" r:id="rId614" xr:uid="{B9D39B54-5728-4732-ACBF-88C9E7BB69BC}"/>
-    <hyperlink ref="C763" r:id="rId615" xr:uid="{5B64FB65-FE64-4A6B-AC64-EFC901A56244}"/>
-    <hyperlink ref="C764" r:id="rId616" xr:uid="{8C07BE98-0EA8-4A43-AF2B-442367D94176}"/>
-    <hyperlink ref="C765" r:id="rId617" xr:uid="{3355522E-84C3-495A-8C36-08E1DE7E740B}"/>
-    <hyperlink ref="C767" r:id="rId618" xr:uid="{B8C3CA87-1E12-457E-A5EA-C907F81668CD}"/>
-    <hyperlink ref="C768" r:id="rId619" xr:uid="{EC7491DD-D308-4AE6-824C-E20C1B0A063C}"/>
-    <hyperlink ref="C769" r:id="rId620" xr:uid="{CE4036C3-C29B-4E9A-BA2F-4103F4685B9D}"/>
-    <hyperlink ref="C161" r:id="rId621" xr:uid="{8DD02B6F-54A2-4FAC-B961-2C220AA1D943}"/>
-    <hyperlink ref="C162" r:id="rId622" xr:uid="{ED2940C7-EB7F-4547-BEC9-673E028B1F6E}"/>
-    <hyperlink ref="C770" r:id="rId623" xr:uid="{4015FD70-74FB-4621-A2FD-7986807085D5}"/>
-    <hyperlink ref="C771" r:id="rId624" xr:uid="{1F87E026-2DE2-4DBC-83B3-D6B951EA1E3C}"/>
-    <hyperlink ref="C772" r:id="rId625" xr:uid="{D6BE8929-2D3C-4A7B-BBAF-A4A4EE063EF8}"/>
-    <hyperlink ref="C773" r:id="rId626" xr:uid="{9DD1D3EA-72B8-45E8-BDA9-021B474CA435}"/>
-    <hyperlink ref="C774" r:id="rId627" xr:uid="{1BEB74B5-CAC1-4F1D-A056-DDD1E6CDBF96}"/>
-    <hyperlink ref="C775" r:id="rId628" xr:uid="{3073747A-DA6A-4CE0-A0B7-7AA867EE17D6}"/>
-    <hyperlink ref="C776" r:id="rId629" xr:uid="{B4E301A8-90DD-46D6-976D-FBA6A1684A1F}"/>
-    <hyperlink ref="C777" r:id="rId630" xr:uid="{CD3DDDEF-3C39-40EC-8B04-FA8675A7977F}"/>
-    <hyperlink ref="C778" r:id="rId631" xr:uid="{65D284DB-F879-47B9-A268-DFBC28C219E5}"/>
-    <hyperlink ref="C779" r:id="rId632" xr:uid="{3AF0420D-3F28-4CBB-BAE4-39DCD9DAEF50}"/>
-    <hyperlink ref="C51" r:id="rId633" xr:uid="{ECEE7BB5-A33D-4352-A89E-8D249C116DCB}"/>
-    <hyperlink ref="C455" r:id="rId634" xr:uid="{973FDA1F-DE1F-48CE-BE77-75DC093E98AA}"/>
-    <hyperlink ref="C366" r:id="rId635" xr:uid="{4696752E-5EF9-49D9-8362-5A976A1F5B12}"/>
-    <hyperlink ref="C365" r:id="rId636" xr:uid="{36DF91A2-AE4E-448A-A9E7-A1F91838B227}"/>
-    <hyperlink ref="C362" r:id="rId637" xr:uid="{09480EB5-1061-45DB-AA34-BC6317432F73}"/>
-    <hyperlink ref="C359" r:id="rId638" xr:uid="{4C8A3339-5E9D-44A2-851B-38820E24A7C1}"/>
-    <hyperlink ref="C457" r:id="rId639" xr:uid="{635DE0D8-AFDF-4529-93F2-B5CCE74EF50C}"/>
-    <hyperlink ref="C780" r:id="rId640" xr:uid="{BC6B2562-6B84-425C-9B87-36CDC918AC76}"/>
-    <hyperlink ref="C781" r:id="rId641" xr:uid="{D521C8BF-0148-4A06-80F7-96B5FD3E47F7}"/>
-    <hyperlink ref="C782" r:id="rId642" xr:uid="{89DA4F63-868B-410D-8AFE-DEAE3F4D14CF}"/>
-    <hyperlink ref="C783" r:id="rId643" xr:uid="{F240B56A-A908-4554-A031-75ABA7FACF20}"/>
-    <hyperlink ref="C784" r:id="rId644" xr:uid="{C6533D41-F550-4BED-9C7C-02E70C8DFA0D}"/>
-    <hyperlink ref="C766" r:id="rId645" xr:uid="{29B0C30A-FA81-4314-A11E-2CF9021B0C5D}"/>
-    <hyperlink ref="C785" r:id="rId646" xr:uid="{1DD05091-13EF-4185-8598-42B2C13DD25A}"/>
-    <hyperlink ref="C597" r:id="rId647" xr:uid="{AAD3B5F2-348C-4D6F-B2DC-32F09F0A9B13}"/>
-    <hyperlink ref="C596" r:id="rId648" xr:uid="{664C10D8-0E38-4804-B463-7F0186B1738E}"/>
-    <hyperlink ref="C598" r:id="rId649" xr:uid="{0A368D49-1F7C-4FA0-82FD-8A76D82CD659}"/>
-    <hyperlink ref="C786" r:id="rId650" xr:uid="{B1CFA210-9743-4205-9904-B22C9F9EBED7}"/>
-    <hyperlink ref="C787" r:id="rId651" xr:uid="{4D483717-7B75-4C1D-BAF2-3E13CC02FA4B}"/>
-    <hyperlink ref="C788" r:id="rId652" xr:uid="{BA58CA45-509E-4E2D-86A7-BCE34C89B704}"/>
+    <hyperlink ref="C301" r:id="rId56" xr:uid="{50BE28BE-EEC0-42A1-BF88-53F38F6E210D}"/>
+    <hyperlink ref="C300" r:id="rId57" xr:uid="{CFD94F31-1639-49D8-AC52-E4A9B6E79A88}"/>
+    <hyperlink ref="C281" r:id="rId58" xr:uid="{39908BCE-03CE-4E8E-88E0-14867A42C301}"/>
+    <hyperlink ref="C282" r:id="rId59" xr:uid="{B144F34E-4532-445C-99A7-8D0142EF6573}"/>
+    <hyperlink ref="C284" r:id="rId60" xr:uid="{97B1CB3D-D17B-4AA0-B81B-A13DD58BEF07}"/>
+    <hyperlink ref="C285" r:id="rId61" xr:uid="{85716DDE-1BCF-4C45-BD30-F0F32FCC7BA2}"/>
+    <hyperlink ref="C286" r:id="rId62" xr:uid="{1A73D5EC-C5F3-450A-9415-6433112AC5F5}"/>
+    <hyperlink ref="C287" r:id="rId63" xr:uid="{72B68110-7FD3-4CC3-BF9B-C2574C9FABBC}"/>
+    <hyperlink ref="C288" r:id="rId64" xr:uid="{0F47A361-B9DE-414D-8AAC-08AD33F5DBDA}"/>
+    <hyperlink ref="C289" r:id="rId65" xr:uid="{EE607C57-767F-418D-8F35-E4B1333ECE83}"/>
+    <hyperlink ref="C290" r:id="rId66" xr:uid="{3D5C617B-CE68-4732-AF17-3B49144E78EB}"/>
+    <hyperlink ref="C291" r:id="rId67" xr:uid="{76744081-BB3C-4B23-B65F-1C6CF056D4EE}"/>
+    <hyperlink ref="C292" r:id="rId68" xr:uid="{C14DC252-4FD7-49CC-8A77-D245087DAAC4}"/>
+    <hyperlink ref="C293" r:id="rId69" xr:uid="{A425C347-D05D-4B03-A1C8-85A516D4D679}"/>
+    <hyperlink ref="C294" r:id="rId70" xr:uid="{1A0A2778-C528-4240-AE1C-C721590C29A0}"/>
+    <hyperlink ref="C295" r:id="rId71" xr:uid="{075590E0-3ED6-48C1-8C36-BC102567B233}"/>
+    <hyperlink ref="C296" r:id="rId72" xr:uid="{2850DD06-7003-4B9B-91BD-7BB02A744727}"/>
+    <hyperlink ref="C297" r:id="rId73" xr:uid="{46BEC18B-400C-4027-A3EE-BB7604D3737C}"/>
+    <hyperlink ref="C298" r:id="rId74" xr:uid="{1C99AAE8-E2BA-45C3-8A01-9F78A181E0CD}"/>
+    <hyperlink ref="C299" r:id="rId75" xr:uid="{6103D502-998D-427A-9A23-6679ECC115E0}"/>
+    <hyperlink ref="C348" r:id="rId76" xr:uid="{2085C974-D039-483D-830E-688CA69587CE}"/>
+    <hyperlink ref="C349" r:id="rId77" xr:uid="{92BDC019-D47F-42C6-88EF-FF3D15C3253C}"/>
+    <hyperlink ref="C350" r:id="rId78" xr:uid="{A02D7A54-7141-4DC3-BD2C-401F1F063D6A}"/>
+    <hyperlink ref="C351" r:id="rId79" xr:uid="{3696490A-3DF9-4760-BD7A-E5DDF2847C97}"/>
+    <hyperlink ref="C352" r:id="rId80" xr:uid="{D2ED480E-8869-4050-ACEC-D41D9BED3531}"/>
+    <hyperlink ref="C353" r:id="rId81" xr:uid="{35FE7A98-D273-4A53-A436-4D6DC405CE44}"/>
+    <hyperlink ref="C354" r:id="rId82" xr:uid="{02AFB5CE-7536-438D-B2CA-FD65369F785B}"/>
+    <hyperlink ref="C355" r:id="rId83" xr:uid="{80824CD4-A47B-491E-AD53-0E7CE2983953}"/>
+    <hyperlink ref="C357" r:id="rId84" xr:uid="{E42870AF-4970-422D-BF87-CF83600C953D}"/>
+    <hyperlink ref="C358" r:id="rId85" xr:uid="{B00B442D-9361-44A2-A000-59B7159F8A5F}"/>
+    <hyperlink ref="C360" r:id="rId86" xr:uid="{E38D219C-145E-4473-B879-70FF23EE0192}"/>
+    <hyperlink ref="C361" r:id="rId87" xr:uid="{D8E0CEBF-68A2-499E-896E-05DB38D0B569}"/>
+    <hyperlink ref="C363" r:id="rId88" xr:uid="{E35E0044-2BA8-4628-84A9-FB97196C55AD}"/>
+    <hyperlink ref="C364" r:id="rId89" xr:uid="{F6947610-E27A-44A0-9509-E18C4A91087E}"/>
+    <hyperlink ref="C367" r:id="rId90" xr:uid="{DEC92388-812C-41BF-8187-02600A52A136}"/>
+    <hyperlink ref="C369" r:id="rId91" xr:uid="{95752DC6-55EC-4FB6-89D8-2502BFFA6DA2}"/>
+    <hyperlink ref="C370:C383" r:id="rId92" display="https://drive.google.com/file/d/1vog0rWXRzF2SF33kPUkXoESePa2Hb8wr/view" xr:uid="{C3AE02AF-1F36-4B36-8496-90AA87FFF470}"/>
+    <hyperlink ref="C388" r:id="rId93" xr:uid="{C6049889-C71C-406E-850C-4A6007DB2B0B}"/>
+    <hyperlink ref="C389:C404" r:id="rId94" display="https://drive.google.com/file/d/1vog0rWXRzF2SF33kPUkXoESePa2Hb8wr/view" xr:uid="{A36E29EE-BB11-4244-BCE2-DD9B55DC7098}"/>
+    <hyperlink ref="C456" r:id="rId95" xr:uid="{7CD6D41E-3B33-4720-BAB0-B43E7D8876FE}"/>
+    <hyperlink ref="C449" r:id="rId96" xr:uid="{08D546DD-62CC-4F48-85C0-BE27C50B1380}"/>
+    <hyperlink ref="C458" r:id="rId97" xr:uid="{8F138784-F396-44B3-8C5B-34D8CBB85FA8}"/>
+    <hyperlink ref="C45" r:id="rId98" xr:uid="{9C6777DC-9050-416C-A895-3805C52237CC}"/>
+    <hyperlink ref="C46" r:id="rId99" xr:uid="{D8BBE816-3252-4B73-881D-738B7A638572}"/>
+    <hyperlink ref="C47" r:id="rId100" xr:uid="{DB604BA5-DF8C-47A2-9D97-F721C4BA7E09}"/>
+    <hyperlink ref="C48" r:id="rId101" xr:uid="{8B1A4CD8-BF23-4F35-83AF-10776947E5EF}"/>
+    <hyperlink ref="C49" r:id="rId102" xr:uid="{AD98015A-EF46-4A97-9F4B-ED452873A2C9}"/>
+    <hyperlink ref="C50" r:id="rId103" xr:uid="{B6926384-7374-484C-A09B-5E6859DB1B53}"/>
+    <hyperlink ref="C444" r:id="rId104" xr:uid="{1A7BED46-A4D2-4122-AE6B-8D9B7BC1E57E}"/>
+    <hyperlink ref="C443" r:id="rId105" xr:uid="{B42A7545-0A4B-4720-8F10-69F89F36E4A2}"/>
+    <hyperlink ref="C442" r:id="rId106" xr:uid="{B01190ED-7FA4-4324-A4AA-A0B423EF3F2F}"/>
+    <hyperlink ref="C387" r:id="rId107" xr:uid="{E77156BB-529F-4C0A-9E10-F8A630153851}"/>
+    <hyperlink ref="C441" r:id="rId108" xr:uid="{5F8E80AC-1EC8-47B9-8E66-DCFA235AA1A7}"/>
+    <hyperlink ref="C429" r:id="rId109" xr:uid="{A1B03889-75C2-4FBB-90CE-69C8A85694E2}"/>
+    <hyperlink ref="C432" r:id="rId110" xr:uid="{A688D2FB-7C80-493D-8E33-81F480A1079A}"/>
+    <hyperlink ref="C334" r:id="rId111" xr:uid="{409DEF6B-637B-4337-AC44-3FBF64FC2184}"/>
+    <hyperlink ref="C52" r:id="rId112" xr:uid="{25A0B1B3-F505-42AC-B470-194048815C37}"/>
+    <hyperlink ref="C53" r:id="rId113" xr:uid="{651BB4B5-94B4-4E7C-B602-48074069E520}"/>
+    <hyperlink ref="C54" r:id="rId114" xr:uid="{ADAAA73E-15E5-4523-B79F-44D50D9F665E}"/>
+    <hyperlink ref="C55" r:id="rId115" xr:uid="{B8FF9BDA-DC69-4E1F-A29C-CA2FC6758FA4}"/>
+    <hyperlink ref="C56" r:id="rId116" xr:uid="{D1069D97-0F2F-46FE-981C-DE27B837E146}"/>
+    <hyperlink ref="C57" r:id="rId117" xr:uid="{71C34B2C-4806-4433-8843-5E2C9D37997A}"/>
+    <hyperlink ref="C58" r:id="rId118" xr:uid="{59FFCFC0-B91B-45B4-BA1A-44CC77CAB8E6}"/>
+    <hyperlink ref="C74" r:id="rId119" xr:uid="{E2C1FEF6-329B-4047-B2DC-A65627AA2EBB}"/>
+    <hyperlink ref="C80" r:id="rId120" xr:uid="{F0ECA015-E7E4-4C2E-A634-3E3DE03FF78D}"/>
+    <hyperlink ref="C83" r:id="rId121" xr:uid="{1CA08F40-73C7-4E1E-B100-CFF54A53EF6A}"/>
+    <hyperlink ref="C84" r:id="rId122" xr:uid="{C2FAD9F8-5365-4F7B-939B-161DD7F9E21E}"/>
+    <hyperlink ref="C85" r:id="rId123" xr:uid="{8749C6A4-5913-4791-8743-C46F14EB0330}"/>
+    <hyperlink ref="C86" r:id="rId124" xr:uid="{C0821B94-7A8E-4CF0-9FB2-665C66F0FEF5}"/>
+    <hyperlink ref="C90" r:id="rId125" xr:uid="{6F3A4D1D-73E0-4573-A874-B9E6BA54DB8B}"/>
+    <hyperlink ref="C92" r:id="rId126" xr:uid="{CECC8A8E-E7A2-48B9-BEF5-CFDB5FAD1789}"/>
+    <hyperlink ref="C113" r:id="rId127" location="feeDetails" xr:uid="{05D90BFF-52D2-46FA-87CB-DE7EEADAAE3B}"/>
+    <hyperlink ref="C114" r:id="rId128" location="feeDetails" xr:uid="{31BF87E5-F141-4A66-8C9C-D3305B32752F}"/>
+    <hyperlink ref="C115" r:id="rId129" xr:uid="{137D059F-835D-40BB-BE4C-4C8B10C06F79}"/>
+    <hyperlink ref="C116" r:id="rId130" xr:uid="{CDAB71DC-AB58-426A-B4A9-F3E59ADC93B8}"/>
+    <hyperlink ref="C117" r:id="rId131" xr:uid="{15BF9224-665B-4E90-BD0B-79821E6ED4D8}"/>
+    <hyperlink ref="C118" r:id="rId132" xr:uid="{C559B688-3520-4AAE-AD9D-139E016C9C51}"/>
+    <hyperlink ref="C119" r:id="rId133" xr:uid="{2890A325-FC09-4085-BECB-FFB79098E847}"/>
+    <hyperlink ref="C120" r:id="rId134" xr:uid="{E149005A-D5CD-4279-9774-1F79D5DD7384}"/>
+    <hyperlink ref="C135" r:id="rId135" xr:uid="{654C965C-4AEF-490B-BF67-74F80E293DA9}"/>
+    <hyperlink ref="C335" r:id="rId136" xr:uid="{E9AE3AFD-268E-40D4-8290-625F440E5302}"/>
+    <hyperlink ref="C336" r:id="rId137" xr:uid="{AA2909AE-78FE-473E-B408-EF8505C221E1}"/>
+    <hyperlink ref="C337" r:id="rId138" xr:uid="{9A268E81-8526-4AAD-83A0-DAAA0587F608}"/>
+    <hyperlink ref="C338" r:id="rId139" xr:uid="{9802CB4D-1666-4A2B-BD6B-C4B6DF98DE4B}"/>
+    <hyperlink ref="C339" r:id="rId140" xr:uid="{5B56D843-A553-463F-96D6-1F9B7F750CC9}"/>
+    <hyperlink ref="C340" r:id="rId141" xr:uid="{3F82A7F4-2089-4A78-AD3F-404325FD8806}"/>
+    <hyperlink ref="C341" r:id="rId142" xr:uid="{D4C39F60-C7A5-4EC5-8381-0BA84090CEF1}"/>
+    <hyperlink ref="C342" r:id="rId143" xr:uid="{E846D15C-B6B9-4C3D-9DEE-0C6D38A1B104}"/>
+    <hyperlink ref="C368" r:id="rId144" xr:uid="{C159B9BC-C021-4F27-A49F-56A8B6A7BFED}"/>
+    <hyperlink ref="C385" r:id="rId145" xr:uid="{061EE0CD-4E7F-4ACA-9861-EE92BA563DD3}"/>
+    <hyperlink ref="C386" r:id="rId146" xr:uid="{CE99FFE1-C83F-4DA8-B248-BB8F708004C2}"/>
+    <hyperlink ref="C440" r:id="rId147" xr:uid="{58AF09A1-4DA1-4C13-A924-7038BAFF295B}"/>
+    <hyperlink ref="C439" r:id="rId148" xr:uid="{236BF6F5-D6E3-45C6-8B23-68B8D0655F15}"/>
+    <hyperlink ref="C437" r:id="rId149" xr:uid="{E69F8561-4FEC-4C42-8E14-50B2E9393A13}"/>
+    <hyperlink ref="C438" r:id="rId150" xr:uid="{4C6593DF-C1C6-42A1-842C-BE5F55D1C605}"/>
+    <hyperlink ref="C436" r:id="rId151" xr:uid="{516AD057-D9E0-436D-AD29-4C3C49BC1430}"/>
+    <hyperlink ref="C435" r:id="rId152" xr:uid="{7C7C69A3-9F29-4F4D-A44D-6990529D8FAF}"/>
+    <hyperlink ref="C434" r:id="rId153" xr:uid="{91542EDF-6A2E-4075-B7BA-B2F1F8D0A714}"/>
+    <hyperlink ref="C433" r:id="rId154" xr:uid="{CB0F8AB7-B42B-4853-A3B5-088035C1D966}"/>
+    <hyperlink ref="C228" r:id="rId155" xr:uid="{FDB9A05E-682B-4C8D-80B7-C00B35288AE0}"/>
+    <hyperlink ref="C384" r:id="rId156" xr:uid="{8B09D238-BC27-4FFB-9A65-E4DF63A42C1D}"/>
+    <hyperlink ref="C59" r:id="rId157" location="!/admission" xr:uid="{61B8463B-D859-4230-9FF8-1B5393E117F3}"/>
+    <hyperlink ref="C60" r:id="rId158" location="!/mtech_cyber" xr:uid="{B55FEB65-57AD-405E-8A56-2FA984A4A9B0}"/>
+    <hyperlink ref="C61" r:id="rId159" xr:uid="{F278F221-DB82-4A2A-A653-F528F133A217}"/>
+    <hyperlink ref="C62" r:id="rId160" xr:uid="{0DF5AEA7-57A2-4E89-9283-89F20D3AF94D}"/>
+    <hyperlink ref="C431" r:id="rId161" xr:uid="{934D29A8-8919-4C31-8AB6-C15B23F2A0E9}"/>
+    <hyperlink ref="C430" r:id="rId162" xr:uid="{3A901F7E-443D-4533-B3A8-32D563BE970D}"/>
+    <hyperlink ref="C428" r:id="rId163" xr:uid="{5F53F94F-A1DD-478A-992E-B8B23E6434F4}"/>
+    <hyperlink ref="C427" r:id="rId164" xr:uid="{3295F066-4FDB-4115-9B6A-BF8DF52B2D4F}"/>
+    <hyperlink ref="C426" r:id="rId165" xr:uid="{C3B52501-E6F1-4E5A-9414-2A60F3A8BF4C}"/>
+    <hyperlink ref="C425" r:id="rId166" xr:uid="{ABFD91D8-D01D-459E-B4E0-59B864E00056}"/>
+    <hyperlink ref="C424" r:id="rId167" xr:uid="{0529A5F1-3179-4D02-8652-30F9A46D33DD}"/>
+    <hyperlink ref="C423" r:id="rId168" xr:uid="{3A72B964-7DA8-4F2E-94CF-E6E47D26B07C}"/>
+    <hyperlink ref="C422" r:id="rId169" xr:uid="{0F21AB0F-7276-40FC-8DAC-13265F890365}"/>
+    <hyperlink ref="C421" r:id="rId170" xr:uid="{E8578DFD-6ED9-4928-A1E5-DA3E7E6F68E1}"/>
+    <hyperlink ref="C420" r:id="rId171" xr:uid="{DF332798-21C9-4E8B-B57B-B6065E3D7DBD}"/>
+    <hyperlink ref="C419" r:id="rId172" xr:uid="{8E709FB1-3B19-4143-9110-724B80D71CD5}"/>
+    <hyperlink ref="C418" r:id="rId173" xr:uid="{CC5498BB-5E6F-403B-9D7F-4B5DD6C55F15}"/>
+    <hyperlink ref="C417" r:id="rId174" xr:uid="{57AF8459-4E89-47B0-B109-1902EB74EF2E}"/>
+    <hyperlink ref="C416" r:id="rId175" xr:uid="{870A97EE-A952-4484-8DB7-39D344D5DBC1}"/>
+    <hyperlink ref="C405" r:id="rId176" xr:uid="{38DF5807-6CF4-4F71-938E-536834854BFC}"/>
+    <hyperlink ref="C407" r:id="rId177" xr:uid="{70870616-497E-4084-B506-707215E9CE0A}"/>
+    <hyperlink ref="C406" r:id="rId178" xr:uid="{4DE6439C-F439-443A-BB85-E7246A24CC8C}"/>
+    <hyperlink ref="C408" r:id="rId179" xr:uid="{F1D3A36D-1474-41C0-8AD5-D6A33A52F519}"/>
+    <hyperlink ref="C409" r:id="rId180" xr:uid="{FFE2DBCB-1CCC-4940-BCAC-505A097C6ACA}"/>
+    <hyperlink ref="C411" r:id="rId181" xr:uid="{9DD54BD2-B079-4E90-A72D-103383F2F20E}"/>
+    <hyperlink ref="C410" r:id="rId182" xr:uid="{24D497AA-AF1E-486A-8878-BD99E4F3F3E4}"/>
+    <hyperlink ref="C412" r:id="rId183" xr:uid="{7D208A04-2A48-449D-9453-661B7BD8EA56}"/>
+    <hyperlink ref="C413" r:id="rId184" xr:uid="{16A944FF-67D5-4B20-A323-FE46D5E2AE88}"/>
+    <hyperlink ref="C414" r:id="rId185" xr:uid="{E17D51B2-6B89-4974-8E6A-D2079806A523}"/>
+    <hyperlink ref="C415" r:id="rId186" xr:uid="{ACB0A0C3-40A8-4A8D-9E1A-ED7AB3025BA2}"/>
+    <hyperlink ref="C280" r:id="rId187" xr:uid="{CA05E1D2-B622-49FA-B37E-10F9644FD81F}"/>
+    <hyperlink ref="C63" r:id="rId188" xr:uid="{00D49E34-09B7-4A9E-973C-31610ABB8154}"/>
+    <hyperlink ref="C64" r:id="rId189" xr:uid="{BF168807-AA0C-4040-8B55-A33C673C58D1}"/>
+    <hyperlink ref="C65" r:id="rId190" xr:uid="{42A01053-45C6-4C93-8CDC-640176507BA8}"/>
+    <hyperlink ref="C66" r:id="rId191" xr:uid="{16F0E7D0-33D8-4F6C-B2E1-55A5C1EF0BA0}"/>
+    <hyperlink ref="C67" r:id="rId192" xr:uid="{FAC80AD1-D0E1-49C5-8B4C-A85BAF8AB259}"/>
+    <hyperlink ref="C68" r:id="rId193" xr:uid="{7AE725A3-C413-4112-B74C-3B61A4C51726}"/>
+    <hyperlink ref="C69" r:id="rId194" xr:uid="{9B200477-E6FA-4964-8910-235734D4D88D}"/>
+    <hyperlink ref="C70" r:id="rId195" xr:uid="{F40500AC-8A80-4F18-85DA-4CAD2FC6AD98}"/>
+    <hyperlink ref="C71" r:id="rId196" xr:uid="{8138436D-4A9C-4406-9464-7EF994C91067}"/>
+    <hyperlink ref="C72" r:id="rId197" xr:uid="{D2BA7CF4-D077-40D7-83E8-E25BB8C4BFC8}"/>
+    <hyperlink ref="C73" r:id="rId198" xr:uid="{9B5A9BEF-F202-4CB7-80D5-801876E4D999}"/>
+    <hyperlink ref="C75" r:id="rId199" xr:uid="{B520082F-5A8C-42E4-B8A0-85A54CA0490F}"/>
+    <hyperlink ref="C76" r:id="rId200" xr:uid="{414BE7E8-4C7C-46E1-86EA-CA5BE61BD3BB}"/>
+    <hyperlink ref="C77" r:id="rId201" xr:uid="{220CEA6A-6CFE-4E9D-8149-755E9C622E49}"/>
+    <hyperlink ref="C78" r:id="rId202" xr:uid="{E00F5BD2-4966-435C-A636-0040FD4AE6EC}"/>
+    <hyperlink ref="C79" r:id="rId203" xr:uid="{8B50ECF6-203A-472A-B3B1-68D4365008FD}"/>
+    <hyperlink ref="C81" r:id="rId204" xr:uid="{89B41390-21AA-41E7-AFAE-384E689F93B8}"/>
+    <hyperlink ref="C82" r:id="rId205" xr:uid="{84869D7A-67E7-4CED-86CA-5444BCBC5F6F}"/>
+    <hyperlink ref="C93" r:id="rId206" xr:uid="{7FB09E3F-E7AF-4F62-8BB6-E2979CEB3C51}"/>
+    <hyperlink ref="C94" r:id="rId207" xr:uid="{61CB8AE9-5D0F-4FCA-B851-93B682722A4C}"/>
+    <hyperlink ref="C95" r:id="rId208" xr:uid="{2D80F475-6FC9-4172-845F-BAAFA138E4A0}"/>
+    <hyperlink ref="C96" r:id="rId209" xr:uid="{D51EC73D-CB09-4A74-A3C2-F06D27CFD5AB}"/>
+    <hyperlink ref="C97" r:id="rId210" xr:uid="{7C7D2F14-0EA3-445D-BEAD-8F7CCEC0E375}"/>
+    <hyperlink ref="C98" r:id="rId211" xr:uid="{E180A90F-81F5-4738-B2AA-7672ABEE4F37}"/>
+    <hyperlink ref="C99" r:id="rId212" xr:uid="{4ECA026B-0747-44CB-9D31-474E1A82D397}"/>
+    <hyperlink ref="C100" r:id="rId213" xr:uid="{48D08408-BB76-4331-B95E-B1F5E44AECB3}"/>
+    <hyperlink ref="C101" r:id="rId214" xr:uid="{62C42544-F088-440A-ACEC-B663575744EC}"/>
+    <hyperlink ref="C192" r:id="rId215" xr:uid="{FD8F3FF6-B6D3-470D-A2B1-F17BE6071352}"/>
+    <hyperlink ref="C193:C201" r:id="rId216" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{C58B0A20-C20C-47C7-880A-56B75CCD0AA4}"/>
+    <hyperlink ref="C202" r:id="rId217" xr:uid="{70518E27-1FB3-4922-A9A0-6F0B82901DC3}"/>
+    <hyperlink ref="C203" r:id="rId218" xr:uid="{5178E260-CD9F-4988-BC34-CA9577046958}"/>
+    <hyperlink ref="C128" r:id="rId219" xr:uid="{E87D8A80-F6BC-452B-B97C-CAF8F9A3BB5A}"/>
+    <hyperlink ref="C129:C131" r:id="rId220" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{08C8A54B-58B2-4F53-888C-E421AACE9D9A}"/>
+    <hyperlink ref="C186" r:id="rId221" xr:uid="{DDF05934-8C66-408F-A3FE-7356C1AFB789}"/>
+    <hyperlink ref="C188" r:id="rId222" xr:uid="{EA2271AC-EFC5-4265-B6EB-546C89D8F321}"/>
+    <hyperlink ref="C247" r:id="rId223" xr:uid="{4EC4FF74-1934-49F8-A1CA-7BBABB016C70}"/>
+    <hyperlink ref="C248:C250" r:id="rId224" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{2E883870-4C94-41D5-9745-3E512B680395}"/>
+    <hyperlink ref="C251" r:id="rId225" xr:uid="{C679360F-EDEF-4CF9-AD5D-DDB5C453EFA3}"/>
+    <hyperlink ref="C252" r:id="rId226" xr:uid="{31073172-6E59-40A0-B301-1C3E80E80C79}"/>
+    <hyperlink ref="C253" r:id="rId227" xr:uid="{D91C0790-63C8-4D7E-B375-838D54599BB5}"/>
+    <hyperlink ref="C254" r:id="rId228" xr:uid="{3BE4031E-904D-479C-B94F-FA21E9BB6C9B}"/>
+    <hyperlink ref="C255" r:id="rId229" xr:uid="{D9320C11-CF38-4DC5-A972-4CE40F2702A0}"/>
+    <hyperlink ref="C279" r:id="rId230" xr:uid="{E022713A-1ABD-4553-8D41-38E0D2117BC0}"/>
+    <hyperlink ref="C278" r:id="rId231" xr:uid="{A603A503-83F2-413F-8441-AB78EB17DA72}"/>
+    <hyperlink ref="C187" r:id="rId232" xr:uid="{1D565744-D70E-4E1A-B939-DEA40AFCBDFA}"/>
+    <hyperlink ref="C273" r:id="rId233" xr:uid="{9FAFA356-00F7-458E-8170-CCFBA7A8CAF9}"/>
+    <hyperlink ref="C274" r:id="rId234" xr:uid="{91F50700-E6E1-405D-884D-003BAD84CF6E}"/>
+    <hyperlink ref="C275" r:id="rId235" xr:uid="{AA3DA20E-FE16-41F6-8ED7-8F5678E81426}"/>
+    <hyperlink ref="C276" r:id="rId236" xr:uid="{8CE261A8-CA95-4381-8F7A-BA7947013160}"/>
+    <hyperlink ref="C277" r:id="rId237" xr:uid="{6A25D613-5662-4B27-AE60-55FA6309D7A7}"/>
+    <hyperlink ref="C160" r:id="rId238" xr:uid="{7D8A021C-BEFB-46B6-9465-17F517B264FA}"/>
+    <hyperlink ref="C163" r:id="rId239" xr:uid="{754497C5-B35D-4D8D-A73D-D6C04230A65D}"/>
+    <hyperlink ref="C164:C165" r:id="rId240" display="https://www.sanskriti.edu.in/admissions/eligibilty-and-fee-structure.php" xr:uid="{67EC2355-EEEA-4588-9FB9-030B9D46FA56}"/>
+    <hyperlink ref="C166" r:id="rId241" xr:uid="{B906D7DB-4CBB-4051-98B6-D84969E49A3D}"/>
+    <hyperlink ref="C167" r:id="rId242" xr:uid="{D0A25218-E720-4813-94C7-A3AFFC06EE5D}"/>
+    <hyperlink ref="C168" r:id="rId243" xr:uid="{0DB740AE-A804-4189-975E-34555E589CE0}"/>
+    <hyperlink ref="C169" r:id="rId244" xr:uid="{1AAB6151-0D15-4AE9-8D34-BB1459CEAB33}"/>
+    <hyperlink ref="C191" r:id="rId245" xr:uid="{6223C244-02A7-4FC0-A825-B1CEDF933567}"/>
+    <hyperlink ref="C190" r:id="rId246" xr:uid="{E370FD19-9FFA-428C-9F77-5E3E9C2842B9}"/>
+    <hyperlink ref="C189" r:id="rId247" xr:uid="{A742A948-3925-4118-801D-7A89FC650F19}"/>
+    <hyperlink ref="C102" r:id="rId248" xr:uid="{5F65C71C-DEA5-425C-828B-57EF9A6B6746}"/>
+    <hyperlink ref="C103" r:id="rId249" xr:uid="{61A7FFCA-C177-4280-90B0-9C2F3B852BDC}"/>
+    <hyperlink ref="C104" r:id="rId250" xr:uid="{82202B66-784F-4D9C-BA61-A5D395291FB1}"/>
+    <hyperlink ref="C105" r:id="rId251" xr:uid="{D1FC4980-AA57-4887-AB9A-91CE4936A97C}"/>
+    <hyperlink ref="C106" r:id="rId252" xr:uid="{D1D99F66-E8E7-4092-AD14-AF5347154355}"/>
+    <hyperlink ref="C107:C108" r:id="rId253" display="https://www.krmangalam.edu.in/fee-structure" xr:uid="{041D9F7C-0B8D-4204-BDD2-41566D9CDABA}"/>
+    <hyperlink ref="C109" r:id="rId254" xr:uid="{B1DA8F4A-A9BF-430C-ADCD-1467BD21089F}"/>
+    <hyperlink ref="C110" r:id="rId255" xr:uid="{8B00BAAF-6A4E-4F37-AB70-9E5584E5E0AD}"/>
+    <hyperlink ref="C112" r:id="rId256" xr:uid="{DCC6876A-46B3-4475-8D11-D32285D0066B}"/>
+    <hyperlink ref="C121" r:id="rId257" xr:uid="{87F7A942-4D6F-40DB-975B-6D93C1BA428C}"/>
+    <hyperlink ref="C122" r:id="rId258" xr:uid="{DE0490D6-496F-4F6C-8BA9-CD46CF5C9F77}"/>
+    <hyperlink ref="C272" r:id="rId259" xr:uid="{6CE3AFEA-E1D9-489B-8C5D-201EAF186C38}"/>
+    <hyperlink ref="C271" r:id="rId260" xr:uid="{934B4DFF-33A3-4EA4-AC1F-597C69761C0B}"/>
+    <hyperlink ref="C270" r:id="rId261" xr:uid="{E669D885-E739-4BD6-869A-D12708B4E845}"/>
+    <hyperlink ref="C269" r:id="rId262" xr:uid="{833A5F42-00A6-4864-AB2A-502D00F0178F}"/>
+    <hyperlink ref="C268" r:id="rId263" xr:uid="{C9A75FFF-6031-4BF4-A2EF-2B74612FC588}"/>
+    <hyperlink ref="C267" r:id="rId264" xr:uid="{910B5DBB-5CBF-4A25-B2C8-C34AFAD9A15B}"/>
+    <hyperlink ref="C266" r:id="rId265" xr:uid="{E7BB6CD5-434F-4DAD-B7B2-FEF59F5BDF6A}"/>
+    <hyperlink ref="C265" r:id="rId266" xr:uid="{AA4C275D-D058-4FE8-8B2B-D7966333612E}"/>
+    <hyperlink ref="C264" r:id="rId267" xr:uid="{2A007E23-5293-4B95-B807-97D238EB1028}"/>
+    <hyperlink ref="C263" r:id="rId268" xr:uid="{781268BD-6ECD-48F8-B948-CA1763EB88B5}"/>
+    <hyperlink ref="C262" r:id="rId269" xr:uid="{A014BCDF-8751-44F9-8255-EC6EF94F02EB}"/>
+    <hyperlink ref="C261" r:id="rId270" xr:uid="{32BE2A73-3831-4F9F-9188-82D7241CC633}"/>
+    <hyperlink ref="C260" r:id="rId271" xr:uid="{28931F66-6D1F-450B-BA78-6079CD437337}"/>
+    <hyperlink ref="C259" r:id="rId272" xr:uid="{03A1A604-E522-4B2E-9129-2DBCC086E524}"/>
+    <hyperlink ref="C258" r:id="rId273" xr:uid="{11CC5024-0FAC-43F9-A277-A0FABE39A171}"/>
+    <hyperlink ref="C257" r:id="rId274" xr:uid="{00EED605-FD52-4668-B4C9-3AE6A0380213}"/>
+    <hyperlink ref="C256" r:id="rId275" xr:uid="{B73E7671-B06F-48B7-A489-DF42F8206025}"/>
+    <hyperlink ref="C210" r:id="rId276" xr:uid="{884A2211-4FF0-40E0-9D41-63827D4F9E33}"/>
+    <hyperlink ref="C205:C209" r:id="rId277" display="https://www.niilmuniversity.ac.in/page/domestic-fee" xr:uid="{4D0998A5-ADE4-474F-8919-F9D9E65445C7}"/>
+    <hyperlink ref="C204" r:id="rId278" xr:uid="{92AB9E3A-3740-4E42-8C5E-3AE1F91C4248}"/>
+    <hyperlink ref="C244" r:id="rId279" xr:uid="{F7A24EF7-FFF2-4EB9-A23D-278B2F25FF71}"/>
+    <hyperlink ref="C245" r:id="rId280" xr:uid="{0E76EC08-B404-4A3B-895C-55A24BA3DE07}"/>
+    <hyperlink ref="C246" r:id="rId281" xr:uid="{A5E36846-E219-462A-8019-2BD0A5912A91}"/>
+    <hyperlink ref="C243" r:id="rId282" xr:uid="{D1E84938-1080-4D26-8E66-44242951B470}"/>
+    <hyperlink ref="C242" r:id="rId283" xr:uid="{C396EDF0-1A95-4843-B018-7A004FCC0CA1}"/>
+    <hyperlink ref="C241" r:id="rId284" xr:uid="{BBC3A9F2-24DD-409F-A293-A40816186309}"/>
+    <hyperlink ref="C240" r:id="rId285" xr:uid="{861A8984-FC97-432D-AEDB-6C6F0C28849E}"/>
+    <hyperlink ref="C239" r:id="rId286" xr:uid="{73E8FC8B-D981-4D40-B451-08A903237BF6}"/>
+    <hyperlink ref="C238" r:id="rId287" xr:uid="{93144211-564D-4012-87FD-FADD1C7BB886}"/>
+    <hyperlink ref="C237" r:id="rId288" xr:uid="{752B0DA3-974C-4265-B2E3-745AAC530D50}"/>
+    <hyperlink ref="C236" r:id="rId289" xr:uid="{D9A762DF-9474-4708-B4FC-576A5BF5417B}"/>
+    <hyperlink ref="C234" r:id="rId290" xr:uid="{74443DD3-85E5-4D8D-AF47-025F0237936A}"/>
+    <hyperlink ref="C235" r:id="rId291" xr:uid="{26C6D44F-AD06-404E-A439-BAB869152981}"/>
+    <hyperlink ref="C232:C233" r:id="rId292" display="https://drive.google.com/file/d/1-XYvZlg7yblN8siHvowA7MDqYvaVwxmT/view?usp=drive_link" xr:uid="{9CB5D6BA-45EF-435D-AA05-5D8D0F634A29}"/>
+    <hyperlink ref="C231" r:id="rId293" xr:uid="{7243E531-903C-4938-9F91-52535DE094A3}"/>
+    <hyperlink ref="C230" r:id="rId294" xr:uid="{9BB80BA5-E208-48F8-9305-2C19B3F4AE50}"/>
+    <hyperlink ref="C229" r:id="rId295" xr:uid="{EE33DEC9-C7FD-45DD-8172-DB3C92F205DD}"/>
+    <hyperlink ref="C170" r:id="rId296" xr:uid="{E609FE68-8129-4F76-A406-C616F4475FFF}"/>
+    <hyperlink ref="C171" r:id="rId297" xr:uid="{8C71D231-DEFC-41D2-B20C-A2B68ED1AF50}"/>
+    <hyperlink ref="C172" r:id="rId298" xr:uid="{D9227C42-5CFB-4E22-88F0-D1DA08A5B641}"/>
+    <hyperlink ref="C173" r:id="rId299" xr:uid="{C4E9765D-AD6D-45C0-82FD-C48F5D2DFF7A}"/>
+    <hyperlink ref="C174" r:id="rId300" xr:uid="{63279210-5C8F-48D9-8A96-4F2EEB965471}"/>
+    <hyperlink ref="C175" r:id="rId301" xr:uid="{17552510-4E38-4F27-BABB-EF7117617DA1}"/>
+    <hyperlink ref="C176" r:id="rId302" xr:uid="{1FF3E28B-483B-4301-948F-210FDA7A328F}"/>
+    <hyperlink ref="C177" r:id="rId303" xr:uid="{2B3BB96A-22A5-4DF3-819F-AC6C2F83D70D}"/>
+    <hyperlink ref="C178" r:id="rId304" xr:uid="{27396A5C-ABAF-4AC4-8BFC-DE96363F1329}"/>
+    <hyperlink ref="C179" r:id="rId305" xr:uid="{A0D9E9FE-9B75-45B4-8C98-2E918DA04801}"/>
+    <hyperlink ref="C180" r:id="rId306" xr:uid="{BA9D60C8-3A62-4FBF-AC68-30BCE66C3054}"/>
+    <hyperlink ref="C181" r:id="rId307" xr:uid="{94371691-82FF-4BC1-8C40-6060D10DEA93}"/>
+    <hyperlink ref="C182" r:id="rId308" xr:uid="{F161FF5D-D939-4ECD-A684-367B9D4E8F3B}"/>
+    <hyperlink ref="C183" r:id="rId309" xr:uid="{A87C3849-3A96-4E64-B06B-0FA36A4D1A50}"/>
+    <hyperlink ref="C227" r:id="rId310" xr:uid="{69A6E3B4-B9BE-406B-9449-B6F1C52859BD}"/>
+    <hyperlink ref="C226" r:id="rId311" xr:uid="{A65F5E63-F864-497D-B4E2-8D7B991B7A9F}"/>
+    <hyperlink ref="C225" r:id="rId312" xr:uid="{9E0A3F3E-F295-4D05-9358-31E7E3F975B0}"/>
+    <hyperlink ref="C123" r:id="rId313" xr:uid="{025751A2-5E7B-4B2C-94BC-0695460BE8FA}"/>
+    <hyperlink ref="C124" r:id="rId314" xr:uid="{333AB1E1-ED40-4E48-BB49-34418ED912F7}"/>
+    <hyperlink ref="C217" r:id="rId315" xr:uid="{FBB97787-2F14-4BB2-917B-775C371C9762}"/>
+    <hyperlink ref="C184" r:id="rId316" xr:uid="{5DCA712E-B5BD-450D-B0B7-2BE98A50C5B4}"/>
+    <hyperlink ref="C132" r:id="rId317" xr:uid="{957E3857-240F-405B-8368-4641DF8EC154}"/>
+    <hyperlink ref="C133" r:id="rId318" xr:uid="{B4D4928E-7C0F-45C4-8CE2-873EC0C89A81}"/>
+    <hyperlink ref="C134" r:id="rId319" xr:uid="{4061BF43-FC11-4722-A43E-C366B88F19F1}"/>
+    <hyperlink ref="C136" r:id="rId320" xr:uid="{34F9BF4C-6418-4046-A21C-92FE36275EF2}"/>
+    <hyperlink ref="C137" r:id="rId321" xr:uid="{F2578955-7E22-4475-80C7-A39349E8FEA6}"/>
+    <hyperlink ref="C224" r:id="rId322" xr:uid="{86DA7070-85E7-462C-92FB-83548FC9FDEF}"/>
+    <hyperlink ref="C223" r:id="rId323" xr:uid="{4239EE1C-E740-4EF1-B3C2-2930AFF4ED33}"/>
+    <hyperlink ref="C222" r:id="rId324" xr:uid="{8113E903-7AE6-499F-826D-AA5E1D82404A}"/>
+    <hyperlink ref="C221" r:id="rId325" xr:uid="{19C2FEE2-A4BD-4801-8A7E-E5A2B4BB7DF9}"/>
+    <hyperlink ref="C220" r:id="rId326" xr:uid="{7F873713-D8E7-4368-8D89-D4EA6A780A4D}"/>
+    <hyperlink ref="C219" r:id="rId327" xr:uid="{257A14A4-3665-4E91-A3DF-75AF79A04428}"/>
+    <hyperlink ref="C218" r:id="rId328" xr:uid="{17DE8754-080F-42A0-8008-3B22FE424381}"/>
+    <hyperlink ref="C216" r:id="rId329" xr:uid="{C7A26D3E-6B13-4390-A3B8-076C93AC8280}"/>
+    <hyperlink ref="C215" r:id="rId330" xr:uid="{3CC019A7-5595-4626-B258-2152CBAEF85E}"/>
+    <hyperlink ref="C214" r:id="rId331" xr:uid="{37E486E4-616E-40B3-B0C1-F3FF6CC33F97}"/>
+    <hyperlink ref="C213" r:id="rId332" xr:uid="{5CE33C60-403A-4391-A6ED-75181F17DB38}"/>
+    <hyperlink ref="C212" r:id="rId333" xr:uid="{88A01FF5-9960-46AC-B62A-D63A692F81EC}"/>
+    <hyperlink ref="C211" r:id="rId334" xr:uid="{375182E1-BF7E-4D5B-AEB9-B21138D96106}"/>
+    <hyperlink ref="C485" r:id="rId335" xr:uid="{0D700A3B-31B6-49B0-9A4C-8800BD838F55}"/>
+    <hyperlink ref="C487" r:id="rId336" xr:uid="{37D6CE14-05F0-4575-90CA-1961380A3B0A}"/>
+    <hyperlink ref="C488" r:id="rId337" xr:uid="{BD7ED2EB-D561-4548-9ECD-9D18B410E687}"/>
+    <hyperlink ref="C489" r:id="rId338" xr:uid="{822813F8-60EB-439F-8E3A-F86768DEB37B}"/>
+    <hyperlink ref="C490" r:id="rId339" xr:uid="{958FA13C-EEE0-4F80-9135-81CA5B1A0295}"/>
+    <hyperlink ref="C491" r:id="rId340" xr:uid="{4D572C2A-6FDB-4913-A3E0-517056D63DA7}"/>
+    <hyperlink ref="C492" r:id="rId341" xr:uid="{71657101-3C84-4944-9D2E-2C1E23E72A41}"/>
+    <hyperlink ref="C493" r:id="rId342" xr:uid="{62611662-48DB-4599-BABF-444498618EB1}"/>
+    <hyperlink ref="C494" r:id="rId343" xr:uid="{821D9F99-F1A5-4C60-A0B8-EC5B800A5572}"/>
+    <hyperlink ref="C495" r:id="rId344" xr:uid="{84BED024-EB1B-4425-A1CA-922374ACF188}"/>
+    <hyperlink ref="C616" r:id="rId345" xr:uid="{0EFC7DC7-72F6-4B29-89C8-67F10DEE9A54}"/>
+    <hyperlink ref="C618" r:id="rId346" xr:uid="{85605A6A-6936-4352-A4E0-080226705436}"/>
+    <hyperlink ref="C617" r:id="rId347" xr:uid="{A33CC4D9-2118-40F3-8797-04D5E7CA31C3}"/>
+    <hyperlink ref="C619" r:id="rId348" xr:uid="{496B62F6-A429-4833-9B25-45FF193F1B69}"/>
+    <hyperlink ref="C620" r:id="rId349" xr:uid="{23B0E2BF-C57E-41BE-AE89-729361F9D101}"/>
+    <hyperlink ref="C621" r:id="rId350" xr:uid="{FD5F0098-93F2-4746-BA83-9394F7706198}"/>
+    <hyperlink ref="C622" r:id="rId351" xr:uid="{ABF20253-94C6-4105-8060-5DD8ACBCF3ED}"/>
+    <hyperlink ref="C623" r:id="rId352" xr:uid="{5AAD0D59-1AE3-4A27-8D5A-A8782A47BEFF}"/>
+    <hyperlink ref="C624" r:id="rId353" xr:uid="{4A1CAE48-1E67-4FE0-8974-A0FBC3D89A15}"/>
+    <hyperlink ref="C626" r:id="rId354" xr:uid="{DFDA7392-9030-46C1-8E32-782EE28524DC}"/>
+    <hyperlink ref="C625" r:id="rId355" xr:uid="{B9060AA0-D62C-46CB-B594-315F3EECD8D4}"/>
+    <hyperlink ref="C628" r:id="rId356" xr:uid="{BAC0E18A-DF61-4CAF-AC82-B4EB7B8C8F3C}"/>
+    <hyperlink ref="C627" r:id="rId357" xr:uid="{3A75497B-A717-4B4D-BECB-0FFB8BC79629}"/>
+    <hyperlink ref="C629" r:id="rId358" xr:uid="{E1B1465D-C375-4CA0-B346-4058CD793DF6}"/>
+    <hyperlink ref="C630" r:id="rId359" xr:uid="{AD92CF36-346E-4A37-B661-80DF86D590EF}"/>
+    <hyperlink ref="C631" r:id="rId360" xr:uid="{FB2F82BC-70B9-4149-8269-BB52AFCF9AE2}"/>
+    <hyperlink ref="C632" r:id="rId361" xr:uid="{B6022C23-98EB-4D0F-9B5C-A29C3BF69B04}"/>
+    <hyperlink ref="C633" r:id="rId362" xr:uid="{D0FB1C11-C3F6-4ED3-9465-C7F546387C21}"/>
+    <hyperlink ref="C634" r:id="rId363" xr:uid="{BDEF1248-1B6C-4C2E-99F0-BB23AC10FAE7}"/>
+    <hyperlink ref="C635" r:id="rId364" xr:uid="{C012353D-A7C1-4C9F-9034-CAAF98034D25}"/>
+    <hyperlink ref="C636" r:id="rId365" xr:uid="{79189C6E-4C69-4F02-A218-69A8C0803FD5}"/>
+    <hyperlink ref="C637" r:id="rId366" xr:uid="{BD278F26-DE2D-4294-9F54-E705BD0E01F4}"/>
+    <hyperlink ref="C638" r:id="rId367" xr:uid="{3A3CF422-DB40-4AC2-A775-FE585834DEA3}"/>
+    <hyperlink ref="C639" r:id="rId368" xr:uid="{4C73EEAB-646D-4568-B4A0-A11CC0BC7713}"/>
+    <hyperlink ref="C640" r:id="rId369" xr:uid="{6B84AD41-BC2D-4783-B320-4B30D9E8E8FA}"/>
+    <hyperlink ref="C641" r:id="rId370" xr:uid="{99E79A20-8220-4969-B2B1-D8FBFBB512DC}"/>
+    <hyperlink ref="C642" r:id="rId371" xr:uid="{C149BBA6-109D-4CAF-9D2F-22FD82A6B132}"/>
+    <hyperlink ref="C643" r:id="rId372" xr:uid="{C731F0B6-7F48-4318-8635-EBF35CBF46BD}"/>
+    <hyperlink ref="C644" r:id="rId373" xr:uid="{198C72BF-1766-4C20-963F-266D3042F81A}"/>
+    <hyperlink ref="C645" r:id="rId374" xr:uid="{A061E847-AE51-475E-AD17-C671B390B5B3}"/>
+    <hyperlink ref="C646" r:id="rId375" xr:uid="{CE07D610-59B2-4041-B18D-AD4AE9A4670A}"/>
+    <hyperlink ref="C647" r:id="rId376" xr:uid="{80A033D7-4C74-484D-A0B0-F34217F5C104}"/>
+    <hyperlink ref="C648" r:id="rId377" xr:uid="{0D21866E-AF2B-43E3-B333-42B18F1445F4}"/>
+    <hyperlink ref="C649" r:id="rId378" xr:uid="{F0416CDE-3D0C-480A-BE65-7201D4D12F82}"/>
+    <hyperlink ref="C650" r:id="rId379" xr:uid="{DCA6828D-43E2-43A8-B09D-F5C390B6E180}"/>
+    <hyperlink ref="C651" r:id="rId380" xr:uid="{E26BC46D-70D9-41D6-8DAA-0B375579437D}"/>
+    <hyperlink ref="C652" r:id="rId381" xr:uid="{287A5501-C096-4A06-A6B6-CD41C2FEE1F9}"/>
+    <hyperlink ref="C653" r:id="rId382" xr:uid="{BDBB7C64-2A5A-44B0-81A4-98071DA1B340}"/>
+    <hyperlink ref="C654" r:id="rId383" xr:uid="{D531282E-505B-4400-ADCA-1AB93A945183}"/>
+    <hyperlink ref="C655" r:id="rId384" xr:uid="{FA80F1FC-48E4-4917-AA8F-D9C36A18E7C1}"/>
+    <hyperlink ref="C656" r:id="rId385" xr:uid="{386BBE77-3464-47B3-9372-C585691F46B0}"/>
+    <hyperlink ref="C657" r:id="rId386" xr:uid="{AB473EB1-D825-4DDF-8E1A-4CA160AE68EE}"/>
+    <hyperlink ref="C658" r:id="rId387" xr:uid="{80CD06A1-FB90-4B6B-86FF-D0A47E7D0BA6}"/>
+    <hyperlink ref="C659" r:id="rId388" xr:uid="{14B7A1AD-A6A0-4F1F-A1DC-385B65B72767}"/>
+    <hyperlink ref="C660" r:id="rId389" xr:uid="{998A36D4-03A0-4C6C-8131-1AE94A96617B}"/>
+    <hyperlink ref="C661" r:id="rId390" xr:uid="{40D5F952-36AE-4165-B326-2487A88030F1}"/>
+    <hyperlink ref="C662" r:id="rId391" xr:uid="{09144B8E-7793-47BE-AD91-466849211AD9}"/>
+    <hyperlink ref="C663" r:id="rId392" xr:uid="{00D2F3EE-0EDB-4583-982F-7920B3E07F3D}"/>
+    <hyperlink ref="C664" r:id="rId393" xr:uid="{C3271A95-F2E6-4826-9884-9B95E04A8A93}"/>
+    <hyperlink ref="C665" r:id="rId394" xr:uid="{F57EE512-19F2-4AFE-9F73-10B11F7F1034}"/>
+    <hyperlink ref="C666" r:id="rId395" xr:uid="{A3E2614C-92D9-45E7-BD75-D9A81CB35C8B}"/>
+    <hyperlink ref="C667" r:id="rId396" xr:uid="{BFA1A328-EAFC-4A59-975D-1F4916645A21}"/>
+    <hyperlink ref="C668" r:id="rId397" xr:uid="{5B92D9F8-244C-4016-929F-BB7644514E62}"/>
+    <hyperlink ref="C669" r:id="rId398" xr:uid="{9C5475AE-2251-4061-8B47-A905C1B49030}"/>
+    <hyperlink ref="C670" r:id="rId399" xr:uid="{5815F2F9-997D-4B2A-A8FC-CB735FEE4830}"/>
+    <hyperlink ref="C671" r:id="rId400" xr:uid="{E2DC4F07-1866-4752-923A-B3F471F1A220}"/>
+    <hyperlink ref="C672" r:id="rId401" location="costs" xr:uid="{49AA71EC-190B-4115-BCFF-CFFAD2984979}"/>
+    <hyperlink ref="C673" r:id="rId402" xr:uid="{272B1A72-18FD-46D5-BC64-22AB89BE362D}"/>
+    <hyperlink ref="C674" r:id="rId403" xr:uid="{741CEB76-A7BA-4773-9A62-89EFC6D4E6CF}"/>
+    <hyperlink ref="C675" r:id="rId404" xr:uid="{1007ADA1-4291-470A-9A52-5A3DC9278117}"/>
+    <hyperlink ref="C676" r:id="rId405" xr:uid="{73F9F876-2ACC-40CF-A0E8-288E9B4311A9}"/>
+    <hyperlink ref="C677" r:id="rId406" xr:uid="{3395B036-CCBA-4783-99DA-8435E02A25E6}"/>
+    <hyperlink ref="C678" r:id="rId407" xr:uid="{8022E184-A012-460F-9EFB-764A47B0692C}"/>
+    <hyperlink ref="C679" r:id="rId408" xr:uid="{B141A840-39F3-4D59-A96C-795FA224B5D1}"/>
+    <hyperlink ref="C680" r:id="rId409" xr:uid="{074EC546-A68C-4A62-9C9D-2E0B05E2ADF5}"/>
+    <hyperlink ref="C681" r:id="rId410" xr:uid="{B99D8076-D718-4573-B81C-EC0D11D4459E}"/>
+    <hyperlink ref="C682" r:id="rId411" xr:uid="{06E87414-821D-4C0F-9D21-329503A51BDD}"/>
+    <hyperlink ref="C683" r:id="rId412" xr:uid="{1B54B4A3-52EE-4E72-A4ED-5EB4433F548F}"/>
+    <hyperlink ref="C684" r:id="rId413" xr:uid="{3AB6E156-29F8-48A0-95D1-737838B26C8A}"/>
+    <hyperlink ref="C685" r:id="rId414" xr:uid="{1BAFC71F-F029-4EE4-A8FE-06BC7BF24C1C}"/>
+    <hyperlink ref="C686" r:id="rId415" xr:uid="{5F2B17CB-999A-49E4-9746-1988BE345B17}"/>
+    <hyperlink ref="C687" r:id="rId416" xr:uid="{46970D8B-ABF8-4FD0-B1BA-7886430454BF}"/>
+    <hyperlink ref="C688" r:id="rId417" xr:uid="{E3789310-5C51-45AA-8C38-8A481E35B0F2}"/>
+    <hyperlink ref="C689" r:id="rId418" xr:uid="{75BC526E-2B46-4B67-AA68-02482139533E}"/>
+    <hyperlink ref="C690" r:id="rId419" xr:uid="{AA2C8397-ED3F-49A3-B14D-D4F7ADADD221}"/>
+    <hyperlink ref="C691" r:id="rId420" xr:uid="{9152CA66-3393-4655-BE4B-05C1343B0938}"/>
+    <hyperlink ref="C692" r:id="rId421" xr:uid="{6B7B50F8-364F-4BC9-A5D6-6A381D15C57F}"/>
+    <hyperlink ref="C693:C695" r:id="rId422" display="https://aahe.edu.au/fees/" xr:uid="{03793D0C-6ED7-4717-B84A-05D4D94B6B19}"/>
+    <hyperlink ref="C696" r:id="rId423" xr:uid="{80DA8DE6-1E1C-49A2-B7A8-F9BE0CC4377E}"/>
+    <hyperlink ref="C697" r:id="rId424" xr:uid="{E2DFCB04-71CF-4514-9DB7-D3600957043D}"/>
+    <hyperlink ref="C698" r:id="rId425" xr:uid="{32D3427F-E74C-4266-A4CF-90D1088AF8D7}"/>
+    <hyperlink ref="C699" r:id="rId426" xr:uid="{85D020A3-C099-441F-B9BE-27CC597C4427}"/>
+    <hyperlink ref="C615" r:id="rId427" xr:uid="{881AA85A-03E8-43BD-AD9C-986E38129888}"/>
+    <hyperlink ref="C614" r:id="rId428" xr:uid="{95B49150-A566-4A62-9562-78EEA4F04444}"/>
+    <hyperlink ref="C613" r:id="rId429" xr:uid="{DF271968-FF08-4467-8410-9DF2DB5D5417}"/>
+    <hyperlink ref="C612" r:id="rId430" xr:uid="{ABCC119E-64AB-49D8-A93F-AC60C5741214}"/>
+    <hyperlink ref="C700" r:id="rId431" xr:uid="{D2D23298-4669-4260-BB99-338E4AFCB5B5}"/>
+    <hyperlink ref="C611" r:id="rId432" xr:uid="{DC80456E-4C0C-4D3C-9562-9CE0E3CEA735}"/>
+    <hyperlink ref="C610" r:id="rId433" xr:uid="{9D7444EB-5819-4A7C-9CA6-ACEA70D06652}"/>
+    <hyperlink ref="C609" r:id="rId434" xr:uid="{80CB13C0-25F1-482D-9B7F-9FFAFE64A323}"/>
+    <hyperlink ref="C608" r:id="rId435" location="2025-2026-undergraduate-tuition-and-fees" xr:uid="{5EDBF750-7EDA-4C4E-AB95-93B94C4EDD4F}"/>
+    <hyperlink ref="C607" r:id="rId436" xr:uid="{8C499F14-E8E7-4EB0-A1DB-1B8BAAEABE2C}"/>
+    <hyperlink ref="C606" r:id="rId437" xr:uid="{8AB4357A-A73B-4115-BAE3-A1B617B4C8BA}"/>
+    <hyperlink ref="C701" r:id="rId438" xr:uid="{0C1168BC-C6A2-4561-928F-DA6BAF02551F}"/>
+    <hyperlink ref="C605" r:id="rId439" xr:uid="{2598ACD9-91FD-4348-9E6A-8C465D24D830}"/>
+    <hyperlink ref="C604" r:id="rId440" xr:uid="{F382E6ED-3EB0-4D36-B9B7-7989AA09F029}"/>
+    <hyperlink ref="C603" r:id="rId441" xr:uid="{CAFC4424-D243-454D-B0F7-5A1C02751D44}"/>
+    <hyperlink ref="C602" r:id="rId442" xr:uid="{A3D39A32-3CA5-403F-B5CB-C21BA9DA6CF6}"/>
+    <hyperlink ref="C601" r:id="rId443" xr:uid="{4AFC9F05-548F-44E8-90F3-81253EC05543}"/>
+    <hyperlink ref="C600" r:id="rId444" xr:uid="{6891D883-6AA3-4692-924E-157B6C9D0857}"/>
+    <hyperlink ref="C599" r:id="rId445" xr:uid="{B4D01991-686F-48D0-842B-3E97940F10DD}"/>
+    <hyperlink ref="C595" r:id="rId446" xr:uid="{18EB0A22-4CFD-44BE-BB55-917DCEFA9CA6}"/>
+    <hyperlink ref="C594" r:id="rId447" xr:uid="{E6393A6C-F5B7-4509-82A1-5B6665A7C821}"/>
+    <hyperlink ref="C593" r:id="rId448" location="grad-tuition" xr:uid="{582AFF7E-8573-4189-986B-D6E98B1A4DA5}"/>
+    <hyperlink ref="C592" r:id="rId449" location="grad-tuition" xr:uid="{12E2B2B6-E506-417A-B52B-681DFFEE413E}"/>
+    <hyperlink ref="C591" r:id="rId450" location="resident-table" xr:uid="{770C3304-744E-40B0-A99D-2B6E86521C88}"/>
+    <hyperlink ref="C590" r:id="rId451" xr:uid="{3938ED2B-239B-4B09-A824-1CD6F646EB17}"/>
+    <hyperlink ref="C589" r:id="rId452" xr:uid="{5F647715-25EB-4657-8D93-7426C58CB684}"/>
+    <hyperlink ref="C588" r:id="rId453" xr:uid="{10C07F72-DD92-4886-9F7A-5CAF0462B509}"/>
+    <hyperlink ref="C587" r:id="rId454" xr:uid="{5741F3B1-8B60-4B23-ACB2-DA55B686C652}"/>
+    <hyperlink ref="C586" r:id="rId455" xr:uid="{3EFA6110-A11B-457B-8659-72012A54BD3A}"/>
+    <hyperlink ref="C585" r:id="rId456" xr:uid="{80B2DADD-BE3F-4EC7-9C12-3BDAD01813E8}"/>
+    <hyperlink ref="C584" r:id="rId457" xr:uid="{FC1DFD8B-AB65-442C-8A3F-D25996D5D4C0}"/>
+    <hyperlink ref="C583" r:id="rId458" xr:uid="{786B9AB5-33CB-4B37-B2A1-9FA3A61D0DD6}"/>
+    <hyperlink ref="C582" r:id="rId459" xr:uid="{7531FEF1-ECCA-4CD5-91DF-310ADDD8620D}"/>
+    <hyperlink ref="C581" r:id="rId460" xr:uid="{2D4038F2-67F3-48E2-8D1B-4C350C4242A7}"/>
+    <hyperlink ref="C580" r:id="rId461" xr:uid="{8C1E2096-E167-499A-AB57-FAC294ECEDCD}"/>
+    <hyperlink ref="C579" r:id="rId462" xr:uid="{A1C64A08-55EA-4EB5-89B5-0F7F4F342B4E}"/>
+    <hyperlink ref="C578" r:id="rId463" xr:uid="{CB94780F-B641-4597-9CE1-45FFF6AD4B24}"/>
+    <hyperlink ref="C576:C577" r:id="rId464" display="https://engineering.washu.edu/academics/graduate-admissions/tuition-financial-assistance/index.html" xr:uid="{94704AD1-79B0-45E6-9E54-DA16CCCFC1D5}"/>
+    <hyperlink ref="C575" r:id="rId465" xr:uid="{2F7C4AEF-B867-4041-A0A5-E963758EC26E}"/>
+    <hyperlink ref="C574" r:id="rId466" xr:uid="{58CC675F-324C-49CC-8E26-E01400549445}"/>
+    <hyperlink ref="C573" r:id="rId467" xr:uid="{E76C2F8E-D177-4AF5-B631-AE2D0BE2CE97}"/>
+    <hyperlink ref="C572" r:id="rId468" xr:uid="{23695B31-E2B8-4257-8223-E7539FD64A00}"/>
+    <hyperlink ref="C571" r:id="rId469" xr:uid="{6076A241-D906-428A-BAD4-365660712C56}"/>
+    <hyperlink ref="C570" r:id="rId470" xr:uid="{0583E2AF-776E-4CFE-95E6-39AB0ECC45D5}"/>
+    <hyperlink ref="C140" r:id="rId471" xr:uid="{3FA076C9-5495-4945-A4AE-B4C9F3E2D651}"/>
+    <hyperlink ref="C139" r:id="rId472" xr:uid="{51F46025-FA8D-4F49-987B-8B7ACF84D46B}"/>
+    <hyperlink ref="C138" r:id="rId473" xr:uid="{96F590C7-1AE4-4D20-949F-27E943D8E9DD}"/>
+    <hyperlink ref="C141" r:id="rId474" xr:uid="{FBABABEF-6172-480C-B6C6-FFDD1742D1BC}"/>
+    <hyperlink ref="C142" r:id="rId475" xr:uid="{1FD9EFE7-3C5D-4629-AAB4-3BA4E758F297}"/>
+    <hyperlink ref="C145" r:id="rId476" xr:uid="{E34B10FB-C082-4D97-951B-BA7BA04C2BFF}"/>
+    <hyperlink ref="C144" r:id="rId477" xr:uid="{FC90D068-9B74-4B67-8A58-04475F302838}"/>
+    <hyperlink ref="C143" r:id="rId478" xr:uid="{124C2F78-505A-46EC-BCEF-939FE257A92C}"/>
+    <hyperlink ref="C146" r:id="rId479" xr:uid="{2B0BC0FA-A684-4FE8-9ADA-F341D5031D9C}"/>
+    <hyperlink ref="C147" r:id="rId480" xr:uid="{57EA4E59-7D86-4715-AA19-80FD2129EA16}"/>
+    <hyperlink ref="C569" r:id="rId481" xr:uid="{174134F4-7EA9-406B-AC8D-971EFE1F24E3}"/>
+    <hyperlink ref="C568" r:id="rId482" xr:uid="{4CE185F9-CED9-438C-86C9-851D7566A9A7}"/>
+    <hyperlink ref="C567" r:id="rId483" xr:uid="{A20522D3-BFD6-4189-AD43-2A60AD94F7C6}"/>
+    <hyperlink ref="C566" r:id="rId484" xr:uid="{BF8FFE00-58C9-498F-9FB7-53370E4F76E6}"/>
+    <hyperlink ref="C565" r:id="rId485" xr:uid="{BA78BBFE-BA3A-4567-8842-D9DAC7BD4114}"/>
+    <hyperlink ref="C564" r:id="rId486" xr:uid="{AB8D8480-94A0-4F6D-94DD-954187AAF1CA}"/>
+    <hyperlink ref="C563" r:id="rId487" xr:uid="{F485B58C-0963-4817-B71B-E1D073DD028E}"/>
+    <hyperlink ref="C562" r:id="rId488" xr:uid="{CC59DEAF-1EFF-452A-ACA7-DC3FF58078F5}"/>
+    <hyperlink ref="C561" r:id="rId489" xr:uid="{D1F90F1B-7BD7-45D3-820D-8E747A8C92D3}"/>
+    <hyperlink ref="C560" r:id="rId490" xr:uid="{5DBD82ED-050A-43F8-8857-D34C7E4480CF}"/>
+    <hyperlink ref="C559" r:id="rId491" xr:uid="{F412E9FE-4C23-4374-A052-04C1F51DECF3}"/>
+    <hyperlink ref="C558" r:id="rId492" xr:uid="{449D0218-88EB-46E3-B0E4-2396D7F735E4}"/>
+    <hyperlink ref="C557" r:id="rId493" xr:uid="{7D6EF784-1F9A-4B36-90F6-AE8F627E5B8E}"/>
+    <hyperlink ref="C556" r:id="rId494" xr:uid="{D8B5388E-51D0-496B-A7D3-74F358D037B4}"/>
+    <hyperlink ref="C555" r:id="rId495" xr:uid="{F9F24C9F-2E3E-4D43-A177-0E5D2ACFC3DB}"/>
+    <hyperlink ref="C554" r:id="rId496" xr:uid="{EBEB933D-B423-41C9-9335-42397362BD62}"/>
+    <hyperlink ref="C553" r:id="rId497" xr:uid="{F4DC805F-FE7E-4A06-B475-D0E38D707111}"/>
+    <hyperlink ref="C552" r:id="rId498" xr:uid="{20418103-4EDF-42B7-9CBC-B36B42BA50FC}"/>
+    <hyperlink ref="C551" r:id="rId499" xr:uid="{6E09CD2C-B320-448D-A7EA-AB8C174E2970}"/>
+    <hyperlink ref="C550" r:id="rId500" xr:uid="{6E97C3B1-4CCB-44C9-ADA0-F640C6D728C6}"/>
+    <hyperlink ref="C549" r:id="rId501" xr:uid="{A3CBBBD1-2612-4CDD-81EF-7B827025D704}"/>
+    <hyperlink ref="C548" r:id="rId502" xr:uid="{889BBB9F-9281-42CD-8162-9C391B05D0E9}"/>
+    <hyperlink ref="C547" r:id="rId503" xr:uid="{3DB128D7-B924-44A9-A7C9-E6BC79E97B53}"/>
+    <hyperlink ref="C546" r:id="rId504" location="ug" xr:uid="{DC468B40-CC91-45B4-89A6-89B34BED7BF2}"/>
+    <hyperlink ref="C545" r:id="rId505" xr:uid="{33329805-9235-4129-B754-2D7734FBDDC7}"/>
+    <hyperlink ref="C544" r:id="rId506" xr:uid="{891F2F49-6F9D-42A2-B1C4-D4C4DE0F80CE}"/>
+    <hyperlink ref="C543" r:id="rId507" xr:uid="{298C3AFD-57FA-4BA3-8E29-707970F312E7}"/>
+    <hyperlink ref="C542" r:id="rId508" xr:uid="{6B0E6526-0C2D-4948-A6DC-921C8EB514C0}"/>
+    <hyperlink ref="C541" r:id="rId509" xr:uid="{58674F07-58BA-4940-9FD6-19FEB6F9995F}"/>
+    <hyperlink ref="C540" r:id="rId510" xr:uid="{CF302509-B5CB-407F-8B80-DBDE5822D97D}"/>
+    <hyperlink ref="C539" r:id="rId511" xr:uid="{53FFE010-86CC-42DA-BACE-36ECDF356E08}"/>
+    <hyperlink ref="C538" r:id="rId512" xr:uid="{B4314B32-2437-45EE-AA5A-5436BB31A223}"/>
+    <hyperlink ref="C537" r:id="rId513" xr:uid="{644D1C8A-4F41-4B57-8560-02BF758E73C4}"/>
+    <hyperlink ref="C536" r:id="rId514" xr:uid="{E86CD9EA-CFB3-41D9-B477-51F488869BDA}"/>
+    <hyperlink ref="C535" r:id="rId515" xr:uid="{0E4455B9-563E-43B3-9B53-A67F42506607}"/>
+    <hyperlink ref="C534" r:id="rId516" xr:uid="{562E68DB-94AF-45A2-936A-29A55800A148}"/>
+    <hyperlink ref="C533" r:id="rId517" xr:uid="{3A9CECF8-3087-4F4D-9265-80DC3E35D0CD}"/>
+    <hyperlink ref="C532" r:id="rId518" xr:uid="{6D8E7DFC-8EA5-4CD5-A126-6002F2E0A49F}"/>
+    <hyperlink ref="C531" r:id="rId519" xr:uid="{4185B687-50FC-4DC7-AB12-13062EE007F1}"/>
+    <hyperlink ref="C530" r:id="rId520" xr:uid="{9F49DD3E-B4A4-459C-AB78-866AAE5F3740}"/>
+    <hyperlink ref="C529" r:id="rId521" xr:uid="{39591972-9528-46B2-B533-F57A0735C396}"/>
+    <hyperlink ref="C528" r:id="rId522" xr:uid="{6A585B48-9DED-40FF-AAD1-CA36B8D95708}"/>
+    <hyperlink ref="C527" r:id="rId523" xr:uid="{77D0E52D-2981-4747-8803-EF1ED3E783DA}"/>
+    <hyperlink ref="C526" r:id="rId524" location="campus" xr:uid="{52922C32-37C3-4208-A1F7-E78E2A373254}"/>
+    <hyperlink ref="C525" r:id="rId525" location="masters" xr:uid="{D649413F-95A1-4375-9598-286113814371}"/>
+    <hyperlink ref="C524" r:id="rId526" xr:uid="{24A3EBAB-422A-4271-B422-720A28073A9F}"/>
+    <hyperlink ref="C523" r:id="rId527" xr:uid="{88691330-C7B9-467A-98B0-95319440599C}"/>
+    <hyperlink ref="C522" r:id="rId528" xr:uid="{74DC548D-C4A3-4733-AF06-0C7DD6C62157}"/>
+    <hyperlink ref="C521" r:id="rId529" xr:uid="{57365EF2-8AB1-412F-AC9D-E719A61B491A}"/>
+    <hyperlink ref="C520" r:id="rId530" xr:uid="{CA189A21-4B9A-4BB3-B64B-17F20F3049F0}"/>
+    <hyperlink ref="C519" r:id="rId531" xr:uid="{0AE22385-9740-42F1-BA48-F8E80C6C12CB}"/>
+    <hyperlink ref="C518" r:id="rId532" xr:uid="{8F7744FB-5D44-4B28-B752-EEAF67B446C9}"/>
+    <hyperlink ref="C517" r:id="rId533" xr:uid="{284E0EA3-4A3D-4CD0-AB09-51F3DF7D52BD}"/>
+    <hyperlink ref="C516" r:id="rId534" xr:uid="{EAD90F60-C919-4409-876F-FDA530F9D9EA}"/>
+    <hyperlink ref="C515" r:id="rId535" xr:uid="{A8EBE29B-AB58-466D-A3EF-065CFB1AB505}"/>
+    <hyperlink ref="C514" r:id="rId536" xr:uid="{104E7E5B-E107-4FDA-92B8-9CF512BD0F9E}"/>
+    <hyperlink ref="C513" r:id="rId537" xr:uid="{C7E8E7F0-EE55-4307-A285-F9163015384F}"/>
+    <hyperlink ref="C512" r:id="rId538" xr:uid="{7136EEAA-B7A4-423D-B8D2-4805FE4CB0E8}"/>
+    <hyperlink ref="C511" r:id="rId539" xr:uid="{2F6E9089-4464-4A32-B725-83014A8476CB}"/>
+    <hyperlink ref="C510" r:id="rId540" xr:uid="{D857A142-E2FD-451F-96F3-53CF337B9DFF}"/>
+    <hyperlink ref="C509" r:id="rId541" location="ugrad" xr:uid="{AF7624A7-2C13-4F57-A7F2-91499AD42237}"/>
+    <hyperlink ref="C508" r:id="rId542" xr:uid="{E461EA24-B5B5-4A3D-80C4-78BDF2F74205}"/>
+    <hyperlink ref="C507" r:id="rId543" xr:uid="{512D7250-7090-4D3F-9E44-63EA4B71AC1A}"/>
+    <hyperlink ref="C506" r:id="rId544" xr:uid="{0A667B60-C992-483D-82ED-9FE1A7602842}"/>
+    <hyperlink ref="C505" r:id="rId545" xr:uid="{4D1E4B4A-02C1-48DE-AFBE-EEA62554F8FE}"/>
+    <hyperlink ref="C504" r:id="rId546" xr:uid="{FFCA64BE-D68F-4C22-B508-EEDC178D5BBD}"/>
+    <hyperlink ref="C503" r:id="rId547" xr:uid="{527B727E-029F-4D33-9D75-B6891113FFA5}"/>
+    <hyperlink ref="C502" r:id="rId548" location="daytona-beach" xr:uid="{6619E01C-C97E-413A-AE3B-E4E2F21B9D48}"/>
+    <hyperlink ref="C501" r:id="rId549" location="daytona-beach" xr:uid="{FD8E6161-B879-4E13-9A78-61F21A3C7678}"/>
+    <hyperlink ref="C500" r:id="rId550" xr:uid="{F6DE756D-B8DA-4706-AF02-A1F6271A6ACF}"/>
+    <hyperlink ref="C499" r:id="rId551" xr:uid="{22C523A6-EA73-44A9-BFA9-29091694604C}"/>
+    <hyperlink ref="C498" r:id="rId552" xr:uid="{F9693B6F-6879-48C9-A0F7-4BCE9F7C0770}"/>
+    <hyperlink ref="C497" r:id="rId553" xr:uid="{0F1E4574-5A3D-4686-87F2-93F30FC4786A}"/>
+    <hyperlink ref="C496" r:id="rId554" xr:uid="{C947CCBC-4ABC-4909-88A1-891A36C3D143}"/>
+    <hyperlink ref="C148" r:id="rId555" xr:uid="{7F6B9F29-5C0B-44BD-A010-01F97569E946}"/>
+    <hyperlink ref="C149" r:id="rId556" xr:uid="{5BE80C95-BAF0-4A58-9807-04F4F10A3392}"/>
+    <hyperlink ref="C150" r:id="rId557" xr:uid="{25AC73C5-D8D1-4A68-A0ED-2C33B0812D96}"/>
+    <hyperlink ref="C151" r:id="rId558" xr:uid="{20020986-2A6B-4DF5-A8F2-DA0825DA1250}"/>
+    <hyperlink ref="C152" r:id="rId559" xr:uid="{17F73CFB-29AD-46AB-8232-950E37B0E449}"/>
+    <hyperlink ref="C153:C155" r:id="rId560" display="https://legacy.rru.ac.in/wp-content/uploads/2024/05/Fees-Structure-SITAICS-14May2024.pdf" xr:uid="{B02E8987-C0BF-4204-9DEE-15C5487B79D4}"/>
+    <hyperlink ref="C156" r:id="rId561" xr:uid="{425719C5-F52F-47A4-A471-5E9CE58AF26F}"/>
+    <hyperlink ref="C157" r:id="rId562" xr:uid="{B475B03A-FB81-4C71-B29C-70FA7AAFFF80}"/>
+    <hyperlink ref="C159" r:id="rId563" xr:uid="{2DB408F7-F842-4D81-91E1-B7EE65A5333B}"/>
+    <hyperlink ref="C158" r:id="rId564" xr:uid="{2E087C33-3DD1-4C79-9650-FEDFAF3A4CA3}"/>
+    <hyperlink ref="C702" r:id="rId565" xr:uid="{CB6F7D4F-5238-4A25-A57A-5E2CA49D5342}"/>
+    <hyperlink ref="C703" r:id="rId566" xr:uid="{C2947CAE-69C4-4BE5-8DF0-A99CE63CD05B}"/>
+    <hyperlink ref="C704" r:id="rId567" xr:uid="{B185A001-DE46-4EE0-95BB-A4E9B6B6346C}"/>
+    <hyperlink ref="C705" r:id="rId568" xr:uid="{3D7A51E3-B2A6-4C4A-AECD-AD1A1BDE0153}"/>
+    <hyperlink ref="C707" r:id="rId569" xr:uid="{81D9600D-2B5C-4080-927F-A21B1FF13BE9}"/>
+    <hyperlink ref="C706" r:id="rId570" xr:uid="{79FCD9E3-C4DF-4EC5-940E-885C48E301D8}"/>
+    <hyperlink ref="C708" r:id="rId571" xr:uid="{6C7FE20D-7316-4C13-8984-F397B99D740A}"/>
+    <hyperlink ref="C709" r:id="rId572" xr:uid="{C1038379-2771-4E84-9F19-D016F4ECC3E2}"/>
+    <hyperlink ref="C710:C711" r:id="rId573" display="https://drive.google.com/file/d/1fmepJ31Dfjm_qh5g_wunPXVkMUXKCSpc/view?usp=drive_link" xr:uid="{B72A07BB-EE24-4372-A901-142BDEB56755}"/>
+    <hyperlink ref="C712" r:id="rId574" xr:uid="{C95CACC9-22F3-4D48-8ABB-088984800843}"/>
+    <hyperlink ref="C714" r:id="rId575" xr:uid="{857B428D-FF38-4DDB-8BF7-216A91ED3B1E}"/>
+    <hyperlink ref="C713" r:id="rId576" xr:uid="{6F5B5F2A-9EAF-431A-B12D-848D191E74B5}"/>
+    <hyperlink ref="C715" r:id="rId577" xr:uid="{B5F7EFD7-D7A0-447F-8D0B-BEAA0E423624}"/>
+    <hyperlink ref="C716:C717" r:id="rId578" display="https://adypu.edu.in/wp-content/uploads/2024/07/20.ADYPU_Fees-Structure_24_25.pdf" xr:uid="{8E209706-7354-43E9-9E76-780A501BF850}"/>
+    <hyperlink ref="C718" r:id="rId579" xr:uid="{93B84C99-C0B6-427E-B792-003A6B811699}"/>
+    <hyperlink ref="C719" r:id="rId580" xr:uid="{D108B0AB-F2B0-4489-85FF-B2A32E48718F}"/>
+    <hyperlink ref="C720" r:id="rId581" xr:uid="{4A5AE46C-3678-4870-8072-2C019224F376}"/>
+    <hyperlink ref="C721" r:id="rId582" xr:uid="{87423149-8C1C-417F-8927-BA7D7AB22193}"/>
+    <hyperlink ref="C722" r:id="rId583" xr:uid="{45FBAD21-C7D2-4739-92B6-FD2076623CFA}"/>
+    <hyperlink ref="C723" r:id="rId584" xr:uid="{6186688D-F4AE-4360-8BB9-B9A4B17BEDF6}"/>
+    <hyperlink ref="C724" r:id="rId585" xr:uid="{3590360E-D482-446B-9F79-4FFE7C1C073A}"/>
+    <hyperlink ref="C725" r:id="rId586" xr:uid="{BC14503A-7E37-4FFA-9650-52DD0EADF29A}"/>
+    <hyperlink ref="C726" r:id="rId587" xr:uid="{DFDE858C-3C0E-40F6-9020-84277BF915FB}"/>
+    <hyperlink ref="C727" r:id="rId588" xr:uid="{E1D751F8-CB65-4034-804F-EA8E8F306747}"/>
+    <hyperlink ref="C728" r:id="rId589" xr:uid="{8665E79A-CE2F-45D2-BDDF-83DA3585472B}"/>
+    <hyperlink ref="C729" r:id="rId590" xr:uid="{B04D9CA0-2E77-46DA-8B87-8F1D8EF9C049}"/>
+    <hyperlink ref="C730" r:id="rId591" xr:uid="{FC3E61AF-9A93-4DBC-8CA2-A1C543CDB7D8}"/>
+    <hyperlink ref="C731" r:id="rId592" xr:uid="{68780992-6DAA-46A8-B8B4-B4BBA2917299}"/>
+    <hyperlink ref="C732" r:id="rId593" xr:uid="{C7172857-AB2C-429C-B752-E3089788612D}"/>
+    <hyperlink ref="C733" r:id="rId594" xr:uid="{3F50DD60-5393-43B0-8FFA-68A491669212}"/>
+    <hyperlink ref="C734" r:id="rId595" xr:uid="{C2627F34-5141-4887-A16B-CBF356C57E75}"/>
+    <hyperlink ref="C735" r:id="rId596" xr:uid="{EDED4804-2A29-4FCF-B16F-9093CA1F3402}"/>
+    <hyperlink ref="C736" r:id="rId597" xr:uid="{2906778E-2DEE-4AF6-B797-56BD3D3C92ED}"/>
+    <hyperlink ref="C737" r:id="rId598" xr:uid="{CF7BF210-6C7C-4748-B136-7D7D48E92F53}"/>
+    <hyperlink ref="C738" r:id="rId599" xr:uid="{9F8F3B0F-5923-4A92-AA17-551220766D9C}"/>
+    <hyperlink ref="C739" r:id="rId600" xr:uid="{D4072CFA-7E3A-4A31-924C-881FC018FA1A}"/>
+    <hyperlink ref="C741" r:id="rId601" xr:uid="{52487C8C-5AFB-4B5D-B5DF-9746B10422F0}"/>
+    <hyperlink ref="C740" r:id="rId602" xr:uid="{CF4335A8-2F33-49DD-A1EF-E4E9C570D98B}"/>
+    <hyperlink ref="C742" r:id="rId603" xr:uid="{9C63E6AF-038B-4C76-ADBA-E8DAFFC07E08}"/>
+    <hyperlink ref="C743" r:id="rId604" xr:uid="{E8B25F31-922E-4758-B02E-98B6F7060A88}"/>
+    <hyperlink ref="C744" r:id="rId605" xr:uid="{ABBAA515-0609-486C-BF64-FC3D99099187}"/>
+    <hyperlink ref="C745" r:id="rId606" xr:uid="{C00DB4FA-AF1D-4613-90A1-6FA57556076F}"/>
+    <hyperlink ref="C746" r:id="rId607" xr:uid="{CD016168-6D69-4F69-B68F-AA2EC32DFF6B}"/>
+    <hyperlink ref="C747" r:id="rId608" xr:uid="{CBE487E3-FACC-4B31-A120-61DC195C4D23}"/>
+    <hyperlink ref="C748" r:id="rId609" xr:uid="{EA090370-5F35-4063-959B-C8ADF669CEDE}"/>
+    <hyperlink ref="C749" r:id="rId610" xr:uid="{149D1ED3-CD53-4AE1-864A-A603DE5D12BC}"/>
+    <hyperlink ref="C750" r:id="rId611" xr:uid="{F017CC9E-0054-49FE-89AF-2D059AF6377F}"/>
+    <hyperlink ref="C751:C761" r:id="rId612" display="https://beta.nfsu.ac.in/data/pdfs/admission/Programme%20Details.pdf" xr:uid="{3B4E76B5-095C-45FE-B0CF-148644D9E11A}"/>
+    <hyperlink ref="C762" r:id="rId613" xr:uid="{B9D39B54-5728-4732-ACBF-88C9E7BB69BC}"/>
+    <hyperlink ref="C763" r:id="rId614" xr:uid="{5B64FB65-FE64-4A6B-AC64-EFC901A56244}"/>
+    <hyperlink ref="C764" r:id="rId615" xr:uid="{8C07BE98-0EA8-4A43-AF2B-442367D94176}"/>
+    <hyperlink ref="C765" r:id="rId616" xr:uid="{3355522E-84C3-495A-8C36-08E1DE7E740B}"/>
+    <hyperlink ref="C767" r:id="rId617" xr:uid="{B8C3CA87-1E12-457E-A5EA-C907F81668CD}"/>
+    <hyperlink ref="C768" r:id="rId618" xr:uid="{EC7491DD-D308-4AE6-824C-E20C1B0A063C}"/>
+    <hyperlink ref="C769" r:id="rId619" xr:uid="{CE4036C3-C29B-4E9A-BA2F-4103F4685B9D}"/>
+    <hyperlink ref="C161" r:id="rId620" xr:uid="{8DD02B6F-54A2-4FAC-B961-2C220AA1D943}"/>
+    <hyperlink ref="C162" r:id="rId621" xr:uid="{ED2940C7-EB7F-4547-BEC9-673E028B1F6E}"/>
+    <hyperlink ref="C770" r:id="rId622" xr:uid="{4015FD70-74FB-4621-A2FD-7986807085D5}"/>
+    <hyperlink ref="C771" r:id="rId623" xr:uid="{1F87E026-2DE2-4DBC-83B3-D6B951EA1E3C}"/>
+    <hyperlink ref="C772" r:id="rId624" xr:uid="{D6BE8929-2D3C-4A7B-BBAF-A4A4EE063EF8}"/>
+    <hyperlink ref="C773" r:id="rId625" xr:uid="{9DD1D3EA-72B8-45E8-BDA9-021B474CA435}"/>
+    <hyperlink ref="C774" r:id="rId626" xr:uid="{1BEB74B5-CAC1-4F1D-A056-DDD1E6CDBF96}"/>
+    <hyperlink ref="C775" r:id="rId627" xr:uid="{3073747A-DA6A-4CE0-A0B7-7AA867EE17D6}"/>
+    <hyperlink ref="C776" r:id="rId628" xr:uid="{B4E301A8-90DD-46D6-976D-FBA6A1684A1F}"/>
+    <hyperlink ref="C777" r:id="rId629" xr:uid="{CD3DDDEF-3C39-40EC-8B04-FA8675A7977F}"/>
+    <hyperlink ref="C778" r:id="rId630" xr:uid="{65D284DB-F879-47B9-A268-DFBC28C219E5}"/>
+    <hyperlink ref="C779" r:id="rId631" xr:uid="{3AF0420D-3F28-4CBB-BAE4-39DCD9DAEF50}"/>
+    <hyperlink ref="C51" r:id="rId632" xr:uid="{ECEE7BB5-A33D-4352-A89E-8D249C116DCB}"/>
+    <hyperlink ref="C455" r:id="rId633" xr:uid="{973FDA1F-DE1F-48CE-BE77-75DC093E98AA}"/>
+    <hyperlink ref="C366" r:id="rId634" xr:uid="{4696752E-5EF9-49D9-8362-5A976A1F5B12}"/>
+    <hyperlink ref="C365" r:id="rId635" xr:uid="{36DF91A2-AE4E-448A-A9E7-A1F91838B227}"/>
+    <hyperlink ref="C362" r:id="rId636" xr:uid="{09480EB5-1061-45DB-AA34-BC6317432F73}"/>
+    <hyperlink ref="C359" r:id="rId637" xr:uid="{4C8A3339-5E9D-44A2-851B-38820E24A7C1}"/>
+    <hyperlink ref="C457" r:id="rId638" xr:uid="{635DE0D8-AFDF-4529-93F2-B5CCE74EF50C}"/>
+    <hyperlink ref="C780" r:id="rId639" xr:uid="{BC6B2562-6B84-425C-9B87-36CDC918AC76}"/>
+    <hyperlink ref="C781" r:id="rId640" xr:uid="{D521C8BF-0148-4A06-80F7-96B5FD3E47F7}"/>
+    <hyperlink ref="C782" r:id="rId641" xr:uid="{89DA4F63-868B-410D-8AFE-DEAE3F4D14CF}"/>
+    <hyperlink ref="C783" r:id="rId642" xr:uid="{F240B56A-A908-4554-A031-75ABA7FACF20}"/>
+    <hyperlink ref="C784" r:id="rId643" xr:uid="{C6533D41-F550-4BED-9C7C-02E70C8DFA0D}"/>
+    <hyperlink ref="C766" r:id="rId644" xr:uid="{29B0C30A-FA81-4314-A11E-2CF9021B0C5D}"/>
+    <hyperlink ref="C785" r:id="rId645" xr:uid="{1DD05091-13EF-4185-8598-42B2C13DD25A}"/>
+    <hyperlink ref="C597" r:id="rId646" xr:uid="{AAD3B5F2-348C-4D6F-B2DC-32F09F0A9B13}"/>
+    <hyperlink ref="C596" r:id="rId647" xr:uid="{664C10D8-0E38-4804-B463-7F0186B1738E}"/>
+    <hyperlink ref="C598" r:id="rId648" xr:uid="{0A368D49-1F7C-4FA0-82FD-8A76D82CD659}"/>
+    <hyperlink ref="C786" r:id="rId649" xr:uid="{B1CFA210-9743-4205-9904-B22C9F9EBED7}"/>
+    <hyperlink ref="C787" r:id="rId650" xr:uid="{4D483717-7B75-4C1D-BAF2-3E13CC02FA4B}"/>
+    <hyperlink ref="C788" r:id="rId651" xr:uid="{BA58CA45-509E-4E2D-86A7-BCE34C89B704}"/>
+    <hyperlink ref="C303:C333" r:id="rId652" display="https://drive.google.com/file/d/1rdC7GBkH0w9zhAf2amRYlhGy3XpyonNb/view?usp=sharing" xr:uid="{E91BE0FE-8E7E-48D7-BA46-4B39CE5567C7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/fees.xlsx
+++ b/fees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Shlok Parekh\Downloads\Course-Verifier-3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E367B9E-66D2-4B6D-AD62-AF783A6CA707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C584C692-DEF1-47B8-90F7-239EA9455D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
   </bookViews>

--- a/fees.xlsx
+++ b/fees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Shlok Parekh\Downloads\Course-Verifier-3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C584C692-DEF1-47B8-90F7-239EA9455D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB54BE9-9748-4D35-BFEF-A1DDE6F3FAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="1642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="1645">
   <si>
     <t>Acharya Nagarjuna University</t>
   </si>
@@ -4977,6 +4977,15 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/121extnlXkoHQN1PRdacr7yKqTiQ3P52n/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Dr. D. Y. Patil Arts, Commerce &amp; Science College, Pimpri, Pune</t>
+  </si>
+  <si>
+    <t>B.Sc (Cyber and Digital Science)</t>
+  </si>
+  <si>
+    <t>https://acs.dypvp.edu.in/DownloadS3File.aspx?file=UG-fee-structure-26-27</t>
   </si>
 </sst>
 </file>
@@ -14384,8 +14393,16 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C790" s="21"/>
+    <row r="790" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A790" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C790" s="12" t="s">
+        <v>1644</v>
+      </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C791" s="21"/>
@@ -19799,10 +19816,11 @@
     <hyperlink ref="C328" r:id="rId653" xr:uid="{70C06AF8-BDAF-4E1C-96A2-426717989049}"/>
     <hyperlink ref="C302:C327" r:id="rId654" display="https://drive.google.com/file/d/1rdC7GBkH0w9zhAf2amRYlhGy3XpyonNb/view?usp=sharing" xr:uid="{10D40540-1E43-4456-898C-E35DA9DE0070}"/>
     <hyperlink ref="C329:C331" r:id="rId655" display="https://drive.google.com/file/d/1rdC7GBkH0w9zhAf2amRYlhGy3XpyonNb/view?usp=sharing" xr:uid="{73611974-6B47-494F-B05E-78A491B04B35}"/>
+    <hyperlink ref="C790" r:id="rId656" xr:uid="{5E2299AA-1280-4E52-B85F-61AE3BFCACF0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId656"/>
+    <tablePart r:id="rId657"/>
   </tableParts>
 </worksheet>
 </file>
--- a/fees.xlsx
+++ b/fees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Shlok Parekh\Downloads\Course-Verifier-3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB54BE9-9748-4D35-BFEF-A1DDE6F3FAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B9FDF0-14BA-4724-9C29-B6D4024BAE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="601" xr2:uid="{A0B92721-7CDF-495E-B956-6055A365BC29}"/>
   </bookViews>
